--- a/ground_truth2.xlsx
+++ b/ground_truth2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OlavoDefendiDalberto\Projetos\TriaLogic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F3A35C4-81CA-4FAA-8387-8AEC636F3EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E863548D-3E61-4FE8-A293-8ECE53D2C232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="24">
   <si>
     <t>subject_id</t>
   </si>
@@ -132,7 +132,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,6 +161,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -182,7 +188,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -229,11 +235,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -245,6 +260,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1390,15 +1412,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P157"/>
+  <dimension ref="A1:P354"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" customWidth="1"/>
@@ -1416,7 +1439,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
@@ -1844,6 +1867,9 @@
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="5"/>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
       <c r="L10" t="s">
         <v>16</v>
       </c>
@@ -2628,6 +2654,9 @@
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="5"/>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
       <c r="L28" t="s">
         <v>16</v>
       </c>
@@ -3547,6 +3576,9 @@
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="5"/>
+      <c r="K49" t="b">
+        <v>0</v>
+      </c>
       <c r="L49" t="s">
         <v>16</v>
       </c>
@@ -3823,6 +3855,9 @@
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="5"/>
+      <c r="K56" t="b">
+        <v>0</v>
+      </c>
       <c r="L56" t="s">
         <v>16</v>
       </c>
@@ -3958,6 +3993,9 @@
       </c>
       <c r="D60" s="7"/>
       <c r="E60" s="4"/>
+      <c r="K60" t="b">
+        <v>0</v>
+      </c>
       <c r="L60" t="s">
         <v>16</v>
       </c>
@@ -4588,6 +4626,9 @@
       </c>
       <c r="D74" s="7"/>
       <c r="E74" s="4"/>
+      <c r="K74" t="b">
+        <v>0</v>
+      </c>
       <c r="L74" t="s">
         <v>16</v>
       </c>
@@ -5207,7 +5248,7 @@
         <v>16</v>
       </c>
       <c r="M88" t="str">
-        <f>IF(L88="Confusion", "Alert", L88)</f>
+        <f t="shared" ref="M88:M119" si="0">IF(L88="Confusion", "Alert", L88)</f>
         <v>Alert</v>
       </c>
       <c r="N88">
@@ -5248,14 +5289,14 @@
       <c r="J89" t="s">
         <v>23</v>
       </c>
-      <c r="K89" t="s">
-        <v>23</v>
+      <c r="K89" t="b">
+        <v>0</v>
       </c>
       <c r="L89" t="s">
         <v>16</v>
       </c>
       <c r="M89" t="str">
-        <f>IF(L89="Confusion", "Alert", L89)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N89" t="s">
@@ -5303,7 +5344,7 @@
         <v>16</v>
       </c>
       <c r="M90" t="str">
-        <f>IF(L90="Confusion", "Alert", L90)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N90">
@@ -5351,7 +5392,7 @@
         <v>16</v>
       </c>
       <c r="M91" t="str">
-        <f>IF(L91="Confusion", "Alert", L91)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N91" t="s">
@@ -5399,15 +5440,15 @@
         <v>16</v>
       </c>
       <c r="M92" t="str">
-        <f>IF(L92="Confusion", "Alert", L92)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N92">
-        <f>IF(I92&lt;9,2,IF(I92&lt;=14,0,IF(I92&lt;=20,1,IF(I92&lt;=29,2,3)))) + IF(H92&lt;40,2,IF(H92&lt;=50,1,IF(H92&lt;=100,0,IF(H92&lt;=110,1,IF(H92&lt;=129,2,3))))) + IF(F92&lt;=70,3,IF(F92&lt;=80,2,IF(F92&lt;=100,1,IF(F92&lt;=199,0,2)))) + IF(E92&lt;35,2,IF(E92&lt;=38.4,0,IF(E92&lt;=38.9,1,2))) + IF(M92="Alert",0,IF(M92="Voice",1,IF(M92="Pain",2,IF(M92="Unresponsive",3,0))))</f>
+        <f t="shared" ref="N92:N97" si="1">IF(I92&lt;9,2,IF(I92&lt;=14,0,IF(I92&lt;=20,1,IF(I92&lt;=29,2,3)))) + IF(H92&lt;40,2,IF(H92&lt;=50,1,IF(H92&lt;=100,0,IF(H92&lt;=110,1,IF(H92&lt;=129,2,3))))) + IF(F92&lt;=70,3,IF(F92&lt;=80,2,IF(F92&lt;=100,1,IF(F92&lt;=199,0,2)))) + IF(E92&lt;35,2,IF(E92&lt;=38.4,0,IF(E92&lt;=38.9,1,2))) + IF(M92="Alert",0,IF(M92="Voice",1,IF(M92="Pain",2,IF(M92="Unresponsive",3,0))))</f>
         <v>1</v>
       </c>
       <c r="O92">
-        <f>IF(I92&lt;=8,3,IF(I92&lt;=11,1,IF(I92&lt;=20,0,IF(I92&lt;=24,2,3)))) + IF(J92&lt;=91,3,IF(J92&lt;=93,2,IF(J92&lt;=95,1,0))) + IF(K92=TRUE,2,0) + IF(F92&lt;=90,3,IF(F92&lt;=100,2,IF(F92&lt;=110,1,IF(F92&lt;=219,0,3)))) + IF(H92&lt;=40,3,IF(H92&lt;=50,1,IF(H92&lt;=90,0,IF(H92&lt;=110,1,IF(H92&lt;=130,2,3))))) + IF(E92&lt;=35,3,IF(E92&lt;=36,1,IF(E92&lt;=38,0,IF(E92&lt;=39,1,2)))) + IF(L92="Alert",0,3)</f>
+        <f t="shared" ref="O92:O97" si="2">IF(I92&lt;=8,3,IF(I92&lt;=11,1,IF(I92&lt;=20,0,IF(I92&lt;=24,2,3)))) + IF(J92&lt;=91,3,IF(J92&lt;=93,2,IF(J92&lt;=95,1,0))) + IF(K92=TRUE,2,0) + IF(F92&lt;=90,3,IF(F92&lt;=100,2,IF(F92&lt;=110,1,IF(F92&lt;=219,0,3)))) + IF(H92&lt;=40,3,IF(H92&lt;=50,1,IF(H92&lt;=90,0,IF(H92&lt;=110,1,IF(H92&lt;=130,2,3))))) + IF(E92&lt;=35,3,IF(E92&lt;=36,1,IF(E92&lt;=38,0,IF(E92&lt;=39,1,2)))) + IF(L92="Alert",0,3)</f>
         <v>0</v>
       </c>
     </row>
@@ -5449,15 +5490,15 @@
         <v>19</v>
       </c>
       <c r="M93" t="str">
-        <f>IF(L93="Confusion", "Alert", L93)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N93">
-        <f>IF(I93&lt;9,2,IF(I93&lt;=14,0,IF(I93&lt;=20,1,IF(I93&lt;=29,2,3)))) + IF(H93&lt;40,2,IF(H93&lt;=50,1,IF(H93&lt;=100,0,IF(H93&lt;=110,1,IF(H93&lt;=129,2,3))))) + IF(F93&lt;=70,3,IF(F93&lt;=80,2,IF(F93&lt;=100,1,IF(F93&lt;=199,0,2)))) + IF(E93&lt;35,2,IF(E93&lt;=38.4,0,IF(E93&lt;=38.9,1,2))) + IF(M93="Alert",0,IF(M93="Voice",1,IF(M93="Pain",2,IF(M93="Unresponsive",3,0))))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="O93">
-        <f>IF(I93&lt;=8,3,IF(I93&lt;=11,1,IF(I93&lt;=20,0,IF(I93&lt;=24,2,3)))) + IF(J93&lt;=91,3,IF(J93&lt;=93,2,IF(J93&lt;=95,1,0))) + IF(K93=TRUE,2,0) + IF(F93&lt;=90,3,IF(F93&lt;=100,2,IF(F93&lt;=110,1,IF(F93&lt;=219,0,3)))) + IF(H93&lt;=40,3,IF(H93&lt;=50,1,IF(H93&lt;=90,0,IF(H93&lt;=110,1,IF(H93&lt;=130,2,3))))) + IF(E93&lt;=35,3,IF(E93&lt;=36,1,IF(E93&lt;=38,0,IF(E93&lt;=39,1,2)))) + IF(L93="Alert",0,3)</f>
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
     </row>
@@ -5499,15 +5540,15 @@
         <v>16</v>
       </c>
       <c r="M94" t="str">
-        <f>IF(L94="Confusion", "Alert", L94)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N94">
-        <f>IF(I94&lt;9,2,IF(I94&lt;=14,0,IF(I94&lt;=20,1,IF(I94&lt;=29,2,3)))) + IF(H94&lt;40,2,IF(H94&lt;=50,1,IF(H94&lt;=100,0,IF(H94&lt;=110,1,IF(H94&lt;=129,2,3))))) + IF(F94&lt;=70,3,IF(F94&lt;=80,2,IF(F94&lt;=100,1,IF(F94&lt;=199,0,2)))) + IF(E94&lt;35,2,IF(E94&lt;=38.4,0,IF(E94&lt;=38.9,1,2))) + IF(M94="Alert",0,IF(M94="Voice",1,IF(M94="Pain",2,IF(M94="Unresponsive",3,0))))</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="O94">
-        <f>IF(I94&lt;=8,3,IF(I94&lt;=11,1,IF(I94&lt;=20,0,IF(I94&lt;=24,2,3)))) + IF(J94&lt;=91,3,IF(J94&lt;=93,2,IF(J94&lt;=95,1,0))) + IF(K94=TRUE,2,0) + IF(F94&lt;=90,3,IF(F94&lt;=100,2,IF(F94&lt;=110,1,IF(F94&lt;=219,0,3)))) + IF(H94&lt;=40,3,IF(H94&lt;=50,1,IF(H94&lt;=90,0,IF(H94&lt;=110,1,IF(H94&lt;=130,2,3))))) + IF(E94&lt;=35,3,IF(E94&lt;=36,1,IF(E94&lt;=38,0,IF(E94&lt;=39,1,2)))) + IF(L94="Alert",0,3)</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
     </row>
@@ -5549,15 +5590,15 @@
         <v>16</v>
       </c>
       <c r="M95" t="str">
-        <f>IF(L95="Confusion", "Alert", L95)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N95">
-        <f>IF(I95&lt;9,2,IF(I95&lt;=14,0,IF(I95&lt;=20,1,IF(I95&lt;=29,2,3)))) + IF(H95&lt;40,2,IF(H95&lt;=50,1,IF(H95&lt;=100,0,IF(H95&lt;=110,1,IF(H95&lt;=129,2,3))))) + IF(F95&lt;=70,3,IF(F95&lt;=80,2,IF(F95&lt;=100,1,IF(F95&lt;=199,0,2)))) + IF(E95&lt;35,2,IF(E95&lt;=38.4,0,IF(E95&lt;=38.9,1,2))) + IF(M95="Alert",0,IF(M95="Voice",1,IF(M95="Pain",2,IF(M95="Unresponsive",3,0))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O95">
-        <f>IF(I95&lt;=8,3,IF(I95&lt;=11,1,IF(I95&lt;=20,0,IF(I95&lt;=24,2,3)))) + IF(J95&lt;=91,3,IF(J95&lt;=93,2,IF(J95&lt;=95,1,0))) + IF(K95=TRUE,2,0) + IF(F95&lt;=90,3,IF(F95&lt;=100,2,IF(F95&lt;=110,1,IF(F95&lt;=219,0,3)))) + IF(H95&lt;=40,3,IF(H95&lt;=50,1,IF(H95&lt;=90,0,IF(H95&lt;=110,1,IF(H95&lt;=130,2,3))))) + IF(E95&lt;=35,3,IF(E95&lt;=36,1,IF(E95&lt;=38,0,IF(E95&lt;=39,1,2)))) + IF(L95="Alert",0,3)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5599,15 +5640,15 @@
         <v>16</v>
       </c>
       <c r="M96" t="str">
-        <f>IF(L96="Confusion", "Alert", L96)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N96">
-        <f>IF(I96&lt;9,2,IF(I96&lt;=14,0,IF(I96&lt;=20,1,IF(I96&lt;=29,2,3)))) + IF(H96&lt;40,2,IF(H96&lt;=50,1,IF(H96&lt;=100,0,IF(H96&lt;=110,1,IF(H96&lt;=129,2,3))))) + IF(F96&lt;=70,3,IF(F96&lt;=80,2,IF(F96&lt;=100,1,IF(F96&lt;=199,0,2)))) + IF(E96&lt;35,2,IF(E96&lt;=38.4,0,IF(E96&lt;=38.9,1,2))) + IF(M96="Alert",0,IF(M96="Voice",1,IF(M96="Pain",2,IF(M96="Unresponsive",3,0))))</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="O96">
-        <f>IF(I96&lt;=8,3,IF(I96&lt;=11,1,IF(I96&lt;=20,0,IF(I96&lt;=24,2,3)))) + IF(J96&lt;=91,3,IF(J96&lt;=93,2,IF(J96&lt;=95,1,0))) + IF(K96=TRUE,2,0) + IF(F96&lt;=90,3,IF(F96&lt;=100,2,IF(F96&lt;=110,1,IF(F96&lt;=219,0,3)))) + IF(H96&lt;=40,3,IF(H96&lt;=50,1,IF(H96&lt;=90,0,IF(H96&lt;=110,1,IF(H96&lt;=130,2,3))))) + IF(E96&lt;=35,3,IF(E96&lt;=36,1,IF(E96&lt;=38,0,IF(E96&lt;=39,1,2)))) + IF(L96="Alert",0,3)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -5649,15 +5690,15 @@
         <v>16</v>
       </c>
       <c r="M97" t="str">
-        <f>IF(L97="Confusion", "Alert", L97)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N97">
-        <f>IF(I97&lt;9,2,IF(I97&lt;=14,0,IF(I97&lt;=20,1,IF(I97&lt;=29,2,3)))) + IF(H97&lt;40,2,IF(H97&lt;=50,1,IF(H97&lt;=100,0,IF(H97&lt;=110,1,IF(H97&lt;=129,2,3))))) + IF(F97&lt;=70,3,IF(F97&lt;=80,2,IF(F97&lt;=100,1,IF(F97&lt;=199,0,2)))) + IF(E97&lt;35,2,IF(E97&lt;=38.4,0,IF(E97&lt;=38.9,1,2))) + IF(M97="Alert",0,IF(M97="Voice",1,IF(M97="Pain",2,IF(M97="Unresponsive",3,0))))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="O97">
-        <f>IF(I97&lt;=8,3,IF(I97&lt;=11,1,IF(I97&lt;=20,0,IF(I97&lt;=24,2,3)))) + IF(J97&lt;=91,3,IF(J97&lt;=93,2,IF(J97&lt;=95,1,0))) + IF(K97=TRUE,2,0) + IF(F97&lt;=90,3,IF(F97&lt;=100,2,IF(F97&lt;=110,1,IF(F97&lt;=219,0,3)))) + IF(H97&lt;=40,3,IF(H97&lt;=50,1,IF(H97&lt;=90,0,IF(H97&lt;=110,1,IF(H97&lt;=130,2,3))))) + IF(E97&lt;=35,3,IF(E97&lt;=36,1,IF(E97&lt;=38,0,IF(E97&lt;=39,1,2)))) + IF(L97="Alert",0,3)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5690,14 +5731,14 @@
       <c r="J98">
         <v>100</v>
       </c>
-      <c r="K98" t="s">
-        <v>23</v>
+      <c r="K98" t="b">
+        <v>0</v>
       </c>
       <c r="L98" t="s">
         <v>16</v>
       </c>
       <c r="M98" t="str">
-        <f>IF(L98="Confusion", "Alert", L98)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N98" t="s">
@@ -5745,15 +5786,15 @@
         <v>16</v>
       </c>
       <c r="M99" t="str">
-        <f>IF(L99="Confusion", "Alert", L99)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N99">
-        <f>IF(I99&lt;9,2,IF(I99&lt;=14,0,IF(I99&lt;=20,1,IF(I99&lt;=29,2,3)))) + IF(H99&lt;40,2,IF(H99&lt;=50,1,IF(H99&lt;=100,0,IF(H99&lt;=110,1,IF(H99&lt;=129,2,3))))) + IF(F99&lt;=70,3,IF(F99&lt;=80,2,IF(F99&lt;=100,1,IF(F99&lt;=199,0,2)))) + IF(E99&lt;35,2,IF(E99&lt;=38.4,0,IF(E99&lt;=38.9,1,2))) + IF(M99="Alert",0,IF(M99="Voice",1,IF(M99="Pain",2,IF(M99="Unresponsive",3,0))))</f>
+        <f t="shared" ref="N99:N116" si="3">IF(I99&lt;9,2,IF(I99&lt;=14,0,IF(I99&lt;=20,1,IF(I99&lt;=29,2,3)))) + IF(H99&lt;40,2,IF(H99&lt;=50,1,IF(H99&lt;=100,0,IF(H99&lt;=110,1,IF(H99&lt;=129,2,3))))) + IF(F99&lt;=70,3,IF(F99&lt;=80,2,IF(F99&lt;=100,1,IF(F99&lt;=199,0,2)))) + IF(E99&lt;35,2,IF(E99&lt;=38.4,0,IF(E99&lt;=38.9,1,2))) + IF(M99="Alert",0,IF(M99="Voice",1,IF(M99="Pain",2,IF(M99="Unresponsive",3,0))))</f>
         <v>1</v>
       </c>
       <c r="O99">
-        <f>IF(I99&lt;=8,3,IF(I99&lt;=11,1,IF(I99&lt;=20,0,IF(I99&lt;=24,2,3)))) + IF(J99&lt;=91,3,IF(J99&lt;=93,2,IF(J99&lt;=95,1,0))) + IF(K99=TRUE,2,0) + IF(F99&lt;=90,3,IF(F99&lt;=100,2,IF(F99&lt;=110,1,IF(F99&lt;=219,0,3)))) + IF(H99&lt;=40,3,IF(H99&lt;=50,1,IF(H99&lt;=90,0,IF(H99&lt;=110,1,IF(H99&lt;=130,2,3))))) + IF(E99&lt;=35,3,IF(E99&lt;=36,1,IF(E99&lt;=38,0,IF(E99&lt;=39,1,2)))) + IF(L99="Alert",0,3)</f>
+        <f t="shared" ref="O99:O116" si="4">IF(I99&lt;=8,3,IF(I99&lt;=11,1,IF(I99&lt;=20,0,IF(I99&lt;=24,2,3)))) + IF(J99&lt;=91,3,IF(J99&lt;=93,2,IF(J99&lt;=95,1,0))) + IF(K99=TRUE,2,0) + IF(F99&lt;=90,3,IF(F99&lt;=100,2,IF(F99&lt;=110,1,IF(F99&lt;=219,0,3)))) + IF(H99&lt;=40,3,IF(H99&lt;=50,1,IF(H99&lt;=90,0,IF(H99&lt;=110,1,IF(H99&lt;=130,2,3))))) + IF(E99&lt;=35,3,IF(E99&lt;=36,1,IF(E99&lt;=38,0,IF(E99&lt;=39,1,2)))) + IF(L99="Alert",0,3)</f>
         <v>1</v>
       </c>
     </row>
@@ -5795,15 +5836,15 @@
         <v>16</v>
       </c>
       <c r="M100" t="str">
-        <f>IF(L100="Confusion", "Alert", L100)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N100">
-        <f>IF(I100&lt;9,2,IF(I100&lt;=14,0,IF(I100&lt;=20,1,IF(I100&lt;=29,2,3)))) + IF(H100&lt;40,2,IF(H100&lt;=50,1,IF(H100&lt;=100,0,IF(H100&lt;=110,1,IF(H100&lt;=129,2,3))))) + IF(F100&lt;=70,3,IF(F100&lt;=80,2,IF(F100&lt;=100,1,IF(F100&lt;=199,0,2)))) + IF(E100&lt;35,2,IF(E100&lt;=38.4,0,IF(E100&lt;=38.9,1,2))) + IF(M100="Alert",0,IF(M100="Voice",1,IF(M100="Pain",2,IF(M100="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O100">
-        <f>IF(I100&lt;=8,3,IF(I100&lt;=11,1,IF(I100&lt;=20,0,IF(I100&lt;=24,2,3)))) + IF(J100&lt;=91,3,IF(J100&lt;=93,2,IF(J100&lt;=95,1,0))) + IF(K100=TRUE,2,0) + IF(F100&lt;=90,3,IF(F100&lt;=100,2,IF(F100&lt;=110,1,IF(F100&lt;=219,0,3)))) + IF(H100&lt;=40,3,IF(H100&lt;=50,1,IF(H100&lt;=90,0,IF(H100&lt;=110,1,IF(H100&lt;=130,2,3))))) + IF(E100&lt;=35,3,IF(E100&lt;=36,1,IF(E100&lt;=38,0,IF(E100&lt;=39,1,2)))) + IF(L100="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -5845,15 +5886,15 @@
         <v>16</v>
       </c>
       <c r="M101" t="str">
-        <f>IF(L101="Confusion", "Alert", L101)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N101">
-        <f>IF(I101&lt;9,2,IF(I101&lt;=14,0,IF(I101&lt;=20,1,IF(I101&lt;=29,2,3)))) + IF(H101&lt;40,2,IF(H101&lt;=50,1,IF(H101&lt;=100,0,IF(H101&lt;=110,1,IF(H101&lt;=129,2,3))))) + IF(F101&lt;=70,3,IF(F101&lt;=80,2,IF(F101&lt;=100,1,IF(F101&lt;=199,0,2)))) + IF(E101&lt;35,2,IF(E101&lt;=38.4,0,IF(E101&lt;=38.9,1,2))) + IF(M101="Alert",0,IF(M101="Voice",1,IF(M101="Pain",2,IF(M101="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="O101">
-        <f>IF(I101&lt;=8,3,IF(I101&lt;=11,1,IF(I101&lt;=20,0,IF(I101&lt;=24,2,3)))) + IF(J101&lt;=91,3,IF(J101&lt;=93,2,IF(J101&lt;=95,1,0))) + IF(K101=TRUE,2,0) + IF(F101&lt;=90,3,IF(F101&lt;=100,2,IF(F101&lt;=110,1,IF(F101&lt;=219,0,3)))) + IF(H101&lt;=40,3,IF(H101&lt;=50,1,IF(H101&lt;=90,0,IF(H101&lt;=110,1,IF(H101&lt;=130,2,3))))) + IF(E101&lt;=35,3,IF(E101&lt;=36,1,IF(E101&lt;=38,0,IF(E101&lt;=39,1,2)))) + IF(L101="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
     </row>
@@ -5895,15 +5936,15 @@
         <v>16</v>
       </c>
       <c r="M102" t="str">
-        <f>IF(L102="Confusion", "Alert", L102)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N102">
-        <f>IF(I102&lt;9,2,IF(I102&lt;=14,0,IF(I102&lt;=20,1,IF(I102&lt;=29,2,3)))) + IF(H102&lt;40,2,IF(H102&lt;=50,1,IF(H102&lt;=100,0,IF(H102&lt;=110,1,IF(H102&lt;=129,2,3))))) + IF(F102&lt;=70,3,IF(F102&lt;=80,2,IF(F102&lt;=100,1,IF(F102&lt;=199,0,2)))) + IF(E102&lt;35,2,IF(E102&lt;=38.4,0,IF(E102&lt;=38.9,1,2))) + IF(M102="Alert",0,IF(M102="Voice",1,IF(M102="Pain",2,IF(M102="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O102">
-        <f>IF(I102&lt;=8,3,IF(I102&lt;=11,1,IF(I102&lt;=20,0,IF(I102&lt;=24,2,3)))) + IF(J102&lt;=91,3,IF(J102&lt;=93,2,IF(J102&lt;=95,1,0))) + IF(K102=TRUE,2,0) + IF(F102&lt;=90,3,IF(F102&lt;=100,2,IF(F102&lt;=110,1,IF(F102&lt;=219,0,3)))) + IF(H102&lt;=40,3,IF(H102&lt;=50,1,IF(H102&lt;=90,0,IF(H102&lt;=110,1,IF(H102&lt;=130,2,3))))) + IF(E102&lt;=35,3,IF(E102&lt;=36,1,IF(E102&lt;=38,0,IF(E102&lt;=39,1,2)))) + IF(L102="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -5945,15 +5986,15 @@
         <v>16</v>
       </c>
       <c r="M103" t="str">
-        <f>IF(L103="Confusion", "Alert", L103)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N103">
-        <f>IF(I103&lt;9,2,IF(I103&lt;=14,0,IF(I103&lt;=20,1,IF(I103&lt;=29,2,3)))) + IF(H103&lt;40,2,IF(H103&lt;=50,1,IF(H103&lt;=100,0,IF(H103&lt;=110,1,IF(H103&lt;=129,2,3))))) + IF(F103&lt;=70,3,IF(F103&lt;=80,2,IF(F103&lt;=100,1,IF(F103&lt;=199,0,2)))) + IF(E103&lt;35,2,IF(E103&lt;=38.4,0,IF(E103&lt;=38.9,1,2))) + IF(M103="Alert",0,IF(M103="Voice",1,IF(M103="Pain",2,IF(M103="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O103">
-        <f>IF(I103&lt;=8,3,IF(I103&lt;=11,1,IF(I103&lt;=20,0,IF(I103&lt;=24,2,3)))) + IF(J103&lt;=91,3,IF(J103&lt;=93,2,IF(J103&lt;=95,1,0))) + IF(K103=TRUE,2,0) + IF(F103&lt;=90,3,IF(F103&lt;=100,2,IF(F103&lt;=110,1,IF(F103&lt;=219,0,3)))) + IF(H103&lt;=40,3,IF(H103&lt;=50,1,IF(H103&lt;=90,0,IF(H103&lt;=110,1,IF(H103&lt;=130,2,3))))) + IF(E103&lt;=35,3,IF(E103&lt;=36,1,IF(E103&lt;=38,0,IF(E103&lt;=39,1,2)))) + IF(L103="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -5995,15 +6036,15 @@
         <v>16</v>
       </c>
       <c r="M104" t="str">
-        <f>IF(L104="Confusion", "Alert", L104)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N104">
-        <f>IF(I104&lt;9,2,IF(I104&lt;=14,0,IF(I104&lt;=20,1,IF(I104&lt;=29,2,3)))) + IF(H104&lt;40,2,IF(H104&lt;=50,1,IF(H104&lt;=100,0,IF(H104&lt;=110,1,IF(H104&lt;=129,2,3))))) + IF(F104&lt;=70,3,IF(F104&lt;=80,2,IF(F104&lt;=100,1,IF(F104&lt;=199,0,2)))) + IF(E104&lt;35,2,IF(E104&lt;=38.4,0,IF(E104&lt;=38.9,1,2))) + IF(M104="Alert",0,IF(M104="Voice",1,IF(M104="Pain",2,IF(M104="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O104">
-        <f>IF(I104&lt;=8,3,IF(I104&lt;=11,1,IF(I104&lt;=20,0,IF(I104&lt;=24,2,3)))) + IF(J104&lt;=91,3,IF(J104&lt;=93,2,IF(J104&lt;=95,1,0))) + IF(K104=TRUE,2,0) + IF(F104&lt;=90,3,IF(F104&lt;=100,2,IF(F104&lt;=110,1,IF(F104&lt;=219,0,3)))) + IF(H104&lt;=40,3,IF(H104&lt;=50,1,IF(H104&lt;=90,0,IF(H104&lt;=110,1,IF(H104&lt;=130,2,3))))) + IF(E104&lt;=35,3,IF(E104&lt;=36,1,IF(E104&lt;=38,0,IF(E104&lt;=39,1,2)))) + IF(L104="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -6045,15 +6086,15 @@
         <v>16</v>
       </c>
       <c r="M105" t="str">
-        <f>IF(L105="Confusion", "Alert", L105)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N105">
-        <f>IF(I105&lt;9,2,IF(I105&lt;=14,0,IF(I105&lt;=20,1,IF(I105&lt;=29,2,3)))) + IF(H105&lt;40,2,IF(H105&lt;=50,1,IF(H105&lt;=100,0,IF(H105&lt;=110,1,IF(H105&lt;=129,2,3))))) + IF(F105&lt;=70,3,IF(F105&lt;=80,2,IF(F105&lt;=100,1,IF(F105&lt;=199,0,2)))) + IF(E105&lt;35,2,IF(E105&lt;=38.4,0,IF(E105&lt;=38.9,1,2))) + IF(M105="Alert",0,IF(M105="Voice",1,IF(M105="Pain",2,IF(M105="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O105">
-        <f>IF(I105&lt;=8,3,IF(I105&lt;=11,1,IF(I105&lt;=20,0,IF(I105&lt;=24,2,3)))) + IF(J105&lt;=91,3,IF(J105&lt;=93,2,IF(J105&lt;=95,1,0))) + IF(K105=TRUE,2,0) + IF(F105&lt;=90,3,IF(F105&lt;=100,2,IF(F105&lt;=110,1,IF(F105&lt;=219,0,3)))) + IF(H105&lt;=40,3,IF(H105&lt;=50,1,IF(H105&lt;=90,0,IF(H105&lt;=110,1,IF(H105&lt;=130,2,3))))) + IF(E105&lt;=35,3,IF(E105&lt;=36,1,IF(E105&lt;=38,0,IF(E105&lt;=39,1,2)))) + IF(L105="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -6095,15 +6136,15 @@
         <v>16</v>
       </c>
       <c r="M106" t="str">
-        <f>IF(L106="Confusion", "Alert", L106)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N106">
-        <f>IF(I106&lt;9,2,IF(I106&lt;=14,0,IF(I106&lt;=20,1,IF(I106&lt;=29,2,3)))) + IF(H106&lt;40,2,IF(H106&lt;=50,1,IF(H106&lt;=100,0,IF(H106&lt;=110,1,IF(H106&lt;=129,2,3))))) + IF(F106&lt;=70,3,IF(F106&lt;=80,2,IF(F106&lt;=100,1,IF(F106&lt;=199,0,2)))) + IF(E106&lt;35,2,IF(E106&lt;=38.4,0,IF(E106&lt;=38.9,1,2))) + IF(M106="Alert",0,IF(M106="Voice",1,IF(M106="Pain",2,IF(M106="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O106">
-        <f>IF(I106&lt;=8,3,IF(I106&lt;=11,1,IF(I106&lt;=20,0,IF(I106&lt;=24,2,3)))) + IF(J106&lt;=91,3,IF(J106&lt;=93,2,IF(J106&lt;=95,1,0))) + IF(K106=TRUE,2,0) + IF(F106&lt;=90,3,IF(F106&lt;=100,2,IF(F106&lt;=110,1,IF(F106&lt;=219,0,3)))) + IF(H106&lt;=40,3,IF(H106&lt;=50,1,IF(H106&lt;=90,0,IF(H106&lt;=110,1,IF(H106&lt;=130,2,3))))) + IF(E106&lt;=35,3,IF(E106&lt;=36,1,IF(E106&lt;=38,0,IF(E106&lt;=39,1,2)))) + IF(L106="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="P106" s="2"/>
@@ -6146,15 +6187,15 @@
         <v>16</v>
       </c>
       <c r="M107" t="str">
-        <f>IF(L107="Confusion", "Alert", L107)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N107">
-        <f>IF(I107&lt;9,2,IF(I107&lt;=14,0,IF(I107&lt;=20,1,IF(I107&lt;=29,2,3)))) + IF(H107&lt;40,2,IF(H107&lt;=50,1,IF(H107&lt;=100,0,IF(H107&lt;=110,1,IF(H107&lt;=129,2,3))))) + IF(F107&lt;=70,3,IF(F107&lt;=80,2,IF(F107&lt;=100,1,IF(F107&lt;=199,0,2)))) + IF(E107&lt;35,2,IF(E107&lt;=38.4,0,IF(E107&lt;=38.9,1,2))) + IF(M107="Alert",0,IF(M107="Voice",1,IF(M107="Pain",2,IF(M107="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O107">
-        <f>IF(I107&lt;=8,3,IF(I107&lt;=11,1,IF(I107&lt;=20,0,IF(I107&lt;=24,2,3)))) + IF(J107&lt;=91,3,IF(J107&lt;=93,2,IF(J107&lt;=95,1,0))) + IF(K107=TRUE,2,0) + IF(F107&lt;=90,3,IF(F107&lt;=100,2,IF(F107&lt;=110,1,IF(F107&lt;=219,0,3)))) + IF(H107&lt;=40,3,IF(H107&lt;=50,1,IF(H107&lt;=90,0,IF(H107&lt;=110,1,IF(H107&lt;=130,2,3))))) + IF(E107&lt;=35,3,IF(E107&lt;=36,1,IF(E107&lt;=38,0,IF(E107&lt;=39,1,2)))) + IF(L107="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -6196,15 +6237,15 @@
         <v>16</v>
       </c>
       <c r="M108" t="str">
-        <f>IF(L108="Confusion", "Alert", L108)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N108">
-        <f>IF(I108&lt;9,2,IF(I108&lt;=14,0,IF(I108&lt;=20,1,IF(I108&lt;=29,2,3)))) + IF(H108&lt;40,2,IF(H108&lt;=50,1,IF(H108&lt;=100,0,IF(H108&lt;=110,1,IF(H108&lt;=129,2,3))))) + IF(F108&lt;=70,3,IF(F108&lt;=80,2,IF(F108&lt;=100,1,IF(F108&lt;=199,0,2)))) + IF(E108&lt;35,2,IF(E108&lt;=38.4,0,IF(E108&lt;=38.9,1,2))) + IF(M108="Alert",0,IF(M108="Voice",1,IF(M108="Pain",2,IF(M108="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="O108">
-        <f>IF(I108&lt;=8,3,IF(I108&lt;=11,1,IF(I108&lt;=20,0,IF(I108&lt;=24,2,3)))) + IF(J108&lt;=91,3,IF(J108&lt;=93,2,IF(J108&lt;=95,1,0))) + IF(K108=TRUE,2,0) + IF(F108&lt;=90,3,IF(F108&lt;=100,2,IF(F108&lt;=110,1,IF(F108&lt;=219,0,3)))) + IF(H108&lt;=40,3,IF(H108&lt;=50,1,IF(H108&lt;=90,0,IF(H108&lt;=110,1,IF(H108&lt;=130,2,3))))) + IF(E108&lt;=35,3,IF(E108&lt;=36,1,IF(E108&lt;=38,0,IF(E108&lt;=39,1,2)))) + IF(L108="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
     </row>
@@ -6246,15 +6287,15 @@
         <v>16</v>
       </c>
       <c r="M109" t="str">
-        <f>IF(L109="Confusion", "Alert", L109)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N109">
-        <f>IF(I109&lt;9,2,IF(I109&lt;=14,0,IF(I109&lt;=20,1,IF(I109&lt;=29,2,3)))) + IF(H109&lt;40,2,IF(H109&lt;=50,1,IF(H109&lt;=100,0,IF(H109&lt;=110,1,IF(H109&lt;=129,2,3))))) + IF(F109&lt;=70,3,IF(F109&lt;=80,2,IF(F109&lt;=100,1,IF(F109&lt;=199,0,2)))) + IF(E109&lt;35,2,IF(E109&lt;=38.4,0,IF(E109&lt;=38.9,1,2))) + IF(M109="Alert",0,IF(M109="Voice",1,IF(M109="Pain",2,IF(M109="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O109">
-        <f>IF(I109&lt;=8,3,IF(I109&lt;=11,1,IF(I109&lt;=20,0,IF(I109&lt;=24,2,3)))) + IF(J109&lt;=91,3,IF(J109&lt;=93,2,IF(J109&lt;=95,1,0))) + IF(K109=TRUE,2,0) + IF(F109&lt;=90,3,IF(F109&lt;=100,2,IF(F109&lt;=110,1,IF(F109&lt;=219,0,3)))) + IF(H109&lt;=40,3,IF(H109&lt;=50,1,IF(H109&lt;=90,0,IF(H109&lt;=110,1,IF(H109&lt;=130,2,3))))) + IF(E109&lt;=35,3,IF(E109&lt;=36,1,IF(E109&lt;=38,0,IF(E109&lt;=39,1,2)))) + IF(L109="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
@@ -6296,15 +6337,15 @@
         <v>16</v>
       </c>
       <c r="M110" t="str">
-        <f>IF(L110="Confusion", "Alert", L110)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N110">
-        <f>IF(I110&lt;9,2,IF(I110&lt;=14,0,IF(I110&lt;=20,1,IF(I110&lt;=29,2,3)))) + IF(H110&lt;40,2,IF(H110&lt;=50,1,IF(H110&lt;=100,0,IF(H110&lt;=110,1,IF(H110&lt;=129,2,3))))) + IF(F110&lt;=70,3,IF(F110&lt;=80,2,IF(F110&lt;=100,1,IF(F110&lt;=199,0,2)))) + IF(E110&lt;35,2,IF(E110&lt;=38.4,0,IF(E110&lt;=38.9,1,2))) + IF(M110="Alert",0,IF(M110="Voice",1,IF(M110="Pain",2,IF(M110="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O110">
-        <f>IF(I110&lt;=8,3,IF(I110&lt;=11,1,IF(I110&lt;=20,0,IF(I110&lt;=24,2,3)))) + IF(J110&lt;=91,3,IF(J110&lt;=93,2,IF(J110&lt;=95,1,0))) + IF(K110=TRUE,2,0) + IF(F110&lt;=90,3,IF(F110&lt;=100,2,IF(F110&lt;=110,1,IF(F110&lt;=219,0,3)))) + IF(H110&lt;=40,3,IF(H110&lt;=50,1,IF(H110&lt;=90,0,IF(H110&lt;=110,1,IF(H110&lt;=130,2,3))))) + IF(E110&lt;=35,3,IF(E110&lt;=36,1,IF(E110&lt;=38,0,IF(E110&lt;=39,1,2)))) + IF(L110="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -6346,15 +6387,15 @@
         <v>16</v>
       </c>
       <c r="M111" t="str">
-        <f>IF(L111="Confusion", "Alert", L111)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N111">
-        <f>IF(I111&lt;9,2,IF(I111&lt;=14,0,IF(I111&lt;=20,1,IF(I111&lt;=29,2,3)))) + IF(H111&lt;40,2,IF(H111&lt;=50,1,IF(H111&lt;=100,0,IF(H111&lt;=110,1,IF(H111&lt;=129,2,3))))) + IF(F111&lt;=70,3,IF(F111&lt;=80,2,IF(F111&lt;=100,1,IF(F111&lt;=199,0,2)))) + IF(E111&lt;35,2,IF(E111&lt;=38.4,0,IF(E111&lt;=38.9,1,2))) + IF(M111="Alert",0,IF(M111="Voice",1,IF(M111="Pain",2,IF(M111="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O111">
-        <f>IF(I111&lt;=8,3,IF(I111&lt;=11,1,IF(I111&lt;=20,0,IF(I111&lt;=24,2,3)))) + IF(J111&lt;=91,3,IF(J111&lt;=93,2,IF(J111&lt;=95,1,0))) + IF(K111=TRUE,2,0) + IF(F111&lt;=90,3,IF(F111&lt;=100,2,IF(F111&lt;=110,1,IF(F111&lt;=219,0,3)))) + IF(H111&lt;=40,3,IF(H111&lt;=50,1,IF(H111&lt;=90,0,IF(H111&lt;=110,1,IF(H111&lt;=130,2,3))))) + IF(E111&lt;=35,3,IF(E111&lt;=36,1,IF(E111&lt;=38,0,IF(E111&lt;=39,1,2)))) + IF(L111="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -6396,15 +6437,15 @@
         <v>16</v>
       </c>
       <c r="M112" t="str">
-        <f>IF(L112="Confusion", "Alert", L112)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N112">
-        <f>IF(I112&lt;9,2,IF(I112&lt;=14,0,IF(I112&lt;=20,1,IF(I112&lt;=29,2,3)))) + IF(H112&lt;40,2,IF(H112&lt;=50,1,IF(H112&lt;=100,0,IF(H112&lt;=110,1,IF(H112&lt;=129,2,3))))) + IF(F112&lt;=70,3,IF(F112&lt;=80,2,IF(F112&lt;=100,1,IF(F112&lt;=199,0,2)))) + IF(E112&lt;35,2,IF(E112&lt;=38.4,0,IF(E112&lt;=38.9,1,2))) + IF(M112="Alert",0,IF(M112="Voice",1,IF(M112="Pain",2,IF(M112="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O112">
-        <f>IF(I112&lt;=8,3,IF(I112&lt;=11,1,IF(I112&lt;=20,0,IF(I112&lt;=24,2,3)))) + IF(J112&lt;=91,3,IF(J112&lt;=93,2,IF(J112&lt;=95,1,0))) + IF(K112=TRUE,2,0) + IF(F112&lt;=90,3,IF(F112&lt;=100,2,IF(F112&lt;=110,1,IF(F112&lt;=219,0,3)))) + IF(H112&lt;=40,3,IF(H112&lt;=50,1,IF(H112&lt;=90,0,IF(H112&lt;=110,1,IF(H112&lt;=130,2,3))))) + IF(E112&lt;=35,3,IF(E112&lt;=36,1,IF(E112&lt;=38,0,IF(E112&lt;=39,1,2)))) + IF(L112="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -6446,15 +6487,15 @@
         <v>16</v>
       </c>
       <c r="M113" t="str">
-        <f>IF(L113="Confusion", "Alert", L113)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N113">
-        <f>IF(I113&lt;9,2,IF(I113&lt;=14,0,IF(I113&lt;=20,1,IF(I113&lt;=29,2,3)))) + IF(H113&lt;40,2,IF(H113&lt;=50,1,IF(H113&lt;=100,0,IF(H113&lt;=110,1,IF(H113&lt;=129,2,3))))) + IF(F113&lt;=70,3,IF(F113&lt;=80,2,IF(F113&lt;=100,1,IF(F113&lt;=199,0,2)))) + IF(E113&lt;35,2,IF(E113&lt;=38.4,0,IF(E113&lt;=38.9,1,2))) + IF(M113="Alert",0,IF(M113="Voice",1,IF(M113="Pain",2,IF(M113="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="O113">
-        <f>IF(I113&lt;=8,3,IF(I113&lt;=11,1,IF(I113&lt;=20,0,IF(I113&lt;=24,2,3)))) + IF(J113&lt;=91,3,IF(J113&lt;=93,2,IF(J113&lt;=95,1,0))) + IF(K113=TRUE,2,0) + IF(F113&lt;=90,3,IF(F113&lt;=100,2,IF(F113&lt;=110,1,IF(F113&lt;=219,0,3)))) + IF(H113&lt;=40,3,IF(H113&lt;=50,1,IF(H113&lt;=90,0,IF(H113&lt;=110,1,IF(H113&lt;=130,2,3))))) + IF(E113&lt;=35,3,IF(E113&lt;=36,1,IF(E113&lt;=38,0,IF(E113&lt;=39,1,2)))) + IF(L113="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
     </row>
@@ -6496,15 +6537,15 @@
         <v>16</v>
       </c>
       <c r="M114" t="str">
-        <f>IF(L114="Confusion", "Alert", L114)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N114">
-        <f>IF(I114&lt;9,2,IF(I114&lt;=14,0,IF(I114&lt;=20,1,IF(I114&lt;=29,2,3)))) + IF(H114&lt;40,2,IF(H114&lt;=50,1,IF(H114&lt;=100,0,IF(H114&lt;=110,1,IF(H114&lt;=129,2,3))))) + IF(F114&lt;=70,3,IF(F114&lt;=80,2,IF(F114&lt;=100,1,IF(F114&lt;=199,0,2)))) + IF(E114&lt;35,2,IF(E114&lt;=38.4,0,IF(E114&lt;=38.9,1,2))) + IF(M114="Alert",0,IF(M114="Voice",1,IF(M114="Pain",2,IF(M114="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O114">
-        <f>IF(I114&lt;=8,3,IF(I114&lt;=11,1,IF(I114&lt;=20,0,IF(I114&lt;=24,2,3)))) + IF(J114&lt;=91,3,IF(J114&lt;=93,2,IF(J114&lt;=95,1,0))) + IF(K114=TRUE,2,0) + IF(F114&lt;=90,3,IF(F114&lt;=100,2,IF(F114&lt;=110,1,IF(F114&lt;=219,0,3)))) + IF(H114&lt;=40,3,IF(H114&lt;=50,1,IF(H114&lt;=90,0,IF(H114&lt;=110,1,IF(H114&lt;=130,2,3))))) + IF(E114&lt;=35,3,IF(E114&lt;=36,1,IF(E114&lt;=38,0,IF(E114&lt;=39,1,2)))) + IF(L114="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -6546,15 +6587,15 @@
         <v>16</v>
       </c>
       <c r="M115" t="str">
-        <f>IF(L115="Confusion", "Alert", L115)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N115">
-        <f>IF(I115&lt;9,2,IF(I115&lt;=14,0,IF(I115&lt;=20,1,IF(I115&lt;=29,2,3)))) + IF(H115&lt;40,2,IF(H115&lt;=50,1,IF(H115&lt;=100,0,IF(H115&lt;=110,1,IF(H115&lt;=129,2,3))))) + IF(F115&lt;=70,3,IF(F115&lt;=80,2,IF(F115&lt;=100,1,IF(F115&lt;=199,0,2)))) + IF(E115&lt;35,2,IF(E115&lt;=38.4,0,IF(E115&lt;=38.9,1,2))) + IF(M115="Alert",0,IF(M115="Voice",1,IF(M115="Pain",2,IF(M115="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="O115">
-        <f>IF(I115&lt;=8,3,IF(I115&lt;=11,1,IF(I115&lt;=20,0,IF(I115&lt;=24,2,3)))) + IF(J115&lt;=91,3,IF(J115&lt;=93,2,IF(J115&lt;=95,1,0))) + IF(K115=TRUE,2,0) + IF(F115&lt;=90,3,IF(F115&lt;=100,2,IF(F115&lt;=110,1,IF(F115&lt;=219,0,3)))) + IF(H115&lt;=40,3,IF(H115&lt;=50,1,IF(H115&lt;=90,0,IF(H115&lt;=110,1,IF(H115&lt;=130,2,3))))) + IF(E115&lt;=35,3,IF(E115&lt;=36,1,IF(E115&lt;=38,0,IF(E115&lt;=39,1,2)))) + IF(L115="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
@@ -6596,15 +6637,15 @@
         <v>16</v>
       </c>
       <c r="M116" t="str">
-        <f>IF(L116="Confusion", "Alert", L116)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N116">
-        <f>IF(I116&lt;9,2,IF(I116&lt;=14,0,IF(I116&lt;=20,1,IF(I116&lt;=29,2,3)))) + IF(H116&lt;40,2,IF(H116&lt;=50,1,IF(H116&lt;=100,0,IF(H116&lt;=110,1,IF(H116&lt;=129,2,3))))) + IF(F116&lt;=70,3,IF(F116&lt;=80,2,IF(F116&lt;=100,1,IF(F116&lt;=199,0,2)))) + IF(E116&lt;35,2,IF(E116&lt;=38.4,0,IF(E116&lt;=38.9,1,2))) + IF(M116="Alert",0,IF(M116="Voice",1,IF(M116="Pain",2,IF(M116="Unresponsive",3,0))))</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="O116">
-        <f>IF(I116&lt;=8,3,IF(I116&lt;=11,1,IF(I116&lt;=20,0,IF(I116&lt;=24,2,3)))) + IF(J116&lt;=91,3,IF(J116&lt;=93,2,IF(J116&lt;=95,1,0))) + IF(K116=TRUE,2,0) + IF(F116&lt;=90,3,IF(F116&lt;=100,2,IF(F116&lt;=110,1,IF(F116&lt;=219,0,3)))) + IF(H116&lt;=40,3,IF(H116&lt;=50,1,IF(H116&lt;=90,0,IF(H116&lt;=110,1,IF(H116&lt;=130,2,3))))) + IF(E116&lt;=35,3,IF(E116&lt;=36,1,IF(E116&lt;=38,0,IF(E116&lt;=39,1,2)))) + IF(L116="Alert",0,3)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
     </row>
@@ -6646,7 +6687,7 @@
         <v>16</v>
       </c>
       <c r="M117" t="str">
-        <f>IF(L117="Confusion", "Alert", L117)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N117" t="s">
@@ -6694,7 +6735,7 @@
         <v>19</v>
       </c>
       <c r="M118" t="str">
-        <f>IF(L118="Confusion", "Alert", L118)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N118">
@@ -6735,14 +6776,14 @@
       <c r="J119" t="s">
         <v>23</v>
       </c>
-      <c r="K119" t="s">
-        <v>23</v>
+      <c r="K119" t="b">
+        <v>0</v>
       </c>
       <c r="L119" t="s">
         <v>19</v>
       </c>
       <c r="M119" t="str">
-        <f>IF(L119="Confusion", "Alert", L119)</f>
+        <f t="shared" si="0"/>
         <v>Alert</v>
       </c>
       <c r="N119" t="s">
@@ -6790,15 +6831,15 @@
         <v>16</v>
       </c>
       <c r="M120" t="str">
-        <f>IF(L120="Confusion", "Alert", L120)</f>
+        <f t="shared" ref="M120:M151" si="5">IF(L120="Confusion", "Alert", L120)</f>
         <v>Alert</v>
       </c>
       <c r="N120">
-        <f>IF(I120&lt;9,2,IF(I120&lt;=14,0,IF(I120&lt;=20,1,IF(I120&lt;=29,2,3)))) + IF(H120&lt;40,2,IF(H120&lt;=50,1,IF(H120&lt;=100,0,IF(H120&lt;=110,1,IF(H120&lt;=129,2,3))))) + IF(F120&lt;=70,3,IF(F120&lt;=80,2,IF(F120&lt;=100,1,IF(F120&lt;=199,0,2)))) + IF(E120&lt;35,2,IF(E120&lt;=38.4,0,IF(E120&lt;=38.9,1,2))) + IF(M120="Alert",0,IF(M120="Voice",1,IF(M120="Pain",2,IF(M120="Unresponsive",3,0))))</f>
+        <f t="shared" ref="N120:N145" si="6">IF(I120&lt;9,2,IF(I120&lt;=14,0,IF(I120&lt;=20,1,IF(I120&lt;=29,2,3)))) + IF(H120&lt;40,2,IF(H120&lt;=50,1,IF(H120&lt;=100,0,IF(H120&lt;=110,1,IF(H120&lt;=129,2,3))))) + IF(F120&lt;=70,3,IF(F120&lt;=80,2,IF(F120&lt;=100,1,IF(F120&lt;=199,0,2)))) + IF(E120&lt;35,2,IF(E120&lt;=38.4,0,IF(E120&lt;=38.9,1,2))) + IF(M120="Alert",0,IF(M120="Voice",1,IF(M120="Pain",2,IF(M120="Unresponsive",3,0))))</f>
         <v>1</v>
       </c>
       <c r="O120">
-        <f>IF(I120&lt;=8,3,IF(I120&lt;=11,1,IF(I120&lt;=20,0,IF(I120&lt;=24,2,3)))) + IF(J120&lt;=91,3,IF(J120&lt;=93,2,IF(J120&lt;=95,1,0))) + IF(K120=TRUE,2,0) + IF(F120&lt;=90,3,IF(F120&lt;=100,2,IF(F120&lt;=110,1,IF(F120&lt;=219,0,3)))) + IF(H120&lt;=40,3,IF(H120&lt;=50,1,IF(H120&lt;=90,0,IF(H120&lt;=110,1,IF(H120&lt;=130,2,3))))) + IF(E120&lt;=35,3,IF(E120&lt;=36,1,IF(E120&lt;=38,0,IF(E120&lt;=39,1,2)))) + IF(L120="Alert",0,3)</f>
+        <f t="shared" ref="O120:O145" si="7">IF(I120&lt;=8,3,IF(I120&lt;=11,1,IF(I120&lt;=20,0,IF(I120&lt;=24,2,3)))) + IF(J120&lt;=91,3,IF(J120&lt;=93,2,IF(J120&lt;=95,1,0))) + IF(K120=TRUE,2,0) + IF(F120&lt;=90,3,IF(F120&lt;=100,2,IF(F120&lt;=110,1,IF(F120&lt;=219,0,3)))) + IF(H120&lt;=40,3,IF(H120&lt;=50,1,IF(H120&lt;=90,0,IF(H120&lt;=110,1,IF(H120&lt;=130,2,3))))) + IF(E120&lt;=35,3,IF(E120&lt;=36,1,IF(E120&lt;=38,0,IF(E120&lt;=39,1,2)))) + IF(L120="Alert",0,3)</f>
         <v>0</v>
       </c>
     </row>
@@ -6840,15 +6881,15 @@
         <v>16</v>
       </c>
       <c r="M121" t="str">
-        <f>IF(L121="Confusion", "Alert", L121)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N121">
-        <f>IF(I121&lt;9,2,IF(I121&lt;=14,0,IF(I121&lt;=20,1,IF(I121&lt;=29,2,3)))) + IF(H121&lt;40,2,IF(H121&lt;=50,1,IF(H121&lt;=100,0,IF(H121&lt;=110,1,IF(H121&lt;=129,2,3))))) + IF(F121&lt;=70,3,IF(F121&lt;=80,2,IF(F121&lt;=100,1,IF(F121&lt;=199,0,2)))) + IF(E121&lt;35,2,IF(E121&lt;=38.4,0,IF(E121&lt;=38.9,1,2))) + IF(M121="Alert",0,IF(M121="Voice",1,IF(M121="Pain",2,IF(M121="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O121">
-        <f>IF(I121&lt;=8,3,IF(I121&lt;=11,1,IF(I121&lt;=20,0,IF(I121&lt;=24,2,3)))) + IF(J121&lt;=91,3,IF(J121&lt;=93,2,IF(J121&lt;=95,1,0))) + IF(K121=TRUE,2,0) + IF(F121&lt;=90,3,IF(F121&lt;=100,2,IF(F121&lt;=110,1,IF(F121&lt;=219,0,3)))) + IF(H121&lt;=40,3,IF(H121&lt;=50,1,IF(H121&lt;=90,0,IF(H121&lt;=110,1,IF(H121&lt;=130,2,3))))) + IF(E121&lt;=35,3,IF(E121&lt;=36,1,IF(E121&lt;=38,0,IF(E121&lt;=39,1,2)))) + IF(L121="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -6890,15 +6931,15 @@
         <v>16</v>
       </c>
       <c r="M122" t="str">
-        <f>IF(L122="Confusion", "Alert", L122)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N122">
-        <f>IF(I122&lt;9,2,IF(I122&lt;=14,0,IF(I122&lt;=20,1,IF(I122&lt;=29,2,3)))) + IF(H122&lt;40,2,IF(H122&lt;=50,1,IF(H122&lt;=100,0,IF(H122&lt;=110,1,IF(H122&lt;=129,2,3))))) + IF(F122&lt;=70,3,IF(F122&lt;=80,2,IF(F122&lt;=100,1,IF(F122&lt;=199,0,2)))) + IF(E122&lt;35,2,IF(E122&lt;=38.4,0,IF(E122&lt;=38.9,1,2))) + IF(M122="Alert",0,IF(M122="Voice",1,IF(M122="Pain",2,IF(M122="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="O122">
-        <f>IF(I122&lt;=8,3,IF(I122&lt;=11,1,IF(I122&lt;=20,0,IF(I122&lt;=24,2,3)))) + IF(J122&lt;=91,3,IF(J122&lt;=93,2,IF(J122&lt;=95,1,0))) + IF(K122=TRUE,2,0) + IF(F122&lt;=90,3,IF(F122&lt;=100,2,IF(F122&lt;=110,1,IF(F122&lt;=219,0,3)))) + IF(H122&lt;=40,3,IF(H122&lt;=50,1,IF(H122&lt;=90,0,IF(H122&lt;=110,1,IF(H122&lt;=130,2,3))))) + IF(E122&lt;=35,3,IF(E122&lt;=36,1,IF(E122&lt;=38,0,IF(E122&lt;=39,1,2)))) + IF(L122="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -6940,15 +6981,15 @@
         <v>16</v>
       </c>
       <c r="M123" t="str">
-        <f>IF(L123="Confusion", "Alert", L123)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N123">
-        <f>IF(I123&lt;9,2,IF(I123&lt;=14,0,IF(I123&lt;=20,1,IF(I123&lt;=29,2,3)))) + IF(H123&lt;40,2,IF(H123&lt;=50,1,IF(H123&lt;=100,0,IF(H123&lt;=110,1,IF(H123&lt;=129,2,3))))) + IF(F123&lt;=70,3,IF(F123&lt;=80,2,IF(F123&lt;=100,1,IF(F123&lt;=199,0,2)))) + IF(E123&lt;35,2,IF(E123&lt;=38.4,0,IF(E123&lt;=38.9,1,2))) + IF(M123="Alert",0,IF(M123="Voice",1,IF(M123="Pain",2,IF(M123="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O123">
-        <f>IF(I123&lt;=8,3,IF(I123&lt;=11,1,IF(I123&lt;=20,0,IF(I123&lt;=24,2,3)))) + IF(J123&lt;=91,3,IF(J123&lt;=93,2,IF(J123&lt;=95,1,0))) + IF(K123=TRUE,2,0) + IF(F123&lt;=90,3,IF(F123&lt;=100,2,IF(F123&lt;=110,1,IF(F123&lt;=219,0,3)))) + IF(H123&lt;=40,3,IF(H123&lt;=50,1,IF(H123&lt;=90,0,IF(H123&lt;=110,1,IF(H123&lt;=130,2,3))))) + IF(E123&lt;=35,3,IF(E123&lt;=36,1,IF(E123&lt;=38,0,IF(E123&lt;=39,1,2)))) + IF(L123="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -6990,15 +7031,15 @@
         <v>16</v>
       </c>
       <c r="M124" t="str">
-        <f>IF(L124="Confusion", "Alert", L124)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N124">
-        <f>IF(I124&lt;9,2,IF(I124&lt;=14,0,IF(I124&lt;=20,1,IF(I124&lt;=29,2,3)))) + IF(H124&lt;40,2,IF(H124&lt;=50,1,IF(H124&lt;=100,0,IF(H124&lt;=110,1,IF(H124&lt;=129,2,3))))) + IF(F124&lt;=70,3,IF(F124&lt;=80,2,IF(F124&lt;=100,1,IF(F124&lt;=199,0,2)))) + IF(E124&lt;35,2,IF(E124&lt;=38.4,0,IF(E124&lt;=38.9,1,2))) + IF(M124="Alert",0,IF(M124="Voice",1,IF(M124="Pain",2,IF(M124="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O124">
-        <f>IF(I124&lt;=8,3,IF(I124&lt;=11,1,IF(I124&lt;=20,0,IF(I124&lt;=24,2,3)))) + IF(J124&lt;=91,3,IF(J124&lt;=93,2,IF(J124&lt;=95,1,0))) + IF(K124=TRUE,2,0) + IF(F124&lt;=90,3,IF(F124&lt;=100,2,IF(F124&lt;=110,1,IF(F124&lt;=219,0,3)))) + IF(H124&lt;=40,3,IF(H124&lt;=50,1,IF(H124&lt;=90,0,IF(H124&lt;=110,1,IF(H124&lt;=130,2,3))))) + IF(E124&lt;=35,3,IF(E124&lt;=36,1,IF(E124&lt;=38,0,IF(E124&lt;=39,1,2)))) + IF(L124="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -7040,15 +7081,15 @@
         <v>16</v>
       </c>
       <c r="M125" t="str">
-        <f>IF(L125="Confusion", "Alert", L125)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N125">
-        <f>IF(I125&lt;9,2,IF(I125&lt;=14,0,IF(I125&lt;=20,1,IF(I125&lt;=29,2,3)))) + IF(H125&lt;40,2,IF(H125&lt;=50,1,IF(H125&lt;=100,0,IF(H125&lt;=110,1,IF(H125&lt;=129,2,3))))) + IF(F125&lt;=70,3,IF(F125&lt;=80,2,IF(F125&lt;=100,1,IF(F125&lt;=199,0,2)))) + IF(E125&lt;35,2,IF(E125&lt;=38.4,0,IF(E125&lt;=38.9,1,2))) + IF(M125="Alert",0,IF(M125="Voice",1,IF(M125="Pain",2,IF(M125="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="O125">
-        <f>IF(I125&lt;=8,3,IF(I125&lt;=11,1,IF(I125&lt;=20,0,IF(I125&lt;=24,2,3)))) + IF(J125&lt;=91,3,IF(J125&lt;=93,2,IF(J125&lt;=95,1,0))) + IF(K125=TRUE,2,0) + IF(F125&lt;=90,3,IF(F125&lt;=100,2,IF(F125&lt;=110,1,IF(F125&lt;=219,0,3)))) + IF(H125&lt;=40,3,IF(H125&lt;=50,1,IF(H125&lt;=90,0,IF(H125&lt;=110,1,IF(H125&lt;=130,2,3))))) + IF(E125&lt;=35,3,IF(E125&lt;=36,1,IF(E125&lt;=38,0,IF(E125&lt;=39,1,2)))) + IF(L125="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
     </row>
@@ -7090,15 +7131,15 @@
         <v>16</v>
       </c>
       <c r="M126" t="str">
-        <f>IF(L126="Confusion", "Alert", L126)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N126">
-        <f>IF(I126&lt;9,2,IF(I126&lt;=14,0,IF(I126&lt;=20,1,IF(I126&lt;=29,2,3)))) + IF(H126&lt;40,2,IF(H126&lt;=50,1,IF(H126&lt;=100,0,IF(H126&lt;=110,1,IF(H126&lt;=129,2,3))))) + IF(F126&lt;=70,3,IF(F126&lt;=80,2,IF(F126&lt;=100,1,IF(F126&lt;=199,0,2)))) + IF(E126&lt;35,2,IF(E126&lt;=38.4,0,IF(E126&lt;=38.9,1,2))) + IF(M126="Alert",0,IF(M126="Voice",1,IF(M126="Pain",2,IF(M126="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O126">
-        <f>IF(I126&lt;=8,3,IF(I126&lt;=11,1,IF(I126&lt;=20,0,IF(I126&lt;=24,2,3)))) + IF(J126&lt;=91,3,IF(J126&lt;=93,2,IF(J126&lt;=95,1,0))) + IF(K126=TRUE,2,0) + IF(F126&lt;=90,3,IF(F126&lt;=100,2,IF(F126&lt;=110,1,IF(F126&lt;=219,0,3)))) + IF(H126&lt;=40,3,IF(H126&lt;=50,1,IF(H126&lt;=90,0,IF(H126&lt;=110,1,IF(H126&lt;=130,2,3))))) + IF(E126&lt;=35,3,IF(E126&lt;=36,1,IF(E126&lt;=38,0,IF(E126&lt;=39,1,2)))) + IF(L126="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -7140,15 +7181,15 @@
         <v>16</v>
       </c>
       <c r="M127" t="str">
-        <f>IF(L127="Confusion", "Alert", L127)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N127">
-        <f>IF(I127&lt;9,2,IF(I127&lt;=14,0,IF(I127&lt;=20,1,IF(I127&lt;=29,2,3)))) + IF(H127&lt;40,2,IF(H127&lt;=50,1,IF(H127&lt;=100,0,IF(H127&lt;=110,1,IF(H127&lt;=129,2,3))))) + IF(F127&lt;=70,3,IF(F127&lt;=80,2,IF(F127&lt;=100,1,IF(F127&lt;=199,0,2)))) + IF(E127&lt;35,2,IF(E127&lt;=38.4,0,IF(E127&lt;=38.9,1,2))) + IF(M127="Alert",0,IF(M127="Voice",1,IF(M127="Pain",2,IF(M127="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O127">
-        <f>IF(I127&lt;=8,3,IF(I127&lt;=11,1,IF(I127&lt;=20,0,IF(I127&lt;=24,2,3)))) + IF(J127&lt;=91,3,IF(J127&lt;=93,2,IF(J127&lt;=95,1,0))) + IF(K127=TRUE,2,0) + IF(F127&lt;=90,3,IF(F127&lt;=100,2,IF(F127&lt;=110,1,IF(F127&lt;=219,0,3)))) + IF(H127&lt;=40,3,IF(H127&lt;=50,1,IF(H127&lt;=90,0,IF(H127&lt;=110,1,IF(H127&lt;=130,2,3))))) + IF(E127&lt;=35,3,IF(E127&lt;=36,1,IF(E127&lt;=38,0,IF(E127&lt;=39,1,2)))) + IF(L127="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -7190,15 +7231,15 @@
         <v>20</v>
       </c>
       <c r="M128" t="str">
-        <f>IF(L128="Confusion", "Alert", L128)</f>
+        <f t="shared" si="5"/>
         <v>Unresponsive</v>
       </c>
       <c r="N128">
-        <f>IF(I128&lt;9,2,IF(I128&lt;=14,0,IF(I128&lt;=20,1,IF(I128&lt;=29,2,3)))) + IF(H128&lt;40,2,IF(H128&lt;=50,1,IF(H128&lt;=100,0,IF(H128&lt;=110,1,IF(H128&lt;=129,2,3))))) + IF(F128&lt;=70,3,IF(F128&lt;=80,2,IF(F128&lt;=100,1,IF(F128&lt;=199,0,2)))) + IF(E128&lt;35,2,IF(E128&lt;=38.4,0,IF(E128&lt;=38.9,1,2))) + IF(M128="Alert",0,IF(M128="Voice",1,IF(M128="Pain",2,IF(M128="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="O128">
-        <f>IF(I128&lt;=8,3,IF(I128&lt;=11,1,IF(I128&lt;=20,0,IF(I128&lt;=24,2,3)))) + IF(J128&lt;=91,3,IF(J128&lt;=93,2,IF(J128&lt;=95,1,0))) + IF(K128=TRUE,2,0) + IF(F128&lt;=90,3,IF(F128&lt;=100,2,IF(F128&lt;=110,1,IF(F128&lt;=219,0,3)))) + IF(H128&lt;=40,3,IF(H128&lt;=50,1,IF(H128&lt;=90,0,IF(H128&lt;=110,1,IF(H128&lt;=130,2,3))))) + IF(E128&lt;=35,3,IF(E128&lt;=36,1,IF(E128&lt;=38,0,IF(E128&lt;=39,1,2)))) + IF(L128="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
     </row>
@@ -7240,15 +7281,15 @@
         <v>16</v>
       </c>
       <c r="M129" t="str">
-        <f>IF(L129="Confusion", "Alert", L129)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N129">
-        <f>IF(I129&lt;9,2,IF(I129&lt;=14,0,IF(I129&lt;=20,1,IF(I129&lt;=29,2,3)))) + IF(H129&lt;40,2,IF(H129&lt;=50,1,IF(H129&lt;=100,0,IF(H129&lt;=110,1,IF(H129&lt;=129,2,3))))) + IF(F129&lt;=70,3,IF(F129&lt;=80,2,IF(F129&lt;=100,1,IF(F129&lt;=199,0,2)))) + IF(E129&lt;35,2,IF(E129&lt;=38.4,0,IF(E129&lt;=38.9,1,2))) + IF(M129="Alert",0,IF(M129="Voice",1,IF(M129="Pain",2,IF(M129="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="O129">
-        <f>IF(I129&lt;=8,3,IF(I129&lt;=11,1,IF(I129&lt;=20,0,IF(I129&lt;=24,2,3)))) + IF(J129&lt;=91,3,IF(J129&lt;=93,2,IF(J129&lt;=95,1,0))) + IF(K129=TRUE,2,0) + IF(F129&lt;=90,3,IF(F129&lt;=100,2,IF(F129&lt;=110,1,IF(F129&lt;=219,0,3)))) + IF(H129&lt;=40,3,IF(H129&lt;=50,1,IF(H129&lt;=90,0,IF(H129&lt;=110,1,IF(H129&lt;=130,2,3))))) + IF(E129&lt;=35,3,IF(E129&lt;=36,1,IF(E129&lt;=38,0,IF(E129&lt;=39,1,2)))) + IF(L129="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -7290,15 +7331,15 @@
         <v>16</v>
       </c>
       <c r="M130" t="str">
-        <f>IF(L130="Confusion", "Alert", L130)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N130">
-        <f>IF(I130&lt;9,2,IF(I130&lt;=14,0,IF(I130&lt;=20,1,IF(I130&lt;=29,2,3)))) + IF(H130&lt;40,2,IF(H130&lt;=50,1,IF(H130&lt;=100,0,IF(H130&lt;=110,1,IF(H130&lt;=129,2,3))))) + IF(F130&lt;=70,3,IF(F130&lt;=80,2,IF(F130&lt;=100,1,IF(F130&lt;=199,0,2)))) + IF(E130&lt;35,2,IF(E130&lt;=38.4,0,IF(E130&lt;=38.9,1,2))) + IF(M130="Alert",0,IF(M130="Voice",1,IF(M130="Pain",2,IF(M130="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O130">
-        <f>IF(I130&lt;=8,3,IF(I130&lt;=11,1,IF(I130&lt;=20,0,IF(I130&lt;=24,2,3)))) + IF(J130&lt;=91,3,IF(J130&lt;=93,2,IF(J130&lt;=95,1,0))) + IF(K130=TRUE,2,0) + IF(F130&lt;=90,3,IF(F130&lt;=100,2,IF(F130&lt;=110,1,IF(F130&lt;=219,0,3)))) + IF(H130&lt;=40,3,IF(H130&lt;=50,1,IF(H130&lt;=90,0,IF(H130&lt;=110,1,IF(H130&lt;=130,2,3))))) + IF(E130&lt;=35,3,IF(E130&lt;=36,1,IF(E130&lt;=38,0,IF(E130&lt;=39,1,2)))) + IF(L130="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -7340,15 +7381,15 @@
         <v>16</v>
       </c>
       <c r="M131" t="str">
-        <f>IF(L131="Confusion", "Alert", L131)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N131">
-        <f>IF(I131&lt;9,2,IF(I131&lt;=14,0,IF(I131&lt;=20,1,IF(I131&lt;=29,2,3)))) + IF(H131&lt;40,2,IF(H131&lt;=50,1,IF(H131&lt;=100,0,IF(H131&lt;=110,1,IF(H131&lt;=129,2,3))))) + IF(F131&lt;=70,3,IF(F131&lt;=80,2,IF(F131&lt;=100,1,IF(F131&lt;=199,0,2)))) + IF(E131&lt;35,2,IF(E131&lt;=38.4,0,IF(E131&lt;=38.9,1,2))) + IF(M131="Alert",0,IF(M131="Voice",1,IF(M131="Pain",2,IF(M131="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O131">
-        <f>IF(I131&lt;=8,3,IF(I131&lt;=11,1,IF(I131&lt;=20,0,IF(I131&lt;=24,2,3)))) + IF(J131&lt;=91,3,IF(J131&lt;=93,2,IF(J131&lt;=95,1,0))) + IF(K131=TRUE,2,0) + IF(F131&lt;=90,3,IF(F131&lt;=100,2,IF(F131&lt;=110,1,IF(F131&lt;=219,0,3)))) + IF(H131&lt;=40,3,IF(H131&lt;=50,1,IF(H131&lt;=90,0,IF(H131&lt;=110,1,IF(H131&lt;=130,2,3))))) + IF(E131&lt;=35,3,IF(E131&lt;=36,1,IF(E131&lt;=38,0,IF(E131&lt;=39,1,2)))) + IF(L131="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -7390,15 +7431,15 @@
         <v>16</v>
       </c>
       <c r="M132" t="str">
-        <f>IF(L132="Confusion", "Alert", L132)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N132">
-        <f>IF(I132&lt;9,2,IF(I132&lt;=14,0,IF(I132&lt;=20,1,IF(I132&lt;=29,2,3)))) + IF(H132&lt;40,2,IF(H132&lt;=50,1,IF(H132&lt;=100,0,IF(H132&lt;=110,1,IF(H132&lt;=129,2,3))))) + IF(F132&lt;=70,3,IF(F132&lt;=80,2,IF(F132&lt;=100,1,IF(F132&lt;=199,0,2)))) + IF(E132&lt;35,2,IF(E132&lt;=38.4,0,IF(E132&lt;=38.9,1,2))) + IF(M132="Alert",0,IF(M132="Voice",1,IF(M132="Pain",2,IF(M132="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O132">
-        <f>IF(I132&lt;=8,3,IF(I132&lt;=11,1,IF(I132&lt;=20,0,IF(I132&lt;=24,2,3)))) + IF(J132&lt;=91,3,IF(J132&lt;=93,2,IF(J132&lt;=95,1,0))) + IF(K132=TRUE,2,0) + IF(F132&lt;=90,3,IF(F132&lt;=100,2,IF(F132&lt;=110,1,IF(F132&lt;=219,0,3)))) + IF(H132&lt;=40,3,IF(H132&lt;=50,1,IF(H132&lt;=90,0,IF(H132&lt;=110,1,IF(H132&lt;=130,2,3))))) + IF(E132&lt;=35,3,IF(E132&lt;=36,1,IF(E132&lt;=38,0,IF(E132&lt;=39,1,2)))) + IF(L132="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -7440,15 +7481,15 @@
         <v>16</v>
       </c>
       <c r="M133" t="str">
-        <f>IF(L133="Confusion", "Alert", L133)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N133">
-        <f>IF(I133&lt;9,2,IF(I133&lt;=14,0,IF(I133&lt;=20,1,IF(I133&lt;=29,2,3)))) + IF(H133&lt;40,2,IF(H133&lt;=50,1,IF(H133&lt;=100,0,IF(H133&lt;=110,1,IF(H133&lt;=129,2,3))))) + IF(F133&lt;=70,3,IF(F133&lt;=80,2,IF(F133&lt;=100,1,IF(F133&lt;=199,0,2)))) + IF(E133&lt;35,2,IF(E133&lt;=38.4,0,IF(E133&lt;=38.9,1,2))) + IF(M133="Alert",0,IF(M133="Voice",1,IF(M133="Pain",2,IF(M133="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O133">
-        <f>IF(I133&lt;=8,3,IF(I133&lt;=11,1,IF(I133&lt;=20,0,IF(I133&lt;=24,2,3)))) + IF(J133&lt;=91,3,IF(J133&lt;=93,2,IF(J133&lt;=95,1,0))) + IF(K133=TRUE,2,0) + IF(F133&lt;=90,3,IF(F133&lt;=100,2,IF(F133&lt;=110,1,IF(F133&lt;=219,0,3)))) + IF(H133&lt;=40,3,IF(H133&lt;=50,1,IF(H133&lt;=90,0,IF(H133&lt;=110,1,IF(H133&lt;=130,2,3))))) + IF(E133&lt;=35,3,IF(E133&lt;=36,1,IF(E133&lt;=38,0,IF(E133&lt;=39,1,2)))) + IF(L133="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
     </row>
@@ -7490,15 +7531,15 @@
         <v>16</v>
       </c>
       <c r="M134" t="str">
-        <f>IF(L134="Confusion", "Alert", L134)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N134">
-        <f>IF(I134&lt;9,2,IF(I134&lt;=14,0,IF(I134&lt;=20,1,IF(I134&lt;=29,2,3)))) + IF(H134&lt;40,2,IF(H134&lt;=50,1,IF(H134&lt;=100,0,IF(H134&lt;=110,1,IF(H134&lt;=129,2,3))))) + IF(F134&lt;=70,3,IF(F134&lt;=80,2,IF(F134&lt;=100,1,IF(F134&lt;=199,0,2)))) + IF(E134&lt;35,2,IF(E134&lt;=38.4,0,IF(E134&lt;=38.9,1,2))) + IF(M134="Alert",0,IF(M134="Voice",1,IF(M134="Pain",2,IF(M134="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O134">
-        <f>IF(I134&lt;=8,3,IF(I134&lt;=11,1,IF(I134&lt;=20,0,IF(I134&lt;=24,2,3)))) + IF(J134&lt;=91,3,IF(J134&lt;=93,2,IF(J134&lt;=95,1,0))) + IF(K134=TRUE,2,0) + IF(F134&lt;=90,3,IF(F134&lt;=100,2,IF(F134&lt;=110,1,IF(F134&lt;=219,0,3)))) + IF(H134&lt;=40,3,IF(H134&lt;=50,1,IF(H134&lt;=90,0,IF(H134&lt;=110,1,IF(H134&lt;=130,2,3))))) + IF(E134&lt;=35,3,IF(E134&lt;=36,1,IF(E134&lt;=38,0,IF(E134&lt;=39,1,2)))) + IF(L134="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -7540,15 +7581,15 @@
         <v>16</v>
       </c>
       <c r="M135" t="str">
-        <f>IF(L135="Confusion", "Alert", L135)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N135">
-        <f>IF(I135&lt;9,2,IF(I135&lt;=14,0,IF(I135&lt;=20,1,IF(I135&lt;=29,2,3)))) + IF(H135&lt;40,2,IF(H135&lt;=50,1,IF(H135&lt;=100,0,IF(H135&lt;=110,1,IF(H135&lt;=129,2,3))))) + IF(F135&lt;=70,3,IF(F135&lt;=80,2,IF(F135&lt;=100,1,IF(F135&lt;=199,0,2)))) + IF(E135&lt;35,2,IF(E135&lt;=38.4,0,IF(E135&lt;=38.9,1,2))) + IF(M135="Alert",0,IF(M135="Voice",1,IF(M135="Pain",2,IF(M135="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="O135">
-        <f>IF(I135&lt;=8,3,IF(I135&lt;=11,1,IF(I135&lt;=20,0,IF(I135&lt;=24,2,3)))) + IF(J135&lt;=91,3,IF(J135&lt;=93,2,IF(J135&lt;=95,1,0))) + IF(K135=TRUE,2,0) + IF(F135&lt;=90,3,IF(F135&lt;=100,2,IF(F135&lt;=110,1,IF(F135&lt;=219,0,3)))) + IF(H135&lt;=40,3,IF(H135&lt;=50,1,IF(H135&lt;=90,0,IF(H135&lt;=110,1,IF(H135&lt;=130,2,3))))) + IF(E135&lt;=35,3,IF(E135&lt;=36,1,IF(E135&lt;=38,0,IF(E135&lt;=39,1,2)))) + IF(L135="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -7590,15 +7631,15 @@
         <v>19</v>
       </c>
       <c r="M136" t="str">
-        <f>IF(L136="Confusion", "Alert", L136)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N136">
-        <f>IF(I136&lt;9,2,IF(I136&lt;=14,0,IF(I136&lt;=20,1,IF(I136&lt;=29,2,3)))) + IF(H136&lt;40,2,IF(H136&lt;=50,1,IF(H136&lt;=100,0,IF(H136&lt;=110,1,IF(H136&lt;=129,2,3))))) + IF(F136&lt;=70,3,IF(F136&lt;=80,2,IF(F136&lt;=100,1,IF(F136&lt;=199,0,2)))) + IF(E136&lt;35,2,IF(E136&lt;=38.4,0,IF(E136&lt;=38.9,1,2))) + IF(M136="Alert",0,IF(M136="Voice",1,IF(M136="Pain",2,IF(M136="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O136">
-        <f>IF(I136&lt;=8,3,IF(I136&lt;=11,1,IF(I136&lt;=20,0,IF(I136&lt;=24,2,3)))) + IF(J136&lt;=91,3,IF(J136&lt;=93,2,IF(J136&lt;=95,1,0))) + IF(K136=TRUE,2,0) + IF(F136&lt;=90,3,IF(F136&lt;=100,2,IF(F136&lt;=110,1,IF(F136&lt;=219,0,3)))) + IF(H136&lt;=40,3,IF(H136&lt;=50,1,IF(H136&lt;=90,0,IF(H136&lt;=110,1,IF(H136&lt;=130,2,3))))) + IF(E136&lt;=35,3,IF(E136&lt;=36,1,IF(E136&lt;=38,0,IF(E136&lt;=39,1,2)))) + IF(L136="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -7640,15 +7681,15 @@
         <v>16</v>
       </c>
       <c r="M137" t="str">
-        <f>IF(L137="Confusion", "Alert", L137)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N137">
-        <f>IF(I137&lt;9,2,IF(I137&lt;=14,0,IF(I137&lt;=20,1,IF(I137&lt;=29,2,3)))) + IF(H137&lt;40,2,IF(H137&lt;=50,1,IF(H137&lt;=100,0,IF(H137&lt;=110,1,IF(H137&lt;=129,2,3))))) + IF(F137&lt;=70,3,IF(F137&lt;=80,2,IF(F137&lt;=100,1,IF(F137&lt;=199,0,2)))) + IF(E137&lt;35,2,IF(E137&lt;=38.4,0,IF(E137&lt;=38.9,1,2))) + IF(M137="Alert",0,IF(M137="Voice",1,IF(M137="Pain",2,IF(M137="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O137">
-        <f>IF(I137&lt;=8,3,IF(I137&lt;=11,1,IF(I137&lt;=20,0,IF(I137&lt;=24,2,3)))) + IF(J137&lt;=91,3,IF(J137&lt;=93,2,IF(J137&lt;=95,1,0))) + IF(K137=TRUE,2,0) + IF(F137&lt;=90,3,IF(F137&lt;=100,2,IF(F137&lt;=110,1,IF(F137&lt;=219,0,3)))) + IF(H137&lt;=40,3,IF(H137&lt;=50,1,IF(H137&lt;=90,0,IF(H137&lt;=110,1,IF(H137&lt;=130,2,3))))) + IF(E137&lt;=35,3,IF(E137&lt;=36,1,IF(E137&lt;=38,0,IF(E137&lt;=39,1,2)))) + IF(L137="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -7690,15 +7731,15 @@
         <v>16</v>
       </c>
       <c r="M138" t="str">
-        <f>IF(L138="Confusion", "Alert", L138)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N138">
-        <f>IF(I138&lt;9,2,IF(I138&lt;=14,0,IF(I138&lt;=20,1,IF(I138&lt;=29,2,3)))) + IF(H138&lt;40,2,IF(H138&lt;=50,1,IF(H138&lt;=100,0,IF(H138&lt;=110,1,IF(H138&lt;=129,2,3))))) + IF(F138&lt;=70,3,IF(F138&lt;=80,2,IF(F138&lt;=100,1,IF(F138&lt;=199,0,2)))) + IF(E138&lt;35,2,IF(E138&lt;=38.4,0,IF(E138&lt;=38.9,1,2))) + IF(M138="Alert",0,IF(M138="Voice",1,IF(M138="Pain",2,IF(M138="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O138">
-        <f>IF(I138&lt;=8,3,IF(I138&lt;=11,1,IF(I138&lt;=20,0,IF(I138&lt;=24,2,3)))) + IF(J138&lt;=91,3,IF(J138&lt;=93,2,IF(J138&lt;=95,1,0))) + IF(K138=TRUE,2,0) + IF(F138&lt;=90,3,IF(F138&lt;=100,2,IF(F138&lt;=110,1,IF(F138&lt;=219,0,3)))) + IF(H138&lt;=40,3,IF(H138&lt;=50,1,IF(H138&lt;=90,0,IF(H138&lt;=110,1,IF(H138&lt;=130,2,3))))) + IF(E138&lt;=35,3,IF(E138&lt;=36,1,IF(E138&lt;=38,0,IF(E138&lt;=39,1,2)))) + IF(L138="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -7740,15 +7781,15 @@
         <v>16</v>
       </c>
       <c r="M139" t="str">
-        <f>IF(L139="Confusion", "Alert", L139)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N139">
-        <f>IF(I139&lt;9,2,IF(I139&lt;=14,0,IF(I139&lt;=20,1,IF(I139&lt;=29,2,3)))) + IF(H139&lt;40,2,IF(H139&lt;=50,1,IF(H139&lt;=100,0,IF(H139&lt;=110,1,IF(H139&lt;=129,2,3))))) + IF(F139&lt;=70,3,IF(F139&lt;=80,2,IF(F139&lt;=100,1,IF(F139&lt;=199,0,2)))) + IF(E139&lt;35,2,IF(E139&lt;=38.4,0,IF(E139&lt;=38.9,1,2))) + IF(M139="Alert",0,IF(M139="Voice",1,IF(M139="Pain",2,IF(M139="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="O139">
-        <f>IF(I139&lt;=8,3,IF(I139&lt;=11,1,IF(I139&lt;=20,0,IF(I139&lt;=24,2,3)))) + IF(J139&lt;=91,3,IF(J139&lt;=93,2,IF(J139&lt;=95,1,0))) + IF(K139=TRUE,2,0) + IF(F139&lt;=90,3,IF(F139&lt;=100,2,IF(F139&lt;=110,1,IF(F139&lt;=219,0,3)))) + IF(H139&lt;=40,3,IF(H139&lt;=50,1,IF(H139&lt;=90,0,IF(H139&lt;=110,1,IF(H139&lt;=130,2,3))))) + IF(E139&lt;=35,3,IF(E139&lt;=36,1,IF(E139&lt;=38,0,IF(E139&lt;=39,1,2)))) + IF(L139="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
@@ -7790,15 +7831,15 @@
         <v>16</v>
       </c>
       <c r="M140" t="str">
-        <f>IF(L140="Confusion", "Alert", L140)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N140">
-        <f>IF(I140&lt;9,2,IF(I140&lt;=14,0,IF(I140&lt;=20,1,IF(I140&lt;=29,2,3)))) + IF(H140&lt;40,2,IF(H140&lt;=50,1,IF(H140&lt;=100,0,IF(H140&lt;=110,1,IF(H140&lt;=129,2,3))))) + IF(F140&lt;=70,3,IF(F140&lt;=80,2,IF(F140&lt;=100,1,IF(F140&lt;=199,0,2)))) + IF(E140&lt;35,2,IF(E140&lt;=38.4,0,IF(E140&lt;=38.9,1,2))) + IF(M140="Alert",0,IF(M140="Voice",1,IF(M140="Pain",2,IF(M140="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="O140">
-        <f>IF(I140&lt;=8,3,IF(I140&lt;=11,1,IF(I140&lt;=20,0,IF(I140&lt;=24,2,3)))) + IF(J140&lt;=91,3,IF(J140&lt;=93,2,IF(J140&lt;=95,1,0))) + IF(K140=TRUE,2,0) + IF(F140&lt;=90,3,IF(F140&lt;=100,2,IF(F140&lt;=110,1,IF(F140&lt;=219,0,3)))) + IF(H140&lt;=40,3,IF(H140&lt;=50,1,IF(H140&lt;=90,0,IF(H140&lt;=110,1,IF(H140&lt;=130,2,3))))) + IF(E140&lt;=35,3,IF(E140&lt;=36,1,IF(E140&lt;=38,0,IF(E140&lt;=39,1,2)))) + IF(L140="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
     </row>
@@ -7840,15 +7881,15 @@
         <v>16</v>
       </c>
       <c r="M141" t="str">
-        <f>IF(L141="Confusion", "Alert", L141)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N141">
-        <f>IF(I141&lt;9,2,IF(I141&lt;=14,0,IF(I141&lt;=20,1,IF(I141&lt;=29,2,3)))) + IF(H141&lt;40,2,IF(H141&lt;=50,1,IF(H141&lt;=100,0,IF(H141&lt;=110,1,IF(H141&lt;=129,2,3))))) + IF(F141&lt;=70,3,IF(F141&lt;=80,2,IF(F141&lt;=100,1,IF(F141&lt;=199,0,2)))) + IF(E141&lt;35,2,IF(E141&lt;=38.4,0,IF(E141&lt;=38.9,1,2))) + IF(M141="Alert",0,IF(M141="Voice",1,IF(M141="Pain",2,IF(M141="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O141">
-        <f>IF(I141&lt;=8,3,IF(I141&lt;=11,1,IF(I141&lt;=20,0,IF(I141&lt;=24,2,3)))) + IF(J141&lt;=91,3,IF(J141&lt;=93,2,IF(J141&lt;=95,1,0))) + IF(K141=TRUE,2,0) + IF(F141&lt;=90,3,IF(F141&lt;=100,2,IF(F141&lt;=110,1,IF(F141&lt;=219,0,3)))) + IF(H141&lt;=40,3,IF(H141&lt;=50,1,IF(H141&lt;=90,0,IF(H141&lt;=110,1,IF(H141&lt;=130,2,3))))) + IF(E141&lt;=35,3,IF(E141&lt;=36,1,IF(E141&lt;=38,0,IF(E141&lt;=39,1,2)))) + IF(L141="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -7890,15 +7931,15 @@
         <v>20</v>
       </c>
       <c r="M142" t="str">
-        <f>IF(L142="Confusion", "Alert", L142)</f>
+        <f t="shared" si="5"/>
         <v>Unresponsive</v>
       </c>
       <c r="N142">
-        <f>IF(I142&lt;9,2,IF(I142&lt;=14,0,IF(I142&lt;=20,1,IF(I142&lt;=29,2,3)))) + IF(H142&lt;40,2,IF(H142&lt;=50,1,IF(H142&lt;=100,0,IF(H142&lt;=110,1,IF(H142&lt;=129,2,3))))) + IF(F142&lt;=70,3,IF(F142&lt;=80,2,IF(F142&lt;=100,1,IF(F142&lt;=199,0,2)))) + IF(E142&lt;35,2,IF(E142&lt;=38.4,0,IF(E142&lt;=38.9,1,2))) + IF(M142="Alert",0,IF(M142="Voice",1,IF(M142="Pain",2,IF(M142="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="O142">
-        <f>IF(I142&lt;=8,3,IF(I142&lt;=11,1,IF(I142&lt;=20,0,IF(I142&lt;=24,2,3)))) + IF(J142&lt;=91,3,IF(J142&lt;=93,2,IF(J142&lt;=95,1,0))) + IF(K142=TRUE,2,0) + IF(F142&lt;=90,3,IF(F142&lt;=100,2,IF(F142&lt;=110,1,IF(F142&lt;=219,0,3)))) + IF(H142&lt;=40,3,IF(H142&lt;=50,1,IF(H142&lt;=90,0,IF(H142&lt;=110,1,IF(H142&lt;=130,2,3))))) + IF(E142&lt;=35,3,IF(E142&lt;=36,1,IF(E142&lt;=38,0,IF(E142&lt;=39,1,2)))) + IF(L142="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
     </row>
@@ -7940,15 +7981,15 @@
         <v>16</v>
       </c>
       <c r="M143" t="str">
-        <f>IF(L143="Confusion", "Alert", L143)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N143">
-        <f>IF(I143&lt;9,2,IF(I143&lt;=14,0,IF(I143&lt;=20,1,IF(I143&lt;=29,2,3)))) + IF(H143&lt;40,2,IF(H143&lt;=50,1,IF(H143&lt;=100,0,IF(H143&lt;=110,1,IF(H143&lt;=129,2,3))))) + IF(F143&lt;=70,3,IF(F143&lt;=80,2,IF(F143&lt;=100,1,IF(F143&lt;=199,0,2)))) + IF(E143&lt;35,2,IF(E143&lt;=38.4,0,IF(E143&lt;=38.9,1,2))) + IF(M143="Alert",0,IF(M143="Voice",1,IF(M143="Pain",2,IF(M143="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="O143">
-        <f>IF(I143&lt;=8,3,IF(I143&lt;=11,1,IF(I143&lt;=20,0,IF(I143&lt;=24,2,3)))) + IF(J143&lt;=91,3,IF(J143&lt;=93,2,IF(J143&lt;=95,1,0))) + IF(K143=TRUE,2,0) + IF(F143&lt;=90,3,IF(F143&lt;=100,2,IF(F143&lt;=110,1,IF(F143&lt;=219,0,3)))) + IF(H143&lt;=40,3,IF(H143&lt;=50,1,IF(H143&lt;=90,0,IF(H143&lt;=110,1,IF(H143&lt;=130,2,3))))) + IF(E143&lt;=35,3,IF(E143&lt;=36,1,IF(E143&lt;=38,0,IF(E143&lt;=39,1,2)))) + IF(L143="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
     </row>
@@ -7990,15 +8031,15 @@
         <v>20</v>
       </c>
       <c r="M144" t="str">
-        <f>IF(L144="Confusion", "Alert", L144)</f>
+        <f t="shared" si="5"/>
         <v>Unresponsive</v>
       </c>
       <c r="N144">
-        <f>IF(I144&lt;9,2,IF(I144&lt;=14,0,IF(I144&lt;=20,1,IF(I144&lt;=29,2,3)))) + IF(H144&lt;40,2,IF(H144&lt;=50,1,IF(H144&lt;=100,0,IF(H144&lt;=110,1,IF(H144&lt;=129,2,3))))) + IF(F144&lt;=70,3,IF(F144&lt;=80,2,IF(F144&lt;=100,1,IF(F144&lt;=199,0,2)))) + IF(E144&lt;35,2,IF(E144&lt;=38.4,0,IF(E144&lt;=38.9,1,2))) + IF(M144="Alert",0,IF(M144="Voice",1,IF(M144="Pain",2,IF(M144="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="O144">
-        <f>IF(I144&lt;=8,3,IF(I144&lt;=11,1,IF(I144&lt;=20,0,IF(I144&lt;=24,2,3)))) + IF(J144&lt;=91,3,IF(J144&lt;=93,2,IF(J144&lt;=95,1,0))) + IF(K144=TRUE,2,0) + IF(F144&lt;=90,3,IF(F144&lt;=100,2,IF(F144&lt;=110,1,IF(F144&lt;=219,0,3)))) + IF(H144&lt;=40,3,IF(H144&lt;=50,1,IF(H144&lt;=90,0,IF(H144&lt;=110,1,IF(H144&lt;=130,2,3))))) + IF(E144&lt;=35,3,IF(E144&lt;=36,1,IF(E144&lt;=38,0,IF(E144&lt;=39,1,2)))) + IF(L144="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
     </row>
@@ -8040,15 +8081,15 @@
         <v>16</v>
       </c>
       <c r="M145" t="str">
-        <f>IF(L145="Confusion", "Alert", L145)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N145">
-        <f>IF(I145&lt;9,2,IF(I145&lt;=14,0,IF(I145&lt;=20,1,IF(I145&lt;=29,2,3)))) + IF(H145&lt;40,2,IF(H145&lt;=50,1,IF(H145&lt;=100,0,IF(H145&lt;=110,1,IF(H145&lt;=129,2,3))))) + IF(F145&lt;=70,3,IF(F145&lt;=80,2,IF(F145&lt;=100,1,IF(F145&lt;=199,0,2)))) + IF(E145&lt;35,2,IF(E145&lt;=38.4,0,IF(E145&lt;=38.9,1,2))) + IF(M145="Alert",0,IF(M145="Voice",1,IF(M145="Pain",2,IF(M145="Unresponsive",3,0))))</f>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="O145">
-        <f>IF(I145&lt;=8,3,IF(I145&lt;=11,1,IF(I145&lt;=20,0,IF(I145&lt;=24,2,3)))) + IF(J145&lt;=91,3,IF(J145&lt;=93,2,IF(J145&lt;=95,1,0))) + IF(K145=TRUE,2,0) + IF(F145&lt;=90,3,IF(F145&lt;=100,2,IF(F145&lt;=110,1,IF(F145&lt;=219,0,3)))) + IF(H145&lt;=40,3,IF(H145&lt;=50,1,IF(H145&lt;=90,0,IF(H145&lt;=110,1,IF(H145&lt;=130,2,3))))) + IF(E145&lt;=35,3,IF(E145&lt;=36,1,IF(E145&lt;=38,0,IF(E145&lt;=39,1,2)))) + IF(L145="Alert",0,3)</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -8090,7 +8131,7 @@
         <v>16</v>
       </c>
       <c r="M146" t="str">
-        <f>IF(L146="Confusion", "Alert", L146)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N146" t="s">
@@ -8138,15 +8179,15 @@
         <v>16</v>
       </c>
       <c r="M147" t="str">
-        <f>IF(L147="Confusion", "Alert", L147)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N147">
-        <f>IF(I147&lt;9,2,IF(I147&lt;=14,0,IF(I147&lt;=20,1,IF(I147&lt;=29,2,3)))) + IF(H147&lt;40,2,IF(H147&lt;=50,1,IF(H147&lt;=100,0,IF(H147&lt;=110,1,IF(H147&lt;=129,2,3))))) + IF(F147&lt;=70,3,IF(F147&lt;=80,2,IF(F147&lt;=100,1,IF(F147&lt;=199,0,2)))) + IF(E147&lt;35,2,IF(E147&lt;=38.4,0,IF(E147&lt;=38.9,1,2))) + IF(M147="Alert",0,IF(M147="Voice",1,IF(M147="Pain",2,IF(M147="Unresponsive",3,0))))</f>
+        <f t="shared" ref="N147:N152" si="8">IF(I147&lt;9,2,IF(I147&lt;=14,0,IF(I147&lt;=20,1,IF(I147&lt;=29,2,3)))) + IF(H147&lt;40,2,IF(H147&lt;=50,1,IF(H147&lt;=100,0,IF(H147&lt;=110,1,IF(H147&lt;=129,2,3))))) + IF(F147&lt;=70,3,IF(F147&lt;=80,2,IF(F147&lt;=100,1,IF(F147&lt;=199,0,2)))) + IF(E147&lt;35,2,IF(E147&lt;=38.4,0,IF(E147&lt;=38.9,1,2))) + IF(M147="Alert",0,IF(M147="Voice",1,IF(M147="Pain",2,IF(M147="Unresponsive",3,0))))</f>
         <v>1</v>
       </c>
       <c r="O147">
-        <f>IF(I147&lt;=8,3,IF(I147&lt;=11,1,IF(I147&lt;=20,0,IF(I147&lt;=24,2,3)))) + IF(J147&lt;=91,3,IF(J147&lt;=93,2,IF(J147&lt;=95,1,0))) + IF(K147=TRUE,2,0) + IF(F147&lt;=90,3,IF(F147&lt;=100,2,IF(F147&lt;=110,1,IF(F147&lt;=219,0,3)))) + IF(H147&lt;=40,3,IF(H147&lt;=50,1,IF(H147&lt;=90,0,IF(H147&lt;=110,1,IF(H147&lt;=130,2,3))))) + IF(E147&lt;=35,3,IF(E147&lt;=36,1,IF(E147&lt;=38,0,IF(E147&lt;=39,1,2)))) + IF(L147="Alert",0,3)</f>
+        <f t="shared" ref="O147:O152" si="9">IF(I147&lt;=8,3,IF(I147&lt;=11,1,IF(I147&lt;=20,0,IF(I147&lt;=24,2,3)))) + IF(J147&lt;=91,3,IF(J147&lt;=93,2,IF(J147&lt;=95,1,0))) + IF(K147=TRUE,2,0) + IF(F147&lt;=90,3,IF(F147&lt;=100,2,IF(F147&lt;=110,1,IF(F147&lt;=219,0,3)))) + IF(H147&lt;=40,3,IF(H147&lt;=50,1,IF(H147&lt;=90,0,IF(H147&lt;=110,1,IF(H147&lt;=130,2,3))))) + IF(E147&lt;=35,3,IF(E147&lt;=36,1,IF(E147&lt;=38,0,IF(E147&lt;=39,1,2)))) + IF(L147="Alert",0,3)</f>
         <v>1</v>
       </c>
     </row>
@@ -8188,15 +8229,15 @@
         <v>22</v>
       </c>
       <c r="M148" t="str">
-        <f>IF(L148="Confusion", "Alert", L148)</f>
+        <f t="shared" si="5"/>
         <v>Voice</v>
       </c>
       <c r="N148">
-        <f>IF(I148&lt;9,2,IF(I148&lt;=14,0,IF(I148&lt;=20,1,IF(I148&lt;=29,2,3)))) + IF(H148&lt;40,2,IF(H148&lt;=50,1,IF(H148&lt;=100,0,IF(H148&lt;=110,1,IF(H148&lt;=129,2,3))))) + IF(F148&lt;=70,3,IF(F148&lt;=80,2,IF(F148&lt;=100,1,IF(F148&lt;=199,0,2)))) + IF(E148&lt;35,2,IF(E148&lt;=38.4,0,IF(E148&lt;=38.9,1,2))) + IF(M148="Alert",0,IF(M148="Voice",1,IF(M148="Pain",2,IF(M148="Unresponsive",3,0))))</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="O148">
-        <f>IF(I148&lt;=8,3,IF(I148&lt;=11,1,IF(I148&lt;=20,0,IF(I148&lt;=24,2,3)))) + IF(J148&lt;=91,3,IF(J148&lt;=93,2,IF(J148&lt;=95,1,0))) + IF(K148=TRUE,2,0) + IF(F148&lt;=90,3,IF(F148&lt;=100,2,IF(F148&lt;=110,1,IF(F148&lt;=219,0,3)))) + IF(H148&lt;=40,3,IF(H148&lt;=50,1,IF(H148&lt;=90,0,IF(H148&lt;=110,1,IF(H148&lt;=130,2,3))))) + IF(E148&lt;=35,3,IF(E148&lt;=36,1,IF(E148&lt;=38,0,IF(E148&lt;=39,1,2)))) + IF(L148="Alert",0,3)</f>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -8238,15 +8279,15 @@
         <v>16</v>
       </c>
       <c r="M149" t="str">
-        <f>IF(L149="Confusion", "Alert", L149)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N149">
-        <f>IF(I149&lt;9,2,IF(I149&lt;=14,0,IF(I149&lt;=20,1,IF(I149&lt;=29,2,3)))) + IF(H149&lt;40,2,IF(H149&lt;=50,1,IF(H149&lt;=100,0,IF(H149&lt;=110,1,IF(H149&lt;=129,2,3))))) + IF(F149&lt;=70,3,IF(F149&lt;=80,2,IF(F149&lt;=100,1,IF(F149&lt;=199,0,2)))) + IF(E149&lt;35,2,IF(E149&lt;=38.4,0,IF(E149&lt;=38.9,1,2))) + IF(M149="Alert",0,IF(M149="Voice",1,IF(M149="Pain",2,IF(M149="Unresponsive",3,0))))</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O149">
-        <f>IF(I149&lt;=8,3,IF(I149&lt;=11,1,IF(I149&lt;=20,0,IF(I149&lt;=24,2,3)))) + IF(J149&lt;=91,3,IF(J149&lt;=93,2,IF(J149&lt;=95,1,0))) + IF(K149=TRUE,2,0) + IF(F149&lt;=90,3,IF(F149&lt;=100,2,IF(F149&lt;=110,1,IF(F149&lt;=219,0,3)))) + IF(H149&lt;=40,3,IF(H149&lt;=50,1,IF(H149&lt;=90,0,IF(H149&lt;=110,1,IF(H149&lt;=130,2,3))))) + IF(E149&lt;=35,3,IF(E149&lt;=36,1,IF(E149&lt;=38,0,IF(E149&lt;=39,1,2)))) + IF(L149="Alert",0,3)</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -8288,15 +8329,15 @@
         <v>16</v>
       </c>
       <c r="M150" t="str">
-        <f>IF(L150="Confusion", "Alert", L150)</f>
+        <f t="shared" si="5"/>
         <v>Alert</v>
       </c>
       <c r="N150">
-        <f>IF(I150&lt;9,2,IF(I150&lt;=14,0,IF(I150&lt;=20,1,IF(I150&lt;=29,2,3)))) + IF(H150&lt;40,2,IF(H150&lt;=50,1,IF(H150&lt;=100,0,IF(H150&lt;=110,1,IF(H150&lt;=129,2,3))))) + IF(F150&lt;=70,3,IF(F150&lt;=80,2,IF(F150&lt;=100,1,IF(F150&lt;=199,0,2)))) + IF(E150&lt;35,2,IF(E150&lt;=38.4,0,IF(E150&lt;=38.9,1,2))) + IF(M150="Alert",0,IF(M150="Voice",1,IF(M150="Pain",2,IF(M150="Unresponsive",3,0))))</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="O150">
-        <f>IF(I150&lt;=8,3,IF(I150&lt;=11,1,IF(I150&lt;=20,0,IF(I150&lt;=24,2,3)))) + IF(J150&lt;=91,3,IF(J150&lt;=93,2,IF(J150&lt;=95,1,0))) + IF(K150=TRUE,2,0) + IF(F150&lt;=90,3,IF(F150&lt;=100,2,IF(F150&lt;=110,1,IF(F150&lt;=219,0,3)))) + IF(H150&lt;=40,3,IF(H150&lt;=50,1,IF(H150&lt;=90,0,IF(H150&lt;=110,1,IF(H150&lt;=130,2,3))))) + IF(E150&lt;=35,3,IF(E150&lt;=36,1,IF(E150&lt;=38,0,IF(E150&lt;=39,1,2)))) + IF(L150="Alert",0,3)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
     </row>
@@ -8338,15 +8379,15 @@
         <v>22</v>
       </c>
       <c r="M151" t="str">
-        <f>IF(L151="Confusion", "Alert", L151)</f>
+        <f t="shared" si="5"/>
         <v>Voice</v>
       </c>
       <c r="N151">
-        <f>IF(I151&lt;9,2,IF(I151&lt;=14,0,IF(I151&lt;=20,1,IF(I151&lt;=29,2,3)))) + IF(H151&lt;40,2,IF(H151&lt;=50,1,IF(H151&lt;=100,0,IF(H151&lt;=110,1,IF(H151&lt;=129,2,3))))) + IF(F151&lt;=70,3,IF(F151&lt;=80,2,IF(F151&lt;=100,1,IF(F151&lt;=199,0,2)))) + IF(E151&lt;35,2,IF(E151&lt;=38.4,0,IF(E151&lt;=38.9,1,2))) + IF(M151="Alert",0,IF(M151="Voice",1,IF(M151="Pain",2,IF(M151="Unresponsive",3,0))))</f>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="O151">
-        <f>IF(I151&lt;=8,3,IF(I151&lt;=11,1,IF(I151&lt;=20,0,IF(I151&lt;=24,2,3)))) + IF(J151&lt;=91,3,IF(J151&lt;=93,2,IF(J151&lt;=95,1,0))) + IF(K151=TRUE,2,0) + IF(F151&lt;=90,3,IF(F151&lt;=100,2,IF(F151&lt;=110,1,IF(F151&lt;=219,0,3)))) + IF(H151&lt;=40,3,IF(H151&lt;=50,1,IF(H151&lt;=90,0,IF(H151&lt;=110,1,IF(H151&lt;=130,2,3))))) + IF(E151&lt;=35,3,IF(E151&lt;=36,1,IF(E151&lt;=38,0,IF(E151&lt;=39,1,2)))) + IF(L151="Alert",0,3)</f>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
     </row>
@@ -8388,15 +8429,15 @@
         <v>16</v>
       </c>
       <c r="M152" t="str">
-        <f>IF(L152="Confusion", "Alert", L152)</f>
+        <f t="shared" ref="M152:M183" si="10">IF(L152="Confusion", "Alert", L152)</f>
         <v>Alert</v>
       </c>
       <c r="N152">
-        <f>IF(I152&lt;9,2,IF(I152&lt;=14,0,IF(I152&lt;=20,1,IF(I152&lt;=29,2,3)))) + IF(H152&lt;40,2,IF(H152&lt;=50,1,IF(H152&lt;=100,0,IF(H152&lt;=110,1,IF(H152&lt;=129,2,3))))) + IF(F152&lt;=70,3,IF(F152&lt;=80,2,IF(F152&lt;=100,1,IF(F152&lt;=199,0,2)))) + IF(E152&lt;35,2,IF(E152&lt;=38.4,0,IF(E152&lt;=38.9,1,2))) + IF(M152="Alert",0,IF(M152="Voice",1,IF(M152="Pain",2,IF(M152="Unresponsive",3,0))))</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="O152">
-        <f>IF(I152&lt;=8,3,IF(I152&lt;=11,1,IF(I152&lt;=20,0,IF(I152&lt;=24,2,3)))) + IF(J152&lt;=91,3,IF(J152&lt;=93,2,IF(J152&lt;=95,1,0))) + IF(K152=TRUE,2,0) + IF(F152&lt;=90,3,IF(F152&lt;=100,2,IF(F152&lt;=110,1,IF(F152&lt;=219,0,3)))) + IF(H152&lt;=40,3,IF(H152&lt;=50,1,IF(H152&lt;=90,0,IF(H152&lt;=110,1,IF(H152&lt;=130,2,3))))) + IF(E152&lt;=35,3,IF(E152&lt;=36,1,IF(E152&lt;=38,0,IF(E152&lt;=39,1,2)))) + IF(L152="Alert",0,3)</f>
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
     </row>
@@ -8429,14 +8470,14 @@
       <c r="J153">
         <v>100</v>
       </c>
-      <c r="K153" t="s">
-        <v>23</v>
+      <c r="K153" t="b">
+        <v>0</v>
       </c>
       <c r="L153" t="s">
         <v>16</v>
       </c>
       <c r="M153" t="str">
-        <f>IF(L153="Confusion", "Alert", L153)</f>
+        <f t="shared" si="10"/>
         <v>Alert</v>
       </c>
       <c r="N153" t="s">
@@ -8484,7 +8525,7 @@
         <v>16</v>
       </c>
       <c r="M154" t="str">
-        <f>IF(L154="Confusion", "Alert", L154)</f>
+        <f t="shared" si="10"/>
         <v>Alert</v>
       </c>
       <c r="N154">
@@ -8534,7 +8575,7 @@
         <v>16</v>
       </c>
       <c r="M155" t="str">
-        <f>IF(L155="Confusion", "Alert", L155)</f>
+        <f t="shared" si="10"/>
         <v>Alert</v>
       </c>
       <c r="N155">
@@ -8556,12 +8597,6853 @@
       <c r="C156" t="s">
         <v>17</v>
       </c>
-      <c r="D156" s="7"/>
-      <c r="E156" s="4"/>
+      <c r="D156" s="7">
+        <v>98.4</v>
+      </c>
+      <c r="E156" s="5">
+        <f>ROUND((D156-32)*(5/9),1)</f>
+        <v>36.9</v>
+      </c>
+      <c r="F156">
+        <v>148</v>
+      </c>
+      <c r="G156">
+        <v>80</v>
+      </c>
+      <c r="H156">
+        <v>76</v>
+      </c>
+      <c r="I156">
+        <v>16</v>
+      </c>
+      <c r="J156">
+        <v>97</v>
+      </c>
+      <c r="K156" t="b">
+        <v>0</v>
+      </c>
+      <c r="L156" t="s">
+        <v>16</v>
+      </c>
+      <c r="M156" t="s">
+        <v>16</v>
+      </c>
+      <c r="N156">
+        <f>IF(I156&lt;9,2,IF(I156&lt;=14,0,IF(I156&lt;=20,1,IF(I156&lt;=29,2,3))))+IF(H156&lt;=40,2,IF(H156&lt;=50,1,IF(H156&lt;=100,0,IF(H156&lt;=110,1,IF(H156&lt;=129,2,3)))))+IF(F156&lt;=70,3,IF(F156&lt;=80,2,IF(F156&lt;=100,1,IF(F156&lt;200,0,IF(F156&gt;=200,2,0)))))+IF(E156&lt;35,2,IF(E156&lt;=38.4,0,2))+IF(M156="Alert",0,IF(M156="Voice",1,IF(M156="Pain",2,IF(M156="Unresponsive",3,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="O156">
+        <f>IF(I156&lt;=8,3,IF(I156&lt;=11,1,IF(I156&lt;=20,0,IF(I156&lt;=24,2,3))))
++IF(J156&lt;=91,3,IF(J156&lt;=93,2,IF(J156&lt;=95,1,0)))
++IF(K156=TRUE,2,0)
++IF(F156&lt;=90,3,IF(F156&lt;=100,2,IF(F156&lt;=110,1,IF(F156&lt;=219,0,3))))
++IF(H156&lt;=40,3,IF(H156&lt;=50,1,IF(H156&lt;=90,0,IF(H156&lt;=110,1,IF(H156&lt;=130,2,3)))))
++IF(M156="Alert",0,3)
++IF(E156&lt;=35,3,IF(E156&lt;=36,1,IF(E156&lt;=38,0,IF(E156&lt;=39,1,2))))</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="D157" s="8"/>
-      <c r="E157" s="5"/>
+      <c r="A157">
+        <v>16402426</v>
+      </c>
+      <c r="B157">
+        <v>20095203</v>
+      </c>
+      <c r="C157" t="s">
+        <v>15</v>
+      </c>
+      <c r="D157" s="8">
+        <v>101.3</v>
+      </c>
+      <c r="E157" s="5">
+        <f t="shared" ref="E157:E220" si="11">ROUND((D157-32)*(5/9),1)</f>
+        <v>38.5</v>
+      </c>
+      <c r="F157">
+        <v>120</v>
+      </c>
+      <c r="G157">
+        <v>70</v>
+      </c>
+      <c r="H157">
+        <v>99</v>
+      </c>
+      <c r="I157">
+        <v>20</v>
+      </c>
+      <c r="J157">
+        <v>99</v>
+      </c>
+      <c r="K157" t="b">
+        <v>0</v>
+      </c>
+      <c r="L157" t="s">
+        <v>16</v>
+      </c>
+      <c r="M157" t="s">
+        <v>16</v>
+      </c>
+      <c r="N157">
+        <f t="shared" ref="N157:N220" si="12">IF(I157&lt;9,2,IF(I157&lt;=14,0,IF(I157&lt;=20,1,IF(I157&lt;=29,2,3))))+IF(H157&lt;=40,2,IF(H157&lt;=50,1,IF(H157&lt;=100,0,IF(H157&lt;=110,1,IF(H157&lt;=129,2,3)))))+IF(F157&lt;=70,3,IF(F157&lt;=80,2,IF(F157&lt;=100,1,IF(F157&lt;200,0,IF(F157&gt;=200,2,0)))))+IF(E157&lt;35,2,IF(E157&lt;=38.4,0,2))+IF(M157="Alert",0,IF(M157="Voice",1,IF(M157="Pain",2,IF(M157="Unresponsive",3,0))))</f>
+        <v>3</v>
+      </c>
+      <c r="O157">
+        <f t="shared" ref="O157:O220" si="13">IF(I157&lt;=8,3,IF(I157&lt;=11,1,IF(I157&lt;=20,0,IF(I157&lt;=24,2,3))))
++IF(J157&lt;=91,3,IF(J157&lt;=93,2,IF(J157&lt;=95,1,0)))
++IF(K157=TRUE,2,0)
++IF(F157&lt;=90,3,IF(F157&lt;=100,2,IF(F157&lt;=110,1,IF(F157&lt;=219,0,3))))
++IF(H157&lt;=40,3,IF(H157&lt;=50,1,IF(H157&lt;=90,0,IF(H157&lt;=110,1,IF(H157&lt;=130,2,3)))))
++IF(M157="Alert",0,3)
++IF(E157&lt;=35,3,IF(E157&lt;=36,1,IF(E157&lt;=38,0,IF(E157&lt;=39,1,2))))</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>12946587</v>
+      </c>
+      <c r="B158">
+        <v>20370695</v>
+      </c>
+      <c r="C158" t="s">
+        <v>15</v>
+      </c>
+      <c r="D158" s="9">
+        <v>98</v>
+      </c>
+      <c r="E158" s="5">
+        <f t="shared" si="11"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F158">
+        <v>123</v>
+      </c>
+      <c r="G158">
+        <v>55</v>
+      </c>
+      <c r="H158">
+        <v>65</v>
+      </c>
+      <c r="I158">
+        <v>18</v>
+      </c>
+      <c r="J158">
+        <v>99</v>
+      </c>
+      <c r="K158" t="b">
+        <v>0</v>
+      </c>
+      <c r="L158" t="s">
+        <v>16</v>
+      </c>
+      <c r="M158" t="s">
+        <v>16</v>
+      </c>
+      <c r="N158">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O158">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>13876660</v>
+      </c>
+      <c r="B159">
+        <v>20411393</v>
+      </c>
+      <c r="C159" t="s">
+        <v>15</v>
+      </c>
+      <c r="D159" s="10">
+        <v>98</v>
+      </c>
+      <c r="E159" s="5">
+        <f t="shared" si="11"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F159">
+        <v>128</v>
+      </c>
+      <c r="G159">
+        <v>69</v>
+      </c>
+      <c r="H159">
+        <v>60</v>
+      </c>
+      <c r="I159">
+        <v>14</v>
+      </c>
+      <c r="J159">
+        <v>96</v>
+      </c>
+      <c r="K159" t="b">
+        <v>0</v>
+      </c>
+      <c r="L159" t="s">
+        <v>16</v>
+      </c>
+      <c r="M159" t="s">
+        <v>16</v>
+      </c>
+      <c r="N159">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O159">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>11723660</v>
+      </c>
+      <c r="B160">
+        <v>20502229</v>
+      </c>
+      <c r="C160" t="s">
+        <v>17</v>
+      </c>
+      <c r="D160">
+        <v>98.3</v>
+      </c>
+      <c r="E160" s="5">
+        <f t="shared" si="11"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F160">
+        <v>123</v>
+      </c>
+      <c r="G160">
+        <v>85</v>
+      </c>
+      <c r="H160">
+        <v>118</v>
+      </c>
+      <c r="I160">
+        <v>20</v>
+      </c>
+      <c r="J160">
+        <v>94</v>
+      </c>
+      <c r="K160" t="b">
+        <v>0</v>
+      </c>
+      <c r="L160" t="s">
+        <v>16</v>
+      </c>
+      <c r="M160" t="s">
+        <v>16</v>
+      </c>
+      <c r="N160">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="O160">
+        <f t="shared" si="13"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>16566233</v>
+      </c>
+      <c r="B161">
+        <v>21007184</v>
+      </c>
+      <c r="C161" t="s">
+        <v>15</v>
+      </c>
+      <c r="D161">
+        <v>97.5</v>
+      </c>
+      <c r="E161" s="5">
+        <f t="shared" si="11"/>
+        <v>36.4</v>
+      </c>
+      <c r="F161">
+        <v>160</v>
+      </c>
+      <c r="G161">
+        <v>110</v>
+      </c>
+      <c r="H161">
+        <v>81</v>
+      </c>
+      <c r="I161">
+        <v>18</v>
+      </c>
+      <c r="J161">
+        <v>96</v>
+      </c>
+      <c r="K161" t="b">
+        <v>0</v>
+      </c>
+      <c r="L161" t="s">
+        <v>16</v>
+      </c>
+      <c r="M161" t="s">
+        <v>16</v>
+      </c>
+      <c r="N161">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O161">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>19332122</v>
+      </c>
+      <c r="B162">
+        <v>21075884</v>
+      </c>
+      <c r="C162" t="s">
+        <v>17</v>
+      </c>
+      <c r="D162" t="s">
+        <v>23</v>
+      </c>
+      <c r="E162" t="s">
+        <v>23</v>
+      </c>
+      <c r="F162" t="s">
+        <v>23</v>
+      </c>
+      <c r="G162" t="s">
+        <v>23</v>
+      </c>
+      <c r="H162" t="s">
+        <v>23</v>
+      </c>
+      <c r="I162" t="s">
+        <v>23</v>
+      </c>
+      <c r="J162" t="s">
+        <v>23</v>
+      </c>
+      <c r="K162" t="b">
+        <v>0</v>
+      </c>
+      <c r="L162" t="s">
+        <v>16</v>
+      </c>
+      <c r="M162" t="s">
+        <v>16</v>
+      </c>
+      <c r="N162" t="s">
+        <v>23</v>
+      </c>
+      <c r="O162" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>18606160</v>
+      </c>
+      <c r="B163">
+        <v>21234889</v>
+      </c>
+      <c r="C163" t="s">
+        <v>15</v>
+      </c>
+      <c r="D163">
+        <v>98.9</v>
+      </c>
+      <c r="E163" s="5">
+        <f t="shared" si="11"/>
+        <v>37.200000000000003</v>
+      </c>
+      <c r="F163">
+        <v>126</v>
+      </c>
+      <c r="G163">
+        <v>20</v>
+      </c>
+      <c r="H163">
+        <v>88</v>
+      </c>
+      <c r="I163">
+        <v>20</v>
+      </c>
+      <c r="J163">
+        <v>97</v>
+      </c>
+      <c r="K163" t="b">
+        <v>0</v>
+      </c>
+      <c r="L163" t="s">
+        <v>16</v>
+      </c>
+      <c r="M163" t="s">
+        <v>16</v>
+      </c>
+      <c r="N163">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O163">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>18284921</v>
+      </c>
+      <c r="B164">
+        <v>21304621</v>
+      </c>
+      <c r="C164" t="s">
+        <v>15</v>
+      </c>
+      <c r="D164">
+        <v>97.8</v>
+      </c>
+      <c r="E164" s="5">
+        <f t="shared" si="11"/>
+        <v>36.6</v>
+      </c>
+      <c r="F164">
+        <v>135</v>
+      </c>
+      <c r="G164">
+        <v>79</v>
+      </c>
+      <c r="H164">
+        <v>85</v>
+      </c>
+      <c r="I164">
+        <v>17</v>
+      </c>
+      <c r="J164">
+        <v>97</v>
+      </c>
+      <c r="K164" t="b">
+        <v>0</v>
+      </c>
+      <c r="L164" t="s">
+        <v>16</v>
+      </c>
+      <c r="M164" t="s">
+        <v>16</v>
+      </c>
+      <c r="N164">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O164">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>10626542</v>
+      </c>
+      <c r="B165">
+        <v>21419975</v>
+      </c>
+      <c r="C165" t="s">
+        <v>18</v>
+      </c>
+      <c r="D165">
+        <v>97.9</v>
+      </c>
+      <c r="E165" s="5">
+        <f t="shared" si="11"/>
+        <v>36.6</v>
+      </c>
+      <c r="F165">
+        <v>138</v>
+      </c>
+      <c r="G165">
+        <v>65</v>
+      </c>
+      <c r="H165">
+        <v>71</v>
+      </c>
+      <c r="I165">
+        <v>20</v>
+      </c>
+      <c r="J165">
+        <v>97</v>
+      </c>
+      <c r="K165" t="b">
+        <v>0</v>
+      </c>
+      <c r="L165" t="s">
+        <v>16</v>
+      </c>
+      <c r="M165" t="s">
+        <v>16</v>
+      </c>
+      <c r="N165">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O165">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>16536362</v>
+      </c>
+      <c r="B166">
+        <v>21511681</v>
+      </c>
+      <c r="C166" t="s">
+        <v>17</v>
+      </c>
+      <c r="D166" t="s">
+        <v>23</v>
+      </c>
+      <c r="E166" t="s">
+        <v>23</v>
+      </c>
+      <c r="F166" t="s">
+        <v>23</v>
+      </c>
+      <c r="G166" t="s">
+        <v>23</v>
+      </c>
+      <c r="H166" t="s">
+        <v>23</v>
+      </c>
+      <c r="I166" t="s">
+        <v>23</v>
+      </c>
+      <c r="J166" t="s">
+        <v>23</v>
+      </c>
+      <c r="K166" t="b">
+        <v>0</v>
+      </c>
+      <c r="L166" t="s">
+        <v>16</v>
+      </c>
+      <c r="M166" t="s">
+        <v>16</v>
+      </c>
+      <c r="N166" t="s">
+        <v>23</v>
+      </c>
+      <c r="O166" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>15376111</v>
+      </c>
+      <c r="B167">
+        <v>21586695</v>
+      </c>
+      <c r="C167" t="s">
+        <v>17</v>
+      </c>
+      <c r="D167">
+        <v>98.3</v>
+      </c>
+      <c r="E167" s="5">
+        <f t="shared" si="11"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F167">
+        <v>133</v>
+      </c>
+      <c r="G167">
+        <v>62</v>
+      </c>
+      <c r="H167">
+        <v>94</v>
+      </c>
+      <c r="I167">
+        <v>18</v>
+      </c>
+      <c r="J167">
+        <v>99</v>
+      </c>
+      <c r="K167" t="b">
+        <v>0</v>
+      </c>
+      <c r="L167" t="s">
+        <v>16</v>
+      </c>
+      <c r="M167" t="s">
+        <v>16</v>
+      </c>
+      <c r="N167">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O167">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>15802242</v>
+      </c>
+      <c r="B168">
+        <v>21609546</v>
+      </c>
+      <c r="C168" t="s">
+        <v>15</v>
+      </c>
+      <c r="D168">
+        <v>97.7</v>
+      </c>
+      <c r="E168" s="5">
+        <f t="shared" si="11"/>
+        <v>36.5</v>
+      </c>
+      <c r="F168">
+        <v>122</v>
+      </c>
+      <c r="G168">
+        <v>77</v>
+      </c>
+      <c r="H168">
+        <v>70</v>
+      </c>
+      <c r="I168">
+        <v>18</v>
+      </c>
+      <c r="J168">
+        <v>98</v>
+      </c>
+      <c r="K168" t="b">
+        <v>0</v>
+      </c>
+      <c r="L168" t="s">
+        <v>16</v>
+      </c>
+      <c r="M168" t="s">
+        <v>16</v>
+      </c>
+      <c r="N168">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O168">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>16378755</v>
+      </c>
+      <c r="B169">
+        <v>21683806</v>
+      </c>
+      <c r="C169" t="s">
+        <v>17</v>
+      </c>
+      <c r="D169">
+        <v>95.7</v>
+      </c>
+      <c r="E169" s="5">
+        <f t="shared" si="11"/>
+        <v>35.4</v>
+      </c>
+      <c r="F169">
+        <v>134</v>
+      </c>
+      <c r="G169">
+        <v>62</v>
+      </c>
+      <c r="H169">
+        <v>98</v>
+      </c>
+      <c r="I169">
+        <v>22</v>
+      </c>
+      <c r="J169">
+        <v>95</v>
+      </c>
+      <c r="K169" t="b">
+        <v>0</v>
+      </c>
+      <c r="L169" t="s">
+        <v>16</v>
+      </c>
+      <c r="M169" t="s">
+        <v>16</v>
+      </c>
+      <c r="N169">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="O169">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>12450853</v>
+      </c>
+      <c r="B170">
+        <v>21712365</v>
+      </c>
+      <c r="C170" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170">
+        <v>98.2</v>
+      </c>
+      <c r="E170" s="5">
+        <f t="shared" si="11"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F170">
+        <v>155</v>
+      </c>
+      <c r="G170">
+        <v>77</v>
+      </c>
+      <c r="H170">
+        <v>90</v>
+      </c>
+      <c r="I170">
+        <v>18</v>
+      </c>
+      <c r="J170">
+        <v>96</v>
+      </c>
+      <c r="K170" t="b">
+        <v>0</v>
+      </c>
+      <c r="L170" t="s">
+        <v>16</v>
+      </c>
+      <c r="M170" t="s">
+        <v>16</v>
+      </c>
+      <c r="N170">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O170">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>13523655</v>
+      </c>
+      <c r="B171">
+        <v>21983182</v>
+      </c>
+      <c r="C171" t="s">
+        <v>15</v>
+      </c>
+      <c r="D171">
+        <v>98.5</v>
+      </c>
+      <c r="E171" s="5">
+        <f t="shared" si="11"/>
+        <v>36.9</v>
+      </c>
+      <c r="F171">
+        <v>115</v>
+      </c>
+      <c r="G171">
+        <v>72</v>
+      </c>
+      <c r="H171">
+        <v>74</v>
+      </c>
+      <c r="I171">
+        <v>18</v>
+      </c>
+      <c r="J171">
+        <v>99</v>
+      </c>
+      <c r="K171" t="b">
+        <v>0</v>
+      </c>
+      <c r="L171" t="s">
+        <v>16</v>
+      </c>
+      <c r="M171" t="s">
+        <v>16</v>
+      </c>
+      <c r="N171">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O171">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>11334897</v>
+      </c>
+      <c r="B172">
+        <v>22246289</v>
+      </c>
+      <c r="C172" t="s">
+        <v>15</v>
+      </c>
+      <c r="D172">
+        <v>98.2</v>
+      </c>
+      <c r="E172" s="5">
+        <f t="shared" si="11"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F172">
+        <v>126</v>
+      </c>
+      <c r="G172">
+        <v>79</v>
+      </c>
+      <c r="H172">
+        <v>87</v>
+      </c>
+      <c r="I172">
+        <v>19</v>
+      </c>
+      <c r="J172">
+        <v>96</v>
+      </c>
+      <c r="K172" t="b">
+        <v>0</v>
+      </c>
+      <c r="L172" t="s">
+        <v>16</v>
+      </c>
+      <c r="M172" t="s">
+        <v>16</v>
+      </c>
+      <c r="N172">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O172">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>18549459</v>
+      </c>
+      <c r="B173">
+        <v>22264870</v>
+      </c>
+      <c r="C173" t="s">
+        <v>18</v>
+      </c>
+      <c r="D173" t="s">
+        <v>23</v>
+      </c>
+      <c r="E173" t="s">
+        <v>23</v>
+      </c>
+      <c r="F173" t="s">
+        <v>23</v>
+      </c>
+      <c r="G173" t="s">
+        <v>23</v>
+      </c>
+      <c r="H173" t="s">
+        <v>23</v>
+      </c>
+      <c r="I173" t="s">
+        <v>23</v>
+      </c>
+      <c r="J173" t="s">
+        <v>23</v>
+      </c>
+      <c r="K173" t="b">
+        <v>0</v>
+      </c>
+      <c r="L173" t="s">
+        <v>16</v>
+      </c>
+      <c r="M173" t="s">
+        <v>16</v>
+      </c>
+      <c r="N173" t="s">
+        <v>23</v>
+      </c>
+      <c r="O173" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>11868667</v>
+      </c>
+      <c r="B174">
+        <v>22274722</v>
+      </c>
+      <c r="C174" t="s">
+        <v>17</v>
+      </c>
+      <c r="D174">
+        <v>98</v>
+      </c>
+      <c r="E174" s="5">
+        <f t="shared" si="11"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F174">
+        <v>111</v>
+      </c>
+      <c r="G174">
+        <v>38</v>
+      </c>
+      <c r="H174">
+        <v>61</v>
+      </c>
+      <c r="I174" t="s">
+        <v>23</v>
+      </c>
+      <c r="J174">
+        <v>98</v>
+      </c>
+      <c r="K174" t="b">
+        <v>0</v>
+      </c>
+      <c r="L174" t="s">
+        <v>16</v>
+      </c>
+      <c r="M174" t="s">
+        <v>16</v>
+      </c>
+      <c r="N174" t="s">
+        <v>23</v>
+      </c>
+      <c r="O174" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>19833978</v>
+      </c>
+      <c r="B175">
+        <v>22368455</v>
+      </c>
+      <c r="C175" t="s">
+        <v>15</v>
+      </c>
+      <c r="D175" t="s">
+        <v>23</v>
+      </c>
+      <c r="E175" t="s">
+        <v>23</v>
+      </c>
+      <c r="F175" t="s">
+        <v>23</v>
+      </c>
+      <c r="G175" t="s">
+        <v>23</v>
+      </c>
+      <c r="H175" t="s">
+        <v>23</v>
+      </c>
+      <c r="I175" t="s">
+        <v>23</v>
+      </c>
+      <c r="J175" t="s">
+        <v>23</v>
+      </c>
+      <c r="K175" t="b">
+        <v>0</v>
+      </c>
+      <c r="L175" t="s">
+        <v>16</v>
+      </c>
+      <c r="M175" t="s">
+        <v>16</v>
+      </c>
+      <c r="N175" t="s">
+        <v>23</v>
+      </c>
+      <c r="O175" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>10285455</v>
+      </c>
+      <c r="B176">
+        <v>22472652</v>
+      </c>
+      <c r="C176" t="s">
+        <v>15</v>
+      </c>
+      <c r="D176" t="s">
+        <v>23</v>
+      </c>
+      <c r="E176" t="s">
+        <v>23</v>
+      </c>
+      <c r="F176" t="s">
+        <v>23</v>
+      </c>
+      <c r="G176" t="s">
+        <v>23</v>
+      </c>
+      <c r="H176" t="s">
+        <v>23</v>
+      </c>
+      <c r="I176" t="s">
+        <v>23</v>
+      </c>
+      <c r="J176" t="s">
+        <v>23</v>
+      </c>
+      <c r="K176" t="b">
+        <v>0</v>
+      </c>
+      <c r="L176" t="s">
+        <v>16</v>
+      </c>
+      <c r="M176" t="s">
+        <v>16</v>
+      </c>
+      <c r="N176" t="s">
+        <v>23</v>
+      </c>
+      <c r="O176" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>17451713</v>
+      </c>
+      <c r="B177">
+        <v>22951644</v>
+      </c>
+      <c r="C177" t="s">
+        <v>17</v>
+      </c>
+      <c r="D177">
+        <v>96.9</v>
+      </c>
+      <c r="E177" s="5">
+        <f t="shared" si="11"/>
+        <v>36.1</v>
+      </c>
+      <c r="F177">
+        <v>130</v>
+      </c>
+      <c r="G177">
+        <v>74</v>
+      </c>
+      <c r="H177">
+        <v>88</v>
+      </c>
+      <c r="I177">
+        <v>18</v>
+      </c>
+      <c r="J177">
+        <v>100</v>
+      </c>
+      <c r="K177" t="b">
+        <v>0</v>
+      </c>
+      <c r="L177" t="s">
+        <v>16</v>
+      </c>
+      <c r="M177" t="s">
+        <v>16</v>
+      </c>
+      <c r="N177">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O177">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>16271779</v>
+      </c>
+      <c r="B178">
+        <v>22967596</v>
+      </c>
+      <c r="C178" t="s">
+        <v>17</v>
+      </c>
+      <c r="D178">
+        <v>98.7</v>
+      </c>
+      <c r="E178" s="5">
+        <f t="shared" si="11"/>
+        <v>37.1</v>
+      </c>
+      <c r="F178">
+        <v>114</v>
+      </c>
+      <c r="G178">
+        <v>76</v>
+      </c>
+      <c r="H178">
+        <v>92</v>
+      </c>
+      <c r="I178">
+        <v>18</v>
+      </c>
+      <c r="J178">
+        <v>97</v>
+      </c>
+      <c r="K178" t="b">
+        <v>0</v>
+      </c>
+      <c r="L178" t="s">
+        <v>16</v>
+      </c>
+      <c r="M178" t="s">
+        <v>16</v>
+      </c>
+      <c r="N178">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O178">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>17396346</v>
+      </c>
+      <c r="B179">
+        <v>23124779</v>
+      </c>
+      <c r="C179" t="s">
+        <v>17</v>
+      </c>
+      <c r="D179">
+        <v>100.1</v>
+      </c>
+      <c r="E179" s="5">
+        <f t="shared" si="11"/>
+        <v>37.799999999999997</v>
+      </c>
+      <c r="F179">
+        <v>132</v>
+      </c>
+      <c r="G179">
+        <v>53</v>
+      </c>
+      <c r="H179">
+        <v>89</v>
+      </c>
+      <c r="I179">
+        <v>21</v>
+      </c>
+      <c r="J179">
+        <v>94</v>
+      </c>
+      <c r="K179" t="b">
+        <v>1</v>
+      </c>
+      <c r="L179" t="s">
+        <v>16</v>
+      </c>
+      <c r="M179" t="s">
+        <v>16</v>
+      </c>
+      <c r="N179">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="O179">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>16154666</v>
+      </c>
+      <c r="B180">
+        <v>23167950</v>
+      </c>
+      <c r="C180" t="s">
+        <v>15</v>
+      </c>
+      <c r="D180">
+        <v>97.8</v>
+      </c>
+      <c r="E180" s="5">
+        <f t="shared" si="11"/>
+        <v>36.6</v>
+      </c>
+      <c r="F180">
+        <v>114</v>
+      </c>
+      <c r="G180">
+        <v>68</v>
+      </c>
+      <c r="H180">
+        <v>66</v>
+      </c>
+      <c r="I180">
+        <v>24</v>
+      </c>
+      <c r="J180">
+        <v>98</v>
+      </c>
+      <c r="K180" t="b">
+        <v>1</v>
+      </c>
+      <c r="L180" t="s">
+        <v>16</v>
+      </c>
+      <c r="M180" t="s">
+        <v>16</v>
+      </c>
+      <c r="N180">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="O180">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>15974128</v>
+      </c>
+      <c r="B181">
+        <v>23330764</v>
+      </c>
+      <c r="C181" t="s">
+        <v>15</v>
+      </c>
+      <c r="D181">
+        <v>98.3</v>
+      </c>
+      <c r="E181" s="5">
+        <f t="shared" si="11"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F181">
+        <v>102</v>
+      </c>
+      <c r="G181">
+        <v>49</v>
+      </c>
+      <c r="H181">
+        <v>93</v>
+      </c>
+      <c r="I181">
+        <v>20</v>
+      </c>
+      <c r="J181">
+        <v>95</v>
+      </c>
+      <c r="K181" t="b">
+        <v>1</v>
+      </c>
+      <c r="L181" t="s">
+        <v>16</v>
+      </c>
+      <c r="M181" t="s">
+        <v>16</v>
+      </c>
+      <c r="N181">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O181">
+        <f t="shared" si="13"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>17173451</v>
+      </c>
+      <c r="B182">
+        <v>23428803</v>
+      </c>
+      <c r="C182" t="s">
+        <v>17</v>
+      </c>
+      <c r="D182" t="s">
+        <v>23</v>
+      </c>
+      <c r="E182" s="5" t="e">
+        <f t="shared" si="11"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="F182">
+        <v>192</v>
+      </c>
+      <c r="G182">
+        <v>98</v>
+      </c>
+      <c r="H182">
+        <v>86</v>
+      </c>
+      <c r="I182">
+        <v>16</v>
+      </c>
+      <c r="J182">
+        <v>98</v>
+      </c>
+      <c r="K182" t="b">
+        <v>0</v>
+      </c>
+      <c r="L182" t="s">
+        <v>16</v>
+      </c>
+      <c r="M182" t="s">
+        <v>16</v>
+      </c>
+      <c r="N182" t="s">
+        <v>23</v>
+      </c>
+      <c r="O182" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>15929369</v>
+      </c>
+      <c r="B183">
+        <v>23498272</v>
+      </c>
+      <c r="C183" t="s">
+        <v>18</v>
+      </c>
+      <c r="D183">
+        <v>98.4</v>
+      </c>
+      <c r="E183" s="5">
+        <f t="shared" si="11"/>
+        <v>36.9</v>
+      </c>
+      <c r="F183">
+        <v>90</v>
+      </c>
+      <c r="G183">
+        <v>71</v>
+      </c>
+      <c r="H183">
+        <v>114</v>
+      </c>
+      <c r="I183" t="s">
+        <v>23</v>
+      </c>
+      <c r="J183">
+        <v>100</v>
+      </c>
+      <c r="K183" t="b">
+        <v>0</v>
+      </c>
+      <c r="L183" t="s">
+        <v>16</v>
+      </c>
+      <c r="M183" t="s">
+        <v>16</v>
+      </c>
+      <c r="N183" t="s">
+        <v>23</v>
+      </c>
+      <c r="O183" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>10141505</v>
+      </c>
+      <c r="B184">
+        <v>23498379</v>
+      </c>
+      <c r="C184" t="s">
+        <v>15</v>
+      </c>
+      <c r="D184">
+        <v>97.5</v>
+      </c>
+      <c r="E184" s="5">
+        <f t="shared" si="11"/>
+        <v>36.4</v>
+      </c>
+      <c r="F184">
+        <v>150</v>
+      </c>
+      <c r="G184">
+        <v>70</v>
+      </c>
+      <c r="H184">
+        <v>54</v>
+      </c>
+      <c r="I184">
+        <v>18</v>
+      </c>
+      <c r="J184">
+        <v>99</v>
+      </c>
+      <c r="K184" t="b">
+        <v>0</v>
+      </c>
+      <c r="L184" t="s">
+        <v>16</v>
+      </c>
+      <c r="M184" t="s">
+        <v>16</v>
+      </c>
+      <c r="N184">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O184">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>18088163</v>
+      </c>
+      <c r="B185">
+        <v>23597911</v>
+      </c>
+      <c r="C185" t="s">
+        <v>15</v>
+      </c>
+      <c r="D185" t="s">
+        <v>23</v>
+      </c>
+      <c r="E185" t="s">
+        <v>23</v>
+      </c>
+      <c r="F185" t="s">
+        <v>23</v>
+      </c>
+      <c r="G185" t="s">
+        <v>23</v>
+      </c>
+      <c r="H185" t="s">
+        <v>23</v>
+      </c>
+      <c r="I185" t="s">
+        <v>23</v>
+      </c>
+      <c r="J185" t="s">
+        <v>23</v>
+      </c>
+      <c r="K185" t="b">
+        <v>0</v>
+      </c>
+      <c r="L185" t="s">
+        <v>16</v>
+      </c>
+      <c r="M185" t="s">
+        <v>16</v>
+      </c>
+      <c r="N185" t="s">
+        <v>23</v>
+      </c>
+      <c r="O185" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>17158007</v>
+      </c>
+      <c r="B186">
+        <v>23936243</v>
+      </c>
+      <c r="C186" t="s">
+        <v>15</v>
+      </c>
+      <c r="D186">
+        <v>97.5</v>
+      </c>
+      <c r="E186" s="5">
+        <f t="shared" si="11"/>
+        <v>36.4</v>
+      </c>
+      <c r="F186">
+        <v>111</v>
+      </c>
+      <c r="G186">
+        <v>80</v>
+      </c>
+      <c r="H186">
+        <v>96</v>
+      </c>
+      <c r="I186">
+        <v>18</v>
+      </c>
+      <c r="J186">
+        <v>97</v>
+      </c>
+      <c r="K186" t="b">
+        <v>0</v>
+      </c>
+      <c r="L186" t="s">
+        <v>16</v>
+      </c>
+      <c r="M186" t="s">
+        <v>16</v>
+      </c>
+      <c r="N186">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O186">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>18427137</v>
+      </c>
+      <c r="B187">
+        <v>24255830</v>
+      </c>
+      <c r="C187" t="s">
+        <v>15</v>
+      </c>
+      <c r="D187">
+        <v>98.6</v>
+      </c>
+      <c r="E187" s="5">
+        <f t="shared" si="11"/>
+        <v>37</v>
+      </c>
+      <c r="F187">
+        <v>155</v>
+      </c>
+      <c r="G187">
+        <v>94</v>
+      </c>
+      <c r="H187">
+        <v>73</v>
+      </c>
+      <c r="I187">
+        <v>18</v>
+      </c>
+      <c r="J187">
+        <v>95</v>
+      </c>
+      <c r="K187" t="b">
+        <v>0</v>
+      </c>
+      <c r="L187" t="s">
+        <v>16</v>
+      </c>
+      <c r="M187" t="s">
+        <v>16</v>
+      </c>
+      <c r="N187">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O187">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>16543672</v>
+      </c>
+      <c r="B188">
+        <v>24273456</v>
+      </c>
+      <c r="C188" t="s">
+        <v>18</v>
+      </c>
+      <c r="D188" t="s">
+        <v>23</v>
+      </c>
+      <c r="E188" t="s">
+        <v>23</v>
+      </c>
+      <c r="F188" t="s">
+        <v>23</v>
+      </c>
+      <c r="G188" t="s">
+        <v>23</v>
+      </c>
+      <c r="H188" t="s">
+        <v>23</v>
+      </c>
+      <c r="I188" t="s">
+        <v>23</v>
+      </c>
+      <c r="J188" t="s">
+        <v>23</v>
+      </c>
+      <c r="K188" t="b">
+        <v>0</v>
+      </c>
+      <c r="L188" t="s">
+        <v>22</v>
+      </c>
+      <c r="M188" t="s">
+        <v>22</v>
+      </c>
+      <c r="N188" t="s">
+        <v>23</v>
+      </c>
+      <c r="O188" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>12426442</v>
+      </c>
+      <c r="B189">
+        <v>24365063</v>
+      </c>
+      <c r="C189" t="s">
+        <v>17</v>
+      </c>
+      <c r="D189">
+        <v>97.9</v>
+      </c>
+      <c r="E189" s="5">
+        <f t="shared" si="11"/>
+        <v>36.6</v>
+      </c>
+      <c r="F189">
+        <v>139</v>
+      </c>
+      <c r="G189">
+        <v>64</v>
+      </c>
+      <c r="H189">
+        <v>76</v>
+      </c>
+      <c r="I189">
+        <v>16</v>
+      </c>
+      <c r="J189">
+        <v>100</v>
+      </c>
+      <c r="K189" t="b">
+        <v>0</v>
+      </c>
+      <c r="L189" t="s">
+        <v>16</v>
+      </c>
+      <c r="M189" t="s">
+        <v>16</v>
+      </c>
+      <c r="N189">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O189">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>10872930</v>
+      </c>
+      <c r="B190">
+        <v>24406981</v>
+      </c>
+      <c r="C190" t="s">
+        <v>17</v>
+      </c>
+      <c r="D190">
+        <v>97.5</v>
+      </c>
+      <c r="E190" s="5">
+        <f t="shared" si="11"/>
+        <v>36.4</v>
+      </c>
+      <c r="F190">
+        <v>104</v>
+      </c>
+      <c r="G190">
+        <v>42</v>
+      </c>
+      <c r="H190">
+        <v>79</v>
+      </c>
+      <c r="I190">
+        <v>18</v>
+      </c>
+      <c r="J190">
+        <v>98</v>
+      </c>
+      <c r="K190" t="b">
+        <v>0</v>
+      </c>
+      <c r="L190" t="s">
+        <v>16</v>
+      </c>
+      <c r="M190" t="s">
+        <v>16</v>
+      </c>
+      <c r="N190">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O190">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>12789108</v>
+      </c>
+      <c r="B191">
+        <v>24809449</v>
+      </c>
+      <c r="C191" t="s">
+        <v>17</v>
+      </c>
+      <c r="D191">
+        <v>99.4</v>
+      </c>
+      <c r="E191" s="5">
+        <f t="shared" si="11"/>
+        <v>37.4</v>
+      </c>
+      <c r="F191">
+        <v>117</v>
+      </c>
+      <c r="G191">
+        <v>81</v>
+      </c>
+      <c r="H191">
+        <v>76</v>
+      </c>
+      <c r="I191">
+        <v>20</v>
+      </c>
+      <c r="J191">
+        <v>100</v>
+      </c>
+      <c r="K191" t="b">
+        <v>0</v>
+      </c>
+      <c r="L191" t="s">
+        <v>16</v>
+      </c>
+      <c r="M191" t="s">
+        <v>16</v>
+      </c>
+      <c r="N191">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O191">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>17411142</v>
+      </c>
+      <c r="B192">
+        <v>25129204</v>
+      </c>
+      <c r="C192" t="s">
+        <v>18</v>
+      </c>
+      <c r="D192">
+        <v>96.6</v>
+      </c>
+      <c r="E192" s="5">
+        <f t="shared" si="11"/>
+        <v>35.9</v>
+      </c>
+      <c r="F192">
+        <v>153</v>
+      </c>
+      <c r="G192">
+        <v>85</v>
+      </c>
+      <c r="H192">
+        <v>82</v>
+      </c>
+      <c r="I192">
+        <v>16</v>
+      </c>
+      <c r="J192">
+        <v>99</v>
+      </c>
+      <c r="K192" t="b">
+        <v>0</v>
+      </c>
+      <c r="L192" t="s">
+        <v>16</v>
+      </c>
+      <c r="M192" t="s">
+        <v>16</v>
+      </c>
+      <c r="N192">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O192">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>11729221</v>
+      </c>
+      <c r="B193">
+        <v>25294498</v>
+      </c>
+      <c r="C193" t="s">
+        <v>15</v>
+      </c>
+      <c r="D193">
+        <v>97.5</v>
+      </c>
+      <c r="E193" s="5">
+        <f t="shared" si="11"/>
+        <v>36.4</v>
+      </c>
+      <c r="F193">
+        <v>174</v>
+      </c>
+      <c r="G193">
+        <v>74</v>
+      </c>
+      <c r="H193">
+        <v>63</v>
+      </c>
+      <c r="I193">
+        <v>16</v>
+      </c>
+      <c r="J193">
+        <v>97</v>
+      </c>
+      <c r="K193" t="b">
+        <v>0</v>
+      </c>
+      <c r="L193" t="s">
+        <v>16</v>
+      </c>
+      <c r="M193" t="s">
+        <v>16</v>
+      </c>
+      <c r="N193">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O193">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>11459267</v>
+      </c>
+      <c r="B194">
+        <v>25310929</v>
+      </c>
+      <c r="C194" t="s">
+        <v>15</v>
+      </c>
+      <c r="D194">
+        <v>99.1</v>
+      </c>
+      <c r="E194" s="5">
+        <f t="shared" si="11"/>
+        <v>37.299999999999997</v>
+      </c>
+      <c r="F194">
+        <v>109</v>
+      </c>
+      <c r="G194">
+        <v>49</v>
+      </c>
+      <c r="H194">
+        <v>78</v>
+      </c>
+      <c r="I194">
+        <v>16</v>
+      </c>
+      <c r="J194">
+        <v>100</v>
+      </c>
+      <c r="K194" t="b">
+        <v>0</v>
+      </c>
+      <c r="L194" t="s">
+        <v>16</v>
+      </c>
+      <c r="M194" t="s">
+        <v>16</v>
+      </c>
+      <c r="N194">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O194">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>18160217</v>
+      </c>
+      <c r="B195">
+        <v>25436978</v>
+      </c>
+      <c r="C195" t="s">
+        <v>17</v>
+      </c>
+      <c r="D195">
+        <v>98</v>
+      </c>
+      <c r="E195" s="5">
+        <f t="shared" si="11"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F195">
+        <v>122</v>
+      </c>
+      <c r="G195">
+        <v>63</v>
+      </c>
+      <c r="H195">
+        <v>80</v>
+      </c>
+      <c r="I195">
+        <v>16</v>
+      </c>
+      <c r="J195">
+        <v>100</v>
+      </c>
+      <c r="K195" t="b">
+        <v>0</v>
+      </c>
+      <c r="L195" t="s">
+        <v>16</v>
+      </c>
+      <c r="M195" t="s">
+        <v>16</v>
+      </c>
+      <c r="N195">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O195">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>15778426</v>
+      </c>
+      <c r="B196">
+        <v>25546217</v>
+      </c>
+      <c r="C196" t="s">
+        <v>17</v>
+      </c>
+      <c r="D196">
+        <v>101</v>
+      </c>
+      <c r="E196" s="5">
+        <f t="shared" si="11"/>
+        <v>38.299999999999997</v>
+      </c>
+      <c r="F196">
+        <v>145</v>
+      </c>
+      <c r="G196">
+        <v>66</v>
+      </c>
+      <c r="H196">
+        <v>81</v>
+      </c>
+      <c r="I196">
+        <v>18</v>
+      </c>
+      <c r="J196">
+        <v>94</v>
+      </c>
+      <c r="K196" t="b">
+        <v>1</v>
+      </c>
+      <c r="L196" t="s">
+        <v>16</v>
+      </c>
+      <c r="M196" t="s">
+        <v>16</v>
+      </c>
+      <c r="N196">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O196">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>14695267</v>
+      </c>
+      <c r="B197">
+        <v>25560683</v>
+      </c>
+      <c r="C197" t="s">
+        <v>15</v>
+      </c>
+      <c r="D197" t="s">
+        <v>23</v>
+      </c>
+      <c r="E197" t="s">
+        <v>23</v>
+      </c>
+      <c r="F197" t="s">
+        <v>23</v>
+      </c>
+      <c r="G197" t="s">
+        <v>23</v>
+      </c>
+      <c r="H197" t="s">
+        <v>23</v>
+      </c>
+      <c r="I197" t="s">
+        <v>23</v>
+      </c>
+      <c r="J197" t="s">
+        <v>23</v>
+      </c>
+      <c r="K197" t="b">
+        <v>0</v>
+      </c>
+      <c r="L197" t="s">
+        <v>16</v>
+      </c>
+      <c r="M197" t="s">
+        <v>16</v>
+      </c>
+      <c r="N197" t="s">
+        <v>23</v>
+      </c>
+      <c r="O197" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>10194776</v>
+      </c>
+      <c r="B198">
+        <v>25682890</v>
+      </c>
+      <c r="C198" t="s">
+        <v>15</v>
+      </c>
+      <c r="D198">
+        <v>98.8</v>
+      </c>
+      <c r="E198" s="5">
+        <f t="shared" si="11"/>
+        <v>37.1</v>
+      </c>
+      <c r="F198">
+        <v>151</v>
+      </c>
+      <c r="G198">
+        <v>63</v>
+      </c>
+      <c r="H198">
+        <v>87</v>
+      </c>
+      <c r="I198">
+        <v>13</v>
+      </c>
+      <c r="J198">
+        <v>100</v>
+      </c>
+      <c r="K198" t="b">
+        <v>0</v>
+      </c>
+      <c r="L198" t="s">
+        <v>16</v>
+      </c>
+      <c r="M198" t="s">
+        <v>16</v>
+      </c>
+      <c r="N198">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O198">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>15241318</v>
+      </c>
+      <c r="B199">
+        <v>25704973</v>
+      </c>
+      <c r="C199" t="s">
+        <v>17</v>
+      </c>
+      <c r="D199">
+        <v>98.9</v>
+      </c>
+      <c r="E199" s="5">
+        <f t="shared" si="11"/>
+        <v>37.200000000000003</v>
+      </c>
+      <c r="F199">
+        <v>109</v>
+      </c>
+      <c r="G199">
+        <v>67</v>
+      </c>
+      <c r="H199">
+        <v>83</v>
+      </c>
+      <c r="I199">
+        <v>19</v>
+      </c>
+      <c r="J199">
+        <v>99</v>
+      </c>
+      <c r="K199" t="b">
+        <v>0</v>
+      </c>
+      <c r="L199" t="s">
+        <v>16</v>
+      </c>
+      <c r="M199" t="s">
+        <v>16</v>
+      </c>
+      <c r="N199">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O199">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>17910893</v>
+      </c>
+      <c r="B200">
+        <v>25752929</v>
+      </c>
+      <c r="C200" t="s">
+        <v>17</v>
+      </c>
+      <c r="D200">
+        <v>98.4</v>
+      </c>
+      <c r="E200" s="5">
+        <f t="shared" si="11"/>
+        <v>36.9</v>
+      </c>
+      <c r="F200">
+        <v>128</v>
+      </c>
+      <c r="G200">
+        <v>81</v>
+      </c>
+      <c r="H200">
+        <v>111</v>
+      </c>
+      <c r="I200">
+        <v>18</v>
+      </c>
+      <c r="J200">
+        <v>100</v>
+      </c>
+      <c r="K200" t="b">
+        <v>0</v>
+      </c>
+      <c r="L200" t="s">
+        <v>16</v>
+      </c>
+      <c r="M200" t="s">
+        <v>16</v>
+      </c>
+      <c r="N200">
+        <f t="shared" si="12"/>
+        <v>3</v>
+      </c>
+      <c r="O200">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>14329697</v>
+      </c>
+      <c r="B201">
+        <v>25850355</v>
+      </c>
+      <c r="C201" t="s">
+        <v>15</v>
+      </c>
+      <c r="D201">
+        <v>97.5</v>
+      </c>
+      <c r="E201" s="5">
+        <f t="shared" si="11"/>
+        <v>36.4</v>
+      </c>
+      <c r="F201">
+        <v>160</v>
+      </c>
+      <c r="G201">
+        <v>85</v>
+      </c>
+      <c r="H201">
+        <v>67</v>
+      </c>
+      <c r="I201">
+        <v>18</v>
+      </c>
+      <c r="J201">
+        <v>95</v>
+      </c>
+      <c r="K201" t="b">
+        <v>0</v>
+      </c>
+      <c r="L201" t="s">
+        <v>16</v>
+      </c>
+      <c r="M201" t="s">
+        <v>16</v>
+      </c>
+      <c r="N201">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O201">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>14063236</v>
+      </c>
+      <c r="B202">
+        <v>25910280</v>
+      </c>
+      <c r="C202" t="s">
+        <v>18</v>
+      </c>
+      <c r="D202" t="s">
+        <v>23</v>
+      </c>
+      <c r="E202" t="s">
+        <v>23</v>
+      </c>
+      <c r="F202" t="s">
+        <v>23</v>
+      </c>
+      <c r="G202" t="s">
+        <v>23</v>
+      </c>
+      <c r="H202" t="s">
+        <v>23</v>
+      </c>
+      <c r="I202" t="s">
+        <v>23</v>
+      </c>
+      <c r="J202" t="s">
+        <v>23</v>
+      </c>
+      <c r="K202" t="b">
+        <v>0</v>
+      </c>
+      <c r="L202" t="s">
+        <v>16</v>
+      </c>
+      <c r="M202" t="s">
+        <v>16</v>
+      </c>
+      <c r="N202" t="s">
+        <v>23</v>
+      </c>
+      <c r="O202" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>15291456</v>
+      </c>
+      <c r="B203">
+        <v>26017968</v>
+      </c>
+      <c r="C203" t="s">
+        <v>15</v>
+      </c>
+      <c r="D203">
+        <v>98.5</v>
+      </c>
+      <c r="E203" s="5">
+        <f t="shared" si="11"/>
+        <v>36.9</v>
+      </c>
+      <c r="F203">
+        <v>140</v>
+      </c>
+      <c r="G203">
+        <v>76</v>
+      </c>
+      <c r="H203">
+        <v>60</v>
+      </c>
+      <c r="I203">
+        <v>18</v>
+      </c>
+      <c r="J203">
+        <v>99</v>
+      </c>
+      <c r="K203" t="b">
+        <v>0</v>
+      </c>
+      <c r="L203" t="s">
+        <v>16</v>
+      </c>
+      <c r="M203" t="s">
+        <v>16</v>
+      </c>
+      <c r="N203">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O203">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>11724488</v>
+      </c>
+      <c r="B204">
+        <v>26176326</v>
+      </c>
+      <c r="C204" t="s">
+        <v>18</v>
+      </c>
+      <c r="D204">
+        <v>98.8</v>
+      </c>
+      <c r="E204" s="5">
+        <f t="shared" si="11"/>
+        <v>37.1</v>
+      </c>
+      <c r="F204">
+        <v>183</v>
+      </c>
+      <c r="G204">
+        <v>93</v>
+      </c>
+      <c r="H204">
+        <v>65</v>
+      </c>
+      <c r="I204">
+        <v>18</v>
+      </c>
+      <c r="J204">
+        <v>97</v>
+      </c>
+      <c r="K204" t="b">
+        <v>0</v>
+      </c>
+      <c r="L204" t="s">
+        <v>16</v>
+      </c>
+      <c r="M204" t="s">
+        <v>16</v>
+      </c>
+      <c r="N204">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O204">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>19373075</v>
+      </c>
+      <c r="B205">
+        <v>26192816</v>
+      </c>
+      <c r="C205" t="s">
+        <v>15</v>
+      </c>
+      <c r="D205">
+        <v>98.5</v>
+      </c>
+      <c r="E205" s="5">
+        <f t="shared" si="11"/>
+        <v>36.9</v>
+      </c>
+      <c r="F205">
+        <v>156</v>
+      </c>
+      <c r="G205">
+        <v>90</v>
+      </c>
+      <c r="H205">
+        <v>60</v>
+      </c>
+      <c r="I205">
+        <v>16</v>
+      </c>
+      <c r="J205">
+        <v>100</v>
+      </c>
+      <c r="K205" t="b">
+        <v>0</v>
+      </c>
+      <c r="L205" t="s">
+        <v>16</v>
+      </c>
+      <c r="M205" t="s">
+        <v>16</v>
+      </c>
+      <c r="N205">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O205">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>15406838</v>
+      </c>
+      <c r="B206">
+        <v>26220916</v>
+      </c>
+      <c r="C206" t="s">
+        <v>15</v>
+      </c>
+      <c r="D206">
+        <v>98.8</v>
+      </c>
+      <c r="E206" s="5">
+        <f t="shared" si="11"/>
+        <v>37.1</v>
+      </c>
+      <c r="F206">
+        <v>120</v>
+      </c>
+      <c r="G206">
+        <v>66</v>
+      </c>
+      <c r="H206">
+        <v>70</v>
+      </c>
+      <c r="I206">
+        <v>16</v>
+      </c>
+      <c r="J206">
+        <v>97</v>
+      </c>
+      <c r="K206" t="b">
+        <v>0</v>
+      </c>
+      <c r="L206" t="s">
+        <v>16</v>
+      </c>
+      <c r="M206" t="s">
+        <v>16</v>
+      </c>
+      <c r="N206">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O206">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>15591198</v>
+      </c>
+      <c r="B207">
+        <v>26307519</v>
+      </c>
+      <c r="C207" t="s">
+        <v>18</v>
+      </c>
+      <c r="D207" t="s">
+        <v>23</v>
+      </c>
+      <c r="E207" t="s">
+        <v>23</v>
+      </c>
+      <c r="F207" t="s">
+        <v>23</v>
+      </c>
+      <c r="G207" t="s">
+        <v>23</v>
+      </c>
+      <c r="H207" t="s">
+        <v>23</v>
+      </c>
+      <c r="I207" t="s">
+        <v>23</v>
+      </c>
+      <c r="J207" t="s">
+        <v>23</v>
+      </c>
+      <c r="K207" t="b">
+        <v>0</v>
+      </c>
+      <c r="L207" t="s">
+        <v>16</v>
+      </c>
+      <c r="M207" t="s">
+        <v>16</v>
+      </c>
+      <c r="N207" t="s">
+        <v>23</v>
+      </c>
+      <c r="O207" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>10504887</v>
+      </c>
+      <c r="B208">
+        <v>26475849</v>
+      </c>
+      <c r="C208" t="s">
+        <v>18</v>
+      </c>
+      <c r="D208">
+        <v>97.7</v>
+      </c>
+      <c r="E208" s="5">
+        <f t="shared" si="11"/>
+        <v>36.5</v>
+      </c>
+      <c r="F208">
+        <v>160</v>
+      </c>
+      <c r="G208">
+        <v>60</v>
+      </c>
+      <c r="H208">
+        <v>67</v>
+      </c>
+      <c r="I208">
+        <v>18</v>
+      </c>
+      <c r="J208">
+        <v>94</v>
+      </c>
+      <c r="K208" t="b">
+        <v>0</v>
+      </c>
+      <c r="L208" t="s">
+        <v>16</v>
+      </c>
+      <c r="M208" t="s">
+        <v>16</v>
+      </c>
+      <c r="N208">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O208">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>16166469</v>
+      </c>
+      <c r="B209">
+        <v>26727011</v>
+      </c>
+      <c r="C209" t="s">
+        <v>15</v>
+      </c>
+      <c r="D209" t="s">
+        <v>23</v>
+      </c>
+      <c r="E209" t="s">
+        <v>23</v>
+      </c>
+      <c r="F209" t="s">
+        <v>23</v>
+      </c>
+      <c r="G209" t="s">
+        <v>23</v>
+      </c>
+      <c r="H209" t="s">
+        <v>23</v>
+      </c>
+      <c r="I209" t="s">
+        <v>23</v>
+      </c>
+      <c r="J209" t="s">
+        <v>23</v>
+      </c>
+      <c r="K209" t="b">
+        <v>0</v>
+      </c>
+      <c r="L209" t="s">
+        <v>16</v>
+      </c>
+      <c r="M209" t="s">
+        <v>16</v>
+      </c>
+      <c r="N209" t="s">
+        <v>23</v>
+      </c>
+      <c r="O209" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>12716253</v>
+      </c>
+      <c r="B210">
+        <v>26793652</v>
+      </c>
+      <c r="C210" t="s">
+        <v>15</v>
+      </c>
+      <c r="D210" t="s">
+        <v>23</v>
+      </c>
+      <c r="E210" t="s">
+        <v>23</v>
+      </c>
+      <c r="F210" t="s">
+        <v>23</v>
+      </c>
+      <c r="G210" t="s">
+        <v>23</v>
+      </c>
+      <c r="H210" t="s">
+        <v>23</v>
+      </c>
+      <c r="I210" t="s">
+        <v>23</v>
+      </c>
+      <c r="J210" t="s">
+        <v>23</v>
+      </c>
+      <c r="K210" t="b">
+        <v>0</v>
+      </c>
+      <c r="L210" t="s">
+        <v>16</v>
+      </c>
+      <c r="M210" t="s">
+        <v>16</v>
+      </c>
+      <c r="N210" t="s">
+        <v>23</v>
+      </c>
+      <c r="O210" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>18699523</v>
+      </c>
+      <c r="B211">
+        <v>26875738</v>
+      </c>
+      <c r="C211" t="s">
+        <v>17</v>
+      </c>
+      <c r="D211">
+        <v>98.6</v>
+      </c>
+      <c r="E211" s="5">
+        <f t="shared" si="11"/>
+        <v>37</v>
+      </c>
+      <c r="F211">
+        <v>105</v>
+      </c>
+      <c r="G211">
+        <v>69</v>
+      </c>
+      <c r="H211">
+        <v>100</v>
+      </c>
+      <c r="I211">
+        <v>18</v>
+      </c>
+      <c r="J211">
+        <v>99</v>
+      </c>
+      <c r="K211" t="b">
+        <v>0</v>
+      </c>
+      <c r="L211" t="s">
+        <v>16</v>
+      </c>
+      <c r="M211" t="s">
+        <v>16</v>
+      </c>
+      <c r="N211">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O211">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>17466330</v>
+      </c>
+      <c r="B212">
+        <v>27023241</v>
+      </c>
+      <c r="C212" t="s">
+        <v>18</v>
+      </c>
+      <c r="D212">
+        <v>97.8</v>
+      </c>
+      <c r="E212" s="5">
+        <f t="shared" si="11"/>
+        <v>36.6</v>
+      </c>
+      <c r="F212">
+        <v>129</v>
+      </c>
+      <c r="G212">
+        <v>79</v>
+      </c>
+      <c r="H212">
+        <v>87</v>
+      </c>
+      <c r="I212">
+        <v>18</v>
+      </c>
+      <c r="J212">
+        <v>99</v>
+      </c>
+      <c r="K212" t="b">
+        <v>0</v>
+      </c>
+      <c r="L212" t="s">
+        <v>16</v>
+      </c>
+      <c r="M212" t="s">
+        <v>16</v>
+      </c>
+      <c r="N212">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O212">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>11869721</v>
+      </c>
+      <c r="B213">
+        <v>27127472</v>
+      </c>
+      <c r="C213" t="s">
+        <v>18</v>
+      </c>
+      <c r="D213">
+        <v>98.2</v>
+      </c>
+      <c r="E213" s="5">
+        <f t="shared" si="11"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F213">
+        <v>120</v>
+      </c>
+      <c r="G213">
+        <v>59</v>
+      </c>
+      <c r="H213">
+        <v>88</v>
+      </c>
+      <c r="I213">
+        <v>18</v>
+      </c>
+      <c r="J213">
+        <v>96</v>
+      </c>
+      <c r="K213" t="b">
+        <v>0</v>
+      </c>
+      <c r="L213" t="s">
+        <v>16</v>
+      </c>
+      <c r="M213" t="s">
+        <v>16</v>
+      </c>
+      <c r="N213">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O213">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>19997367</v>
+      </c>
+      <c r="B214">
+        <v>27185507</v>
+      </c>
+      <c r="C214" t="s">
+        <v>15</v>
+      </c>
+      <c r="D214">
+        <v>97.6</v>
+      </c>
+      <c r="E214" s="5">
+        <f t="shared" si="11"/>
+        <v>36.4</v>
+      </c>
+      <c r="F214">
+        <v>105</v>
+      </c>
+      <c r="G214">
+        <v>53</v>
+      </c>
+      <c r="H214">
+        <v>90</v>
+      </c>
+      <c r="I214">
+        <v>19</v>
+      </c>
+      <c r="J214">
+        <v>99</v>
+      </c>
+      <c r="K214" t="b">
+        <v>0</v>
+      </c>
+      <c r="L214" t="s">
+        <v>16</v>
+      </c>
+      <c r="M214" t="s">
+        <v>16</v>
+      </c>
+      <c r="N214">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O214">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>14522445</v>
+      </c>
+      <c r="B215">
+        <v>27299730</v>
+      </c>
+      <c r="C215" t="s">
+        <v>18</v>
+      </c>
+      <c r="D215">
+        <v>97.7</v>
+      </c>
+      <c r="E215" s="5">
+        <f t="shared" si="11"/>
+        <v>36.5</v>
+      </c>
+      <c r="F215">
+        <v>149</v>
+      </c>
+      <c r="G215">
+        <v>81</v>
+      </c>
+      <c r="H215">
+        <v>65</v>
+      </c>
+      <c r="I215">
+        <v>18</v>
+      </c>
+      <c r="J215">
+        <v>95</v>
+      </c>
+      <c r="K215" t="b">
+        <v>0</v>
+      </c>
+      <c r="L215" t="s">
+        <v>16</v>
+      </c>
+      <c r="M215" t="s">
+        <v>16</v>
+      </c>
+      <c r="N215">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O215">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>14928745</v>
+      </c>
+      <c r="B216">
+        <v>27332967</v>
+      </c>
+      <c r="C216" t="s">
+        <v>15</v>
+      </c>
+      <c r="D216" t="s">
+        <v>23</v>
+      </c>
+      <c r="E216" t="s">
+        <v>23</v>
+      </c>
+      <c r="F216" t="s">
+        <v>23</v>
+      </c>
+      <c r="G216" t="s">
+        <v>23</v>
+      </c>
+      <c r="H216" t="s">
+        <v>23</v>
+      </c>
+      <c r="I216" t="s">
+        <v>23</v>
+      </c>
+      <c r="J216" t="s">
+        <v>23</v>
+      </c>
+      <c r="K216" t="b">
+        <v>0</v>
+      </c>
+      <c r="L216" t="s">
+        <v>16</v>
+      </c>
+      <c r="M216" t="s">
+        <v>16</v>
+      </c>
+      <c r="N216" t="s">
+        <v>23</v>
+      </c>
+      <c r="O216" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>11181460</v>
+      </c>
+      <c r="B217">
+        <v>27455163</v>
+      </c>
+      <c r="C217" t="s">
+        <v>15</v>
+      </c>
+      <c r="D217">
+        <v>101.6</v>
+      </c>
+      <c r="E217" s="5">
+        <f t="shared" si="11"/>
+        <v>38.700000000000003</v>
+      </c>
+      <c r="F217">
+        <v>188</v>
+      </c>
+      <c r="G217">
+        <v>62</v>
+      </c>
+      <c r="H217">
+        <v>80</v>
+      </c>
+      <c r="I217">
+        <v>27</v>
+      </c>
+      <c r="J217">
+        <v>100</v>
+      </c>
+      <c r="K217" t="b">
+        <v>1</v>
+      </c>
+      <c r="L217" t="s">
+        <v>16</v>
+      </c>
+      <c r="M217" t="s">
+        <v>16</v>
+      </c>
+      <c r="N217">
+        <f t="shared" si="12"/>
+        <v>4</v>
+      </c>
+      <c r="O217">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>13031024</v>
+      </c>
+      <c r="B218">
+        <v>27475024</v>
+      </c>
+      <c r="C218" t="s">
+        <v>15</v>
+      </c>
+      <c r="D218">
+        <v>98</v>
+      </c>
+      <c r="E218" s="5">
+        <f t="shared" si="11"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F218">
+        <v>175</v>
+      </c>
+      <c r="G218">
+        <v>88</v>
+      </c>
+      <c r="H218">
+        <v>74</v>
+      </c>
+      <c r="I218">
+        <v>18</v>
+      </c>
+      <c r="J218">
+        <v>97</v>
+      </c>
+      <c r="K218" t="b">
+        <v>0</v>
+      </c>
+      <c r="L218" t="s">
+        <v>16</v>
+      </c>
+      <c r="M218" t="s">
+        <v>16</v>
+      </c>
+      <c r="N218">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="O218">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>17385589</v>
+      </c>
+      <c r="B219">
+        <v>27500126</v>
+      </c>
+      <c r="C219" t="s">
+        <v>15</v>
+      </c>
+      <c r="D219">
+        <v>97.8</v>
+      </c>
+      <c r="E219" s="5">
+        <f t="shared" si="11"/>
+        <v>36.6</v>
+      </c>
+      <c r="F219">
+        <v>139</v>
+      </c>
+      <c r="G219">
+        <v>90</v>
+      </c>
+      <c r="H219">
+        <v>58</v>
+      </c>
+      <c r="I219">
+        <v>14</v>
+      </c>
+      <c r="J219">
+        <v>99</v>
+      </c>
+      <c r="K219" t="b">
+        <v>0</v>
+      </c>
+      <c r="L219" t="s">
+        <v>16</v>
+      </c>
+      <c r="M219" t="s">
+        <v>16</v>
+      </c>
+      <c r="N219">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="O219">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>11894825</v>
+      </c>
+      <c r="B220">
+        <v>27594672</v>
+      </c>
+      <c r="C220" t="s">
+        <v>15</v>
+      </c>
+      <c r="D220">
+        <v>98.2</v>
+      </c>
+      <c r="E220" s="5">
+        <f t="shared" si="11"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F220">
+        <v>109</v>
+      </c>
+      <c r="G220">
+        <v>76</v>
+      </c>
+      <c r="H220">
+        <v>99</v>
+      </c>
+      <c r="I220">
+        <v>21</v>
+      </c>
+      <c r="J220">
+        <v>97</v>
+      </c>
+      <c r="K220" t="b">
+        <v>1</v>
+      </c>
+      <c r="L220" t="s">
+        <v>16</v>
+      </c>
+      <c r="M220" t="s">
+        <v>16</v>
+      </c>
+      <c r="N220">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="O220">
+        <f t="shared" si="13"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>12618901</v>
+      </c>
+      <c r="B221">
+        <v>27723711</v>
+      </c>
+      <c r="C221" t="s">
+        <v>15</v>
+      </c>
+      <c r="D221">
+        <v>99.5</v>
+      </c>
+      <c r="E221" s="5">
+        <f t="shared" ref="E221:E284" si="14">ROUND((D221-32)*(5/9),1)</f>
+        <v>37.5</v>
+      </c>
+      <c r="F221">
+        <v>138</v>
+      </c>
+      <c r="G221">
+        <v>79</v>
+      </c>
+      <c r="H221">
+        <v>94</v>
+      </c>
+      <c r="I221">
+        <v>16</v>
+      </c>
+      <c r="J221">
+        <v>100</v>
+      </c>
+      <c r="K221" t="b">
+        <v>0</v>
+      </c>
+      <c r="L221" t="s">
+        <v>16</v>
+      </c>
+      <c r="M221" t="s">
+        <v>16</v>
+      </c>
+      <c r="N221">
+        <f t="shared" ref="N221:N284" si="15">IF(I221&lt;9,2,IF(I221&lt;=14,0,IF(I221&lt;=20,1,IF(I221&lt;=29,2,3))))+IF(H221&lt;=40,2,IF(H221&lt;=50,1,IF(H221&lt;=100,0,IF(H221&lt;=110,1,IF(H221&lt;=129,2,3)))))+IF(F221&lt;=70,3,IF(F221&lt;=80,2,IF(F221&lt;=100,1,IF(F221&lt;200,0,IF(F221&gt;=200,2,0)))))+IF(E221&lt;35,2,IF(E221&lt;=38.4,0,2))+IF(M221="Alert",0,IF(M221="Voice",1,IF(M221="Pain",2,IF(M221="Unresponsive",3,0))))</f>
+        <v>1</v>
+      </c>
+      <c r="O221">
+        <f t="shared" ref="O221:O284" si="16">IF(I221&lt;=8,3,IF(I221&lt;=11,1,IF(I221&lt;=20,0,IF(I221&lt;=24,2,3))))
++IF(J221&lt;=91,3,IF(J221&lt;=93,2,IF(J221&lt;=95,1,0)))
++IF(K221=TRUE,2,0)
++IF(F221&lt;=90,3,IF(F221&lt;=100,2,IF(F221&lt;=110,1,IF(F221&lt;=219,0,3))))
++IF(H221&lt;=40,3,IF(H221&lt;=50,1,IF(H221&lt;=90,0,IF(H221&lt;=110,1,IF(H221&lt;=130,2,3)))))
++IF(M221="Alert",0,3)
++IF(E221&lt;=35,3,IF(E221&lt;=36,1,IF(E221&lt;=38,0,IF(E221&lt;=39,1,2))))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>14651424</v>
+      </c>
+      <c r="B222">
+        <v>27825481</v>
+      </c>
+      <c r="C222" t="s">
+        <v>17</v>
+      </c>
+      <c r="D222">
+        <v>98.1</v>
+      </c>
+      <c r="E222" s="5">
+        <f t="shared" si="14"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F222">
+        <v>130</v>
+      </c>
+      <c r="G222">
+        <v>87</v>
+      </c>
+      <c r="H222">
+        <v>89</v>
+      </c>
+      <c r="I222">
+        <v>18</v>
+      </c>
+      <c r="J222">
+        <v>99</v>
+      </c>
+      <c r="K222" t="b">
+        <v>0</v>
+      </c>
+      <c r="L222" t="s">
+        <v>16</v>
+      </c>
+      <c r="M222" t="s">
+        <v>16</v>
+      </c>
+      <c r="N222">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O222">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>14178945</v>
+      </c>
+      <c r="B223">
+        <v>27938104</v>
+      </c>
+      <c r="C223" t="s">
+        <v>15</v>
+      </c>
+      <c r="D223">
+        <v>98.3</v>
+      </c>
+      <c r="E223" s="5">
+        <f t="shared" si="14"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F223">
+        <v>166</v>
+      </c>
+      <c r="G223">
+        <v>96</v>
+      </c>
+      <c r="H223">
+        <v>78</v>
+      </c>
+      <c r="I223">
+        <v>18</v>
+      </c>
+      <c r="J223">
+        <v>96</v>
+      </c>
+      <c r="K223" t="b">
+        <v>0</v>
+      </c>
+      <c r="L223" t="s">
+        <v>16</v>
+      </c>
+      <c r="M223" t="s">
+        <v>16</v>
+      </c>
+      <c r="N223">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O223">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>11790586</v>
+      </c>
+      <c r="B224">
+        <v>28115593</v>
+      </c>
+      <c r="C224" t="s">
+        <v>18</v>
+      </c>
+      <c r="D224">
+        <v>98.3</v>
+      </c>
+      <c r="E224" s="5">
+        <f t="shared" si="14"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F224">
+        <v>151</v>
+      </c>
+      <c r="G224">
+        <v>79</v>
+      </c>
+      <c r="H224">
+        <v>81</v>
+      </c>
+      <c r="I224">
+        <v>18</v>
+      </c>
+      <c r="J224">
+        <v>98</v>
+      </c>
+      <c r="K224" t="b">
+        <v>0</v>
+      </c>
+      <c r="L224" t="s">
+        <v>16</v>
+      </c>
+      <c r="M224" t="s">
+        <v>16</v>
+      </c>
+      <c r="N224">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O224">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>19828866</v>
+      </c>
+      <c r="B225">
+        <v>28141359</v>
+      </c>
+      <c r="C225" t="s">
+        <v>15</v>
+      </c>
+      <c r="D225">
+        <v>98.5</v>
+      </c>
+      <c r="E225" s="5">
+        <f t="shared" si="14"/>
+        <v>36.9</v>
+      </c>
+      <c r="F225">
+        <v>122</v>
+      </c>
+      <c r="G225">
+        <v>65</v>
+      </c>
+      <c r="H225">
+        <v>92</v>
+      </c>
+      <c r="I225">
+        <v>20</v>
+      </c>
+      <c r="J225">
+        <v>98</v>
+      </c>
+      <c r="K225" t="b">
+        <v>1</v>
+      </c>
+      <c r="L225" t="s">
+        <v>22</v>
+      </c>
+      <c r="M225" t="s">
+        <v>22</v>
+      </c>
+      <c r="N225">
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
+      <c r="O225">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>14095400</v>
+      </c>
+      <c r="B226">
+        <v>28165466</v>
+      </c>
+      <c r="C226" t="s">
+        <v>15</v>
+      </c>
+      <c r="D226">
+        <v>98.4</v>
+      </c>
+      <c r="E226" s="5">
+        <f t="shared" si="14"/>
+        <v>36.9</v>
+      </c>
+      <c r="F226">
+        <v>144</v>
+      </c>
+      <c r="G226">
+        <v>84</v>
+      </c>
+      <c r="H226">
+        <v>94</v>
+      </c>
+      <c r="I226">
+        <v>16</v>
+      </c>
+      <c r="J226">
+        <v>97</v>
+      </c>
+      <c r="K226" t="b">
+        <v>0</v>
+      </c>
+      <c r="L226" t="s">
+        <v>16</v>
+      </c>
+      <c r="M226" t="s">
+        <v>16</v>
+      </c>
+      <c r="N226">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O226">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>14690121</v>
+      </c>
+      <c r="B227">
+        <v>28173231</v>
+      </c>
+      <c r="C227" t="s">
+        <v>15</v>
+      </c>
+      <c r="D227">
+        <v>98.3</v>
+      </c>
+      <c r="E227" s="5">
+        <f t="shared" si="14"/>
+        <v>36.799999999999997</v>
+      </c>
+      <c r="F227">
+        <v>120</v>
+      </c>
+      <c r="G227">
+        <v>80</v>
+      </c>
+      <c r="H227">
+        <v>64</v>
+      </c>
+      <c r="I227">
+        <v>18</v>
+      </c>
+      <c r="J227">
+        <v>100</v>
+      </c>
+      <c r="K227" t="b">
+        <v>0</v>
+      </c>
+      <c r="L227" t="s">
+        <v>16</v>
+      </c>
+      <c r="M227" t="s">
+        <v>16</v>
+      </c>
+      <c r="N227">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O227">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>17494298</v>
+      </c>
+      <c r="B228">
+        <v>28486832</v>
+      </c>
+      <c r="C228" t="s">
+        <v>15</v>
+      </c>
+      <c r="D228">
+        <v>98.4</v>
+      </c>
+      <c r="E228" s="5">
+        <f t="shared" si="14"/>
+        <v>36.9</v>
+      </c>
+      <c r="F228">
+        <v>144</v>
+      </c>
+      <c r="G228">
+        <v>51</v>
+      </c>
+      <c r="H228">
+        <v>63</v>
+      </c>
+      <c r="I228">
+        <v>20</v>
+      </c>
+      <c r="J228">
+        <v>100</v>
+      </c>
+      <c r="K228" t="b">
+        <v>0</v>
+      </c>
+      <c r="L228" t="s">
+        <v>16</v>
+      </c>
+      <c r="M228" t="s">
+        <v>16</v>
+      </c>
+      <c r="N228">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O228">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>19877772</v>
+      </c>
+      <c r="B229">
+        <v>28508244</v>
+      </c>
+      <c r="C229" t="s">
+        <v>15</v>
+      </c>
+      <c r="D229" s="13">
+        <v>98</v>
+      </c>
+      <c r="E229" s="5">
+        <f t="shared" si="14"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F229" s="12">
+        <v>115</v>
+      </c>
+      <c r="G229" s="12">
+        <v>75</v>
+      </c>
+      <c r="H229" s="12">
+        <v>67</v>
+      </c>
+      <c r="I229" t="s">
+        <v>23</v>
+      </c>
+      <c r="J229">
+        <v>100</v>
+      </c>
+      <c r="K229" t="b">
+        <v>0</v>
+      </c>
+      <c r="L229" t="s">
+        <v>16</v>
+      </c>
+      <c r="M229" t="s">
+        <v>16</v>
+      </c>
+      <c r="N229" t="s">
+        <v>23</v>
+      </c>
+      <c r="O229" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>14892207</v>
+      </c>
+      <c r="B230">
+        <v>28515120</v>
+      </c>
+      <c r="C230" t="s">
+        <v>15</v>
+      </c>
+      <c r="D230" t="s">
+        <v>23</v>
+      </c>
+      <c r="E230" t="s">
+        <v>23</v>
+      </c>
+      <c r="F230" s="12">
+        <v>224</v>
+      </c>
+      <c r="G230" s="12">
+        <v>140</v>
+      </c>
+      <c r="H230" t="s">
+        <v>23</v>
+      </c>
+      <c r="I230" t="s">
+        <v>23</v>
+      </c>
+      <c r="J230" t="s">
+        <v>23</v>
+      </c>
+      <c r="K230" t="b">
+        <v>0</v>
+      </c>
+      <c r="L230" t="s">
+        <v>16</v>
+      </c>
+      <c r="M230" t="s">
+        <v>16</v>
+      </c>
+      <c r="N230" t="s">
+        <v>23</v>
+      </c>
+      <c r="O230" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>12432052</v>
+      </c>
+      <c r="B231">
+        <v>28578360</v>
+      </c>
+      <c r="C231" t="s">
+        <v>18</v>
+      </c>
+      <c r="D231">
+        <v>97</v>
+      </c>
+      <c r="E231" s="5">
+        <f t="shared" si="14"/>
+        <v>36.1</v>
+      </c>
+      <c r="F231" s="12">
+        <v>105</v>
+      </c>
+      <c r="G231" s="12">
+        <v>50</v>
+      </c>
+      <c r="H231" s="12">
+        <v>77</v>
+      </c>
+      <c r="I231" s="12">
+        <v>18</v>
+      </c>
+      <c r="J231" s="12">
+        <v>98</v>
+      </c>
+      <c r="K231" t="b">
+        <v>0</v>
+      </c>
+      <c r="L231" t="s">
+        <v>16</v>
+      </c>
+      <c r="M231" t="s">
+        <v>16</v>
+      </c>
+      <c r="N231">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O231">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>13684955</v>
+      </c>
+      <c r="B232">
+        <v>28784662</v>
+      </c>
+      <c r="C232" t="s">
+        <v>15</v>
+      </c>
+      <c r="D232" t="s">
+        <v>23</v>
+      </c>
+      <c r="E232" t="s">
+        <v>23</v>
+      </c>
+      <c r="F232" s="12">
+        <v>150</v>
+      </c>
+      <c r="G232" s="12">
+        <v>75</v>
+      </c>
+      <c r="H232" t="s">
+        <v>23</v>
+      </c>
+      <c r="I232" t="s">
+        <v>23</v>
+      </c>
+      <c r="J232" t="s">
+        <v>23</v>
+      </c>
+      <c r="K232" t="b">
+        <v>0</v>
+      </c>
+      <c r="L232" t="s">
+        <v>16</v>
+      </c>
+      <c r="M232" t="s">
+        <v>16</v>
+      </c>
+      <c r="N232" t="s">
+        <v>23</v>
+      </c>
+      <c r="O232" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>16528927</v>
+      </c>
+      <c r="B233">
+        <v>28989828</v>
+      </c>
+      <c r="C233" t="s">
+        <v>17</v>
+      </c>
+      <c r="D233" t="s">
+        <v>23</v>
+      </c>
+      <c r="E233" t="s">
+        <v>23</v>
+      </c>
+      <c r="F233" t="s">
+        <v>23</v>
+      </c>
+      <c r="G233" t="s">
+        <v>23</v>
+      </c>
+      <c r="H233" t="s">
+        <v>23</v>
+      </c>
+      <c r="I233" t="s">
+        <v>23</v>
+      </c>
+      <c r="J233" t="s">
+        <v>23</v>
+      </c>
+      <c r="K233" t="b">
+        <v>1</v>
+      </c>
+      <c r="L233" t="s">
+        <v>20</v>
+      </c>
+      <c r="M233" t="s">
+        <v>20</v>
+      </c>
+      <c r="N233" t="s">
+        <v>23</v>
+      </c>
+      <c r="O233" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>18004615</v>
+      </c>
+      <c r="B234">
+        <v>29199167</v>
+      </c>
+      <c r="C234" t="s">
+        <v>17</v>
+      </c>
+      <c r="D234">
+        <v>98</v>
+      </c>
+      <c r="E234" s="5">
+        <f t="shared" si="14"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F234" s="12">
+        <v>117</v>
+      </c>
+      <c r="G234" s="12">
+        <v>69</v>
+      </c>
+      <c r="H234" s="12">
+        <v>58</v>
+      </c>
+      <c r="I234" s="12">
+        <v>18</v>
+      </c>
+      <c r="J234" s="12">
+        <v>98</v>
+      </c>
+      <c r="K234" t="b">
+        <v>0</v>
+      </c>
+      <c r="L234" t="s">
+        <v>16</v>
+      </c>
+      <c r="M234" t="s">
+        <v>16</v>
+      </c>
+      <c r="N234">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O234">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>10707907</v>
+      </c>
+      <c r="B235">
+        <v>29294557</v>
+      </c>
+      <c r="C235" t="s">
+        <v>17</v>
+      </c>
+      <c r="D235" t="s">
+        <v>23</v>
+      </c>
+      <c r="E235" t="s">
+        <v>23</v>
+      </c>
+      <c r="F235" t="s">
+        <v>23</v>
+      </c>
+      <c r="G235" t="s">
+        <v>23</v>
+      </c>
+      <c r="H235" t="s">
+        <v>23</v>
+      </c>
+      <c r="I235" t="s">
+        <v>23</v>
+      </c>
+      <c r="J235" t="s">
+        <v>23</v>
+      </c>
+      <c r="K235" t="b">
+        <v>1</v>
+      </c>
+      <c r="L235" t="s">
+        <v>21</v>
+      </c>
+      <c r="M235" t="s">
+        <v>21</v>
+      </c>
+      <c r="N235" t="s">
+        <v>23</v>
+      </c>
+      <c r="O235" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>18530734</v>
+      </c>
+      <c r="B236">
+        <v>29703081</v>
+      </c>
+      <c r="C236" t="s">
+        <v>15</v>
+      </c>
+      <c r="D236">
+        <v>98.1</v>
+      </c>
+      <c r="E236" s="5">
+        <f t="shared" si="14"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F236" s="12">
+        <v>154</v>
+      </c>
+      <c r="G236" s="12">
+        <v>82</v>
+      </c>
+      <c r="H236" s="12">
+        <v>72</v>
+      </c>
+      <c r="I236" s="12">
+        <v>16</v>
+      </c>
+      <c r="J236" s="12">
+        <v>99</v>
+      </c>
+      <c r="K236" t="b">
+        <v>0</v>
+      </c>
+      <c r="L236" t="s">
+        <v>16</v>
+      </c>
+      <c r="M236" t="s">
+        <v>16</v>
+      </c>
+      <c r="N236">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O236">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>17585916</v>
+      </c>
+      <c r="B237">
+        <v>29817669</v>
+      </c>
+      <c r="C237" t="s">
+        <v>17</v>
+      </c>
+      <c r="D237">
+        <v>99.2</v>
+      </c>
+      <c r="E237" s="5">
+        <f t="shared" si="14"/>
+        <v>37.299999999999997</v>
+      </c>
+      <c r="F237" s="12">
+        <v>106</v>
+      </c>
+      <c r="G237" s="12">
+        <v>88</v>
+      </c>
+      <c r="H237" s="12">
+        <v>130</v>
+      </c>
+      <c r="I237" s="12">
+        <v>18</v>
+      </c>
+      <c r="J237" s="12">
+        <v>92</v>
+      </c>
+      <c r="K237" t="b">
+        <v>0</v>
+      </c>
+      <c r="L237" t="s">
+        <v>16</v>
+      </c>
+      <c r="M237" t="s">
+        <v>16</v>
+      </c>
+      <c r="N237">
+        <f t="shared" si="15"/>
+        <v>4</v>
+      </c>
+      <c r="O237">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>11875369</v>
+      </c>
+      <c r="B238">
+        <v>29825229</v>
+      </c>
+      <c r="C238" t="s">
+        <v>15</v>
+      </c>
+      <c r="D238">
+        <v>97.8</v>
+      </c>
+      <c r="E238" s="5">
+        <f t="shared" si="14"/>
+        <v>36.6</v>
+      </c>
+      <c r="F238" s="12">
+        <v>133</v>
+      </c>
+      <c r="G238" s="12">
+        <v>46</v>
+      </c>
+      <c r="H238" s="12">
+        <v>64</v>
+      </c>
+      <c r="I238" s="12">
+        <v>14</v>
+      </c>
+      <c r="J238" s="12">
+        <v>96</v>
+      </c>
+      <c r="K238" t="b">
+        <v>0</v>
+      </c>
+      <c r="L238" t="s">
+        <v>16</v>
+      </c>
+      <c r="M238" t="s">
+        <v>16</v>
+      </c>
+      <c r="N238">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O238">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>16029687</v>
+      </c>
+      <c r="B239">
+        <v>29845828</v>
+      </c>
+      <c r="C239" t="s">
+        <v>15</v>
+      </c>
+      <c r="D239">
+        <v>98</v>
+      </c>
+      <c r="E239" s="5">
+        <f t="shared" si="14"/>
+        <v>36.700000000000003</v>
+      </c>
+      <c r="F239" s="12">
+        <v>128</v>
+      </c>
+      <c r="G239" s="12">
+        <v>102</v>
+      </c>
+      <c r="H239" s="12">
+        <v>80</v>
+      </c>
+      <c r="I239" s="12">
+        <v>12</v>
+      </c>
+      <c r="J239" s="12">
+        <v>97</v>
+      </c>
+      <c r="K239" t="b">
+        <v>0</v>
+      </c>
+      <c r="L239" t="s">
+        <v>16</v>
+      </c>
+      <c r="M239" t="s">
+        <v>16</v>
+      </c>
+      <c r="N239">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="O239">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>15938562</v>
+      </c>
+      <c r="B240">
+        <v>29882851</v>
+      </c>
+      <c r="C240" t="s">
+        <v>15</v>
+      </c>
+      <c r="D240">
+        <v>97.7</v>
+      </c>
+      <c r="E240" s="5">
+        <f t="shared" si="14"/>
+        <v>36.5</v>
+      </c>
+      <c r="F240" s="12">
+        <v>143</v>
+      </c>
+      <c r="G240" s="12">
+        <v>95</v>
+      </c>
+      <c r="H240" s="12">
+        <v>79</v>
+      </c>
+      <c r="I240" s="12">
+        <v>16</v>
+      </c>
+      <c r="J240" s="12">
+        <v>98</v>
+      </c>
+      <c r="K240" t="b">
+        <v>0</v>
+      </c>
+      <c r="L240" t="s">
+        <v>16</v>
+      </c>
+      <c r="M240" t="s">
+        <v>16</v>
+      </c>
+      <c r="N240">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O240">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>18535322</v>
+      </c>
+      <c r="B241">
+        <v>29991935</v>
+      </c>
+      <c r="C241" t="s">
+        <v>17</v>
+      </c>
+      <c r="D241">
+        <v>97.7</v>
+      </c>
+      <c r="E241" s="5">
+        <f t="shared" si="14"/>
+        <v>36.5</v>
+      </c>
+      <c r="F241" s="12">
+        <v>143</v>
+      </c>
+      <c r="G241" s="12">
+        <v>80</v>
+      </c>
+      <c r="H241" s="12">
+        <v>80</v>
+      </c>
+      <c r="I241" s="12">
+        <v>18</v>
+      </c>
+      <c r="J241" s="12">
+        <v>96</v>
+      </c>
+      <c r="K241" t="b">
+        <v>0</v>
+      </c>
+      <c r="L241" t="s">
+        <v>16</v>
+      </c>
+      <c r="M241" t="s">
+        <v>16</v>
+      </c>
+      <c r="N241">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="O241">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E242" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K242" t="b">
+        <v>0</v>
+      </c>
+      <c r="L242" t="s">
+        <v>16</v>
+      </c>
+      <c r="M242" t="s">
+        <v>16</v>
+      </c>
+      <c r="N242">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O242">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E243" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K243" t="b">
+        <v>0</v>
+      </c>
+      <c r="L243" t="s">
+        <v>16</v>
+      </c>
+      <c r="M243" t="s">
+        <v>16</v>
+      </c>
+      <c r="N243">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O243">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E244" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K244" t="b">
+        <v>0</v>
+      </c>
+      <c r="L244" t="s">
+        <v>16</v>
+      </c>
+      <c r="M244" t="s">
+        <v>16</v>
+      </c>
+      <c r="N244">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O244">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E245" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K245" t="b">
+        <v>0</v>
+      </c>
+      <c r="L245" t="s">
+        <v>16</v>
+      </c>
+      <c r="M245" t="s">
+        <v>16</v>
+      </c>
+      <c r="N245">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O245">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E246" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K246" t="b">
+        <v>0</v>
+      </c>
+      <c r="L246" t="s">
+        <v>16</v>
+      </c>
+      <c r="M246" t="s">
+        <v>16</v>
+      </c>
+      <c r="N246">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O246">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E247" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K247" t="b">
+        <v>0</v>
+      </c>
+      <c r="L247" t="s">
+        <v>16</v>
+      </c>
+      <c r="M247" t="s">
+        <v>16</v>
+      </c>
+      <c r="N247">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O247">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E248" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K248" t="b">
+        <v>0</v>
+      </c>
+      <c r="L248" t="s">
+        <v>16</v>
+      </c>
+      <c r="M248" t="s">
+        <v>16</v>
+      </c>
+      <c r="N248">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O248">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E249" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K249" t="b">
+        <v>0</v>
+      </c>
+      <c r="L249" t="s">
+        <v>16</v>
+      </c>
+      <c r="M249" t="s">
+        <v>16</v>
+      </c>
+      <c r="N249">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O249">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E250" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K250" t="b">
+        <v>0</v>
+      </c>
+      <c r="L250" t="s">
+        <v>16</v>
+      </c>
+      <c r="M250" t="s">
+        <v>16</v>
+      </c>
+      <c r="N250">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O250">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E251" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K251" t="b">
+        <v>0</v>
+      </c>
+      <c r="L251" t="s">
+        <v>16</v>
+      </c>
+      <c r="M251" t="s">
+        <v>16</v>
+      </c>
+      <c r="N251">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O251">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E252" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K252" t="b">
+        <v>0</v>
+      </c>
+      <c r="L252" t="s">
+        <v>16</v>
+      </c>
+      <c r="M252" t="s">
+        <v>16</v>
+      </c>
+      <c r="N252">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O252">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E253" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K253" t="b">
+        <v>0</v>
+      </c>
+      <c r="L253" t="s">
+        <v>16</v>
+      </c>
+      <c r="M253" t="s">
+        <v>16</v>
+      </c>
+      <c r="N253">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O253">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E254" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K254" t="b">
+        <v>0</v>
+      </c>
+      <c r="L254" t="s">
+        <v>16</v>
+      </c>
+      <c r="M254" t="s">
+        <v>16</v>
+      </c>
+      <c r="N254">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O254">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E255" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K255" t="b">
+        <v>0</v>
+      </c>
+      <c r="L255" t="s">
+        <v>16</v>
+      </c>
+      <c r="M255" t="s">
+        <v>16</v>
+      </c>
+      <c r="N255">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O255">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="E256" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K256" t="b">
+        <v>0</v>
+      </c>
+      <c r="L256" t="s">
+        <v>16</v>
+      </c>
+      <c r="M256" t="s">
+        <v>16</v>
+      </c>
+      <c r="N256">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O256">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E257" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K257" t="b">
+        <v>0</v>
+      </c>
+      <c r="L257" t="s">
+        <v>16</v>
+      </c>
+      <c r="M257" t="s">
+        <v>16</v>
+      </c>
+      <c r="N257">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O257">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="258" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E258" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K258" t="b">
+        <v>0</v>
+      </c>
+      <c r="L258" t="s">
+        <v>16</v>
+      </c>
+      <c r="M258" t="s">
+        <v>16</v>
+      </c>
+      <c r="N258">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O258">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="259" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E259" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K259" t="b">
+        <v>0</v>
+      </c>
+      <c r="L259" t="s">
+        <v>16</v>
+      </c>
+      <c r="M259" t="s">
+        <v>16</v>
+      </c>
+      <c r="N259">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O259">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E260" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K260" t="b">
+        <v>0</v>
+      </c>
+      <c r="L260" t="s">
+        <v>16</v>
+      </c>
+      <c r="M260" t="s">
+        <v>16</v>
+      </c>
+      <c r="N260">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O260">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="261" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E261" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K261" t="b">
+        <v>0</v>
+      </c>
+      <c r="L261" t="s">
+        <v>16</v>
+      </c>
+      <c r="M261" t="s">
+        <v>16</v>
+      </c>
+      <c r="N261">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O261">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E262" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K262" t="b">
+        <v>0</v>
+      </c>
+      <c r="L262" t="s">
+        <v>16</v>
+      </c>
+      <c r="M262" t="s">
+        <v>16</v>
+      </c>
+      <c r="N262">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O262">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="263" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E263" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K263" t="b">
+        <v>0</v>
+      </c>
+      <c r="L263" t="s">
+        <v>16</v>
+      </c>
+      <c r="M263" t="s">
+        <v>16</v>
+      </c>
+      <c r="N263">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O263">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E264" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K264" t="b">
+        <v>0</v>
+      </c>
+      <c r="L264" t="s">
+        <v>16</v>
+      </c>
+      <c r="M264" t="s">
+        <v>16</v>
+      </c>
+      <c r="N264">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O264">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="265" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E265" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K265" t="b">
+        <v>0</v>
+      </c>
+      <c r="L265" t="s">
+        <v>16</v>
+      </c>
+      <c r="M265" t="s">
+        <v>16</v>
+      </c>
+      <c r="N265">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O265">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="266" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E266" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K266" t="b">
+        <v>0</v>
+      </c>
+      <c r="L266" t="s">
+        <v>16</v>
+      </c>
+      <c r="M266" t="s">
+        <v>16</v>
+      </c>
+      <c r="N266">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O266">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="267" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E267" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K267" t="b">
+        <v>0</v>
+      </c>
+      <c r="L267" t="s">
+        <v>16</v>
+      </c>
+      <c r="M267" t="s">
+        <v>16</v>
+      </c>
+      <c r="N267">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O267">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="268" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E268" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K268" t="b">
+        <v>0</v>
+      </c>
+      <c r="L268" t="s">
+        <v>16</v>
+      </c>
+      <c r="M268" t="s">
+        <v>16</v>
+      </c>
+      <c r="N268">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O268">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="269" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E269" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K269" t="b">
+        <v>0</v>
+      </c>
+      <c r="L269" t="s">
+        <v>16</v>
+      </c>
+      <c r="M269" t="s">
+        <v>16</v>
+      </c>
+      <c r="N269">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O269">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="270" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E270" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K270" t="b">
+        <v>0</v>
+      </c>
+      <c r="L270" t="s">
+        <v>16</v>
+      </c>
+      <c r="M270" t="s">
+        <v>16</v>
+      </c>
+      <c r="N270">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O270">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="271" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E271" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K271" t="b">
+        <v>0</v>
+      </c>
+      <c r="L271" t="s">
+        <v>16</v>
+      </c>
+      <c r="M271" t="s">
+        <v>16</v>
+      </c>
+      <c r="N271">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O271">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="272" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E272" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K272" t="b">
+        <v>0</v>
+      </c>
+      <c r="L272" t="s">
+        <v>16</v>
+      </c>
+      <c r="M272" t="s">
+        <v>16</v>
+      </c>
+      <c r="N272">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O272">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="273" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E273" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K273" t="b">
+        <v>0</v>
+      </c>
+      <c r="L273" t="s">
+        <v>16</v>
+      </c>
+      <c r="M273" t="s">
+        <v>16</v>
+      </c>
+      <c r="N273">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O273">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="274" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E274" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K274" t="b">
+        <v>0</v>
+      </c>
+      <c r="L274" t="s">
+        <v>16</v>
+      </c>
+      <c r="M274" t="s">
+        <v>16</v>
+      </c>
+      <c r="N274">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O274">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="275" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E275" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K275" t="b">
+        <v>0</v>
+      </c>
+      <c r="L275" t="s">
+        <v>16</v>
+      </c>
+      <c r="M275" t="s">
+        <v>16</v>
+      </c>
+      <c r="N275">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O275">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="276" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E276" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K276" t="b">
+        <v>0</v>
+      </c>
+      <c r="L276" t="s">
+        <v>16</v>
+      </c>
+      <c r="M276" t="s">
+        <v>16</v>
+      </c>
+      <c r="N276">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O276">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="277" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E277" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K277" t="b">
+        <v>0</v>
+      </c>
+      <c r="L277" t="s">
+        <v>16</v>
+      </c>
+      <c r="M277" t="s">
+        <v>16</v>
+      </c>
+      <c r="N277">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O277">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="278" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E278" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K278" t="b">
+        <v>0</v>
+      </c>
+      <c r="L278" t="s">
+        <v>16</v>
+      </c>
+      <c r="M278" t="s">
+        <v>16</v>
+      </c>
+      <c r="N278">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O278">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="279" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E279" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K279" t="b">
+        <v>0</v>
+      </c>
+      <c r="L279" t="s">
+        <v>16</v>
+      </c>
+      <c r="M279" t="s">
+        <v>16</v>
+      </c>
+      <c r="N279">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O279">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E280" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K280" t="b">
+        <v>0</v>
+      </c>
+      <c r="L280" t="s">
+        <v>16</v>
+      </c>
+      <c r="M280" t="s">
+        <v>16</v>
+      </c>
+      <c r="N280">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O280">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="281" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E281" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K281" t="b">
+        <v>0</v>
+      </c>
+      <c r="L281" t="s">
+        <v>16</v>
+      </c>
+      <c r="M281" t="s">
+        <v>16</v>
+      </c>
+      <c r="N281">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O281">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E282" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K282" t="b">
+        <v>0</v>
+      </c>
+      <c r="L282" t="s">
+        <v>16</v>
+      </c>
+      <c r="M282" t="s">
+        <v>16</v>
+      </c>
+      <c r="N282">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O282">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="283" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E283" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K283" t="b">
+        <v>0</v>
+      </c>
+      <c r="L283" t="s">
+        <v>16</v>
+      </c>
+      <c r="M283" t="s">
+        <v>16</v>
+      </c>
+      <c r="N283">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O283">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="284" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E284" s="5">
+        <f t="shared" si="14"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K284" t="b">
+        <v>0</v>
+      </c>
+      <c r="L284" t="s">
+        <v>16</v>
+      </c>
+      <c r="M284" t="s">
+        <v>16</v>
+      </c>
+      <c r="N284">
+        <f t="shared" si="15"/>
+        <v>9</v>
+      </c>
+      <c r="O284">
+        <f t="shared" si="16"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="285" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E285" s="5">
+        <f t="shared" ref="E285:E348" si="17">ROUND((D285-32)*(5/9),1)</f>
+        <v>-17.8</v>
+      </c>
+      <c r="K285" t="b">
+        <v>0</v>
+      </c>
+      <c r="L285" t="s">
+        <v>16</v>
+      </c>
+      <c r="M285" t="s">
+        <v>16</v>
+      </c>
+      <c r="N285">
+        <f t="shared" ref="N285:N348" si="18">IF(I285&lt;9,2,IF(I285&lt;=14,0,IF(I285&lt;=20,1,IF(I285&lt;=29,2,3))))+IF(H285&lt;=40,2,IF(H285&lt;=50,1,IF(H285&lt;=100,0,IF(H285&lt;=110,1,IF(H285&lt;=129,2,3)))))+IF(F285&lt;=70,3,IF(F285&lt;=80,2,IF(F285&lt;=100,1,IF(F285&lt;200,0,IF(F285&gt;=200,2,0)))))+IF(E285&lt;35,2,IF(E285&lt;=38.4,0,2))+IF(M285="Alert",0,IF(M285="Voice",1,IF(M285="Pain",2,IF(M285="Unresponsive",3,0))))</f>
+        <v>9</v>
+      </c>
+      <c r="O285">
+        <f t="shared" ref="O285:O348" si="19">IF(I285&lt;=8,3,IF(I285&lt;=11,1,IF(I285&lt;=20,0,IF(I285&lt;=24,2,3))))
++IF(J285&lt;=91,3,IF(J285&lt;=93,2,IF(J285&lt;=95,1,0)))
++IF(K285=TRUE,2,0)
++IF(F285&lt;=90,3,IF(F285&lt;=100,2,IF(F285&lt;=110,1,IF(F285&lt;=219,0,3))))
++IF(H285&lt;=40,3,IF(H285&lt;=50,1,IF(H285&lt;=90,0,IF(H285&lt;=110,1,IF(H285&lt;=130,2,3)))))
++IF(M285="Alert",0,3)
++IF(E285&lt;=35,3,IF(E285&lt;=36,1,IF(E285&lt;=38,0,IF(E285&lt;=39,1,2))))</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="286" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E286" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K286" t="b">
+        <v>0</v>
+      </c>
+      <c r="L286" t="s">
+        <v>16</v>
+      </c>
+      <c r="M286" t="s">
+        <v>16</v>
+      </c>
+      <c r="N286">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O286">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="287" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E287" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K287" t="b">
+        <v>0</v>
+      </c>
+      <c r="L287" t="s">
+        <v>16</v>
+      </c>
+      <c r="M287" t="s">
+        <v>16</v>
+      </c>
+      <c r="N287">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O287">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="288" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E288" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K288" t="b">
+        <v>0</v>
+      </c>
+      <c r="L288" t="s">
+        <v>16</v>
+      </c>
+      <c r="M288" t="s">
+        <v>16</v>
+      </c>
+      <c r="N288">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O288">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="289" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E289" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K289" t="b">
+        <v>0</v>
+      </c>
+      <c r="L289" t="s">
+        <v>16</v>
+      </c>
+      <c r="M289" t="s">
+        <v>16</v>
+      </c>
+      <c r="N289">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O289">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="290" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E290" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K290" t="b">
+        <v>0</v>
+      </c>
+      <c r="L290" t="s">
+        <v>16</v>
+      </c>
+      <c r="M290" t="s">
+        <v>16</v>
+      </c>
+      <c r="N290">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O290">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="291" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E291" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K291" t="b">
+        <v>0</v>
+      </c>
+      <c r="L291" t="s">
+        <v>16</v>
+      </c>
+      <c r="M291" t="s">
+        <v>16</v>
+      </c>
+      <c r="N291">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O291">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="292" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E292" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K292" t="b">
+        <v>0</v>
+      </c>
+      <c r="L292" t="s">
+        <v>16</v>
+      </c>
+      <c r="M292" t="s">
+        <v>16</v>
+      </c>
+      <c r="N292">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O292">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="293" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E293" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K293" t="b">
+        <v>0</v>
+      </c>
+      <c r="L293" t="s">
+        <v>16</v>
+      </c>
+      <c r="M293" t="s">
+        <v>16</v>
+      </c>
+      <c r="N293">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O293">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="294" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E294" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K294" t="b">
+        <v>0</v>
+      </c>
+      <c r="L294" t="s">
+        <v>16</v>
+      </c>
+      <c r="M294" t="s">
+        <v>16</v>
+      </c>
+      <c r="N294">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O294">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="295" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E295" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K295" t="b">
+        <v>0</v>
+      </c>
+      <c r="L295" t="s">
+        <v>16</v>
+      </c>
+      <c r="M295" t="s">
+        <v>16</v>
+      </c>
+      <c r="N295">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O295">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="296" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E296" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K296" t="b">
+        <v>0</v>
+      </c>
+      <c r="L296" t="s">
+        <v>16</v>
+      </c>
+      <c r="M296" t="s">
+        <v>16</v>
+      </c>
+      <c r="N296">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O296">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="297" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E297" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K297" t="b">
+        <v>0</v>
+      </c>
+      <c r="L297" t="s">
+        <v>16</v>
+      </c>
+      <c r="M297" t="s">
+        <v>16</v>
+      </c>
+      <c r="N297">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O297">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="298" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E298" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K298" t="b">
+        <v>0</v>
+      </c>
+      <c r="L298" t="s">
+        <v>16</v>
+      </c>
+      <c r="M298" t="s">
+        <v>16</v>
+      </c>
+      <c r="N298">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O298">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="299" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E299" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K299" t="b">
+        <v>0</v>
+      </c>
+      <c r="L299" t="s">
+        <v>16</v>
+      </c>
+      <c r="M299" t="s">
+        <v>16</v>
+      </c>
+      <c r="N299">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O299">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="300" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E300" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K300" t="b">
+        <v>0</v>
+      </c>
+      <c r="L300" t="s">
+        <v>16</v>
+      </c>
+      <c r="M300" t="s">
+        <v>16</v>
+      </c>
+      <c r="N300">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O300">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="301" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E301" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K301" t="b">
+        <v>0</v>
+      </c>
+      <c r="L301" t="s">
+        <v>16</v>
+      </c>
+      <c r="M301" t="s">
+        <v>16</v>
+      </c>
+      <c r="N301">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O301">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="302" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E302" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K302" t="b">
+        <v>0</v>
+      </c>
+      <c r="L302" t="s">
+        <v>16</v>
+      </c>
+      <c r="M302" t="s">
+        <v>16</v>
+      </c>
+      <c r="N302">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O302">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="303" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E303" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K303" t="b">
+        <v>0</v>
+      </c>
+      <c r="L303" t="s">
+        <v>16</v>
+      </c>
+      <c r="M303" t="s">
+        <v>16</v>
+      </c>
+      <c r="N303">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O303">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="304" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E304" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K304" t="b">
+        <v>0</v>
+      </c>
+      <c r="L304" t="s">
+        <v>16</v>
+      </c>
+      <c r="M304" t="s">
+        <v>16</v>
+      </c>
+      <c r="N304">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O304">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="305" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E305" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K305" t="b">
+        <v>0</v>
+      </c>
+      <c r="L305" t="s">
+        <v>16</v>
+      </c>
+      <c r="M305" t="s">
+        <v>16</v>
+      </c>
+      <c r="N305">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O305">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="306" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E306" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K306" t="b">
+        <v>0</v>
+      </c>
+      <c r="L306" t="s">
+        <v>16</v>
+      </c>
+      <c r="M306" t="s">
+        <v>16</v>
+      </c>
+      <c r="N306">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O306">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="307" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E307" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K307" t="b">
+        <v>0</v>
+      </c>
+      <c r="L307" t="s">
+        <v>16</v>
+      </c>
+      <c r="M307" t="s">
+        <v>16</v>
+      </c>
+      <c r="N307">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O307">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="308" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E308" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K308" t="b">
+        <v>0</v>
+      </c>
+      <c r="L308" t="s">
+        <v>16</v>
+      </c>
+      <c r="M308" t="s">
+        <v>16</v>
+      </c>
+      <c r="N308">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O308">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="309" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E309" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K309" t="b">
+        <v>0</v>
+      </c>
+      <c r="L309" t="s">
+        <v>16</v>
+      </c>
+      <c r="M309" t="s">
+        <v>16</v>
+      </c>
+      <c r="N309">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O309">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="310" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E310" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K310" t="b">
+        <v>0</v>
+      </c>
+      <c r="L310" t="s">
+        <v>16</v>
+      </c>
+      <c r="M310" t="s">
+        <v>16</v>
+      </c>
+      <c r="N310">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O310">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="311" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E311" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K311" t="b">
+        <v>0</v>
+      </c>
+      <c r="L311" t="s">
+        <v>16</v>
+      </c>
+      <c r="M311" t="s">
+        <v>16</v>
+      </c>
+      <c r="N311">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O311">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="312" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E312" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K312" t="b">
+        <v>0</v>
+      </c>
+      <c r="L312" t="s">
+        <v>16</v>
+      </c>
+      <c r="M312" t="s">
+        <v>16</v>
+      </c>
+      <c r="N312">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O312">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="313" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E313" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K313" t="b">
+        <v>0</v>
+      </c>
+      <c r="L313" t="s">
+        <v>16</v>
+      </c>
+      <c r="M313" t="s">
+        <v>16</v>
+      </c>
+      <c r="N313">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O313">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="314" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E314" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K314" t="b">
+        <v>0</v>
+      </c>
+      <c r="L314" t="s">
+        <v>16</v>
+      </c>
+      <c r="M314" t="s">
+        <v>16</v>
+      </c>
+      <c r="N314">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O314">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="315" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E315" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K315" t="b">
+        <v>0</v>
+      </c>
+      <c r="L315" t="s">
+        <v>16</v>
+      </c>
+      <c r="M315" t="s">
+        <v>16</v>
+      </c>
+      <c r="N315">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O315">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="316" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E316" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K316" t="b">
+        <v>0</v>
+      </c>
+      <c r="L316" t="s">
+        <v>16</v>
+      </c>
+      <c r="M316" t="s">
+        <v>16</v>
+      </c>
+      <c r="N316">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O316">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="317" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E317" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K317" t="b">
+        <v>0</v>
+      </c>
+      <c r="L317" t="s">
+        <v>16</v>
+      </c>
+      <c r="M317" t="s">
+        <v>16</v>
+      </c>
+      <c r="N317">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O317">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="318" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E318" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K318" t="b">
+        <v>0</v>
+      </c>
+      <c r="L318" t="s">
+        <v>16</v>
+      </c>
+      <c r="M318" t="s">
+        <v>16</v>
+      </c>
+      <c r="N318">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O318">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="319" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E319" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K319" t="b">
+        <v>0</v>
+      </c>
+      <c r="L319" t="s">
+        <v>16</v>
+      </c>
+      <c r="M319" t="s">
+        <v>16</v>
+      </c>
+      <c r="N319">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O319">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="320" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E320" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K320" t="b">
+        <v>0</v>
+      </c>
+      <c r="L320" t="s">
+        <v>16</v>
+      </c>
+      <c r="M320" t="s">
+        <v>16</v>
+      </c>
+      <c r="N320">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O320">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="321" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E321" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K321" t="b">
+        <v>0</v>
+      </c>
+      <c r="L321" t="s">
+        <v>16</v>
+      </c>
+      <c r="M321" t="s">
+        <v>16</v>
+      </c>
+      <c r="N321">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O321">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="322" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E322" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K322" t="b">
+        <v>0</v>
+      </c>
+      <c r="L322" t="s">
+        <v>16</v>
+      </c>
+      <c r="M322" t="s">
+        <v>16</v>
+      </c>
+      <c r="N322">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O322">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="323" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E323" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K323" t="b">
+        <v>0</v>
+      </c>
+      <c r="L323" t="s">
+        <v>16</v>
+      </c>
+      <c r="M323" t="s">
+        <v>16</v>
+      </c>
+      <c r="N323">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O323">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="324" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E324" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K324" t="b">
+        <v>0</v>
+      </c>
+      <c r="L324" t="s">
+        <v>16</v>
+      </c>
+      <c r="M324" t="s">
+        <v>16</v>
+      </c>
+      <c r="N324">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O324">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="325" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E325" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K325" t="b">
+        <v>0</v>
+      </c>
+      <c r="L325" t="s">
+        <v>16</v>
+      </c>
+      <c r="M325" t="s">
+        <v>16</v>
+      </c>
+      <c r="N325">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O325">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="326" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E326" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K326" t="b">
+        <v>0</v>
+      </c>
+      <c r="L326" t="s">
+        <v>16</v>
+      </c>
+      <c r="M326" t="s">
+        <v>16</v>
+      </c>
+      <c r="N326">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O326">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="327" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E327" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K327" t="b">
+        <v>0</v>
+      </c>
+      <c r="L327" t="s">
+        <v>16</v>
+      </c>
+      <c r="M327" t="s">
+        <v>16</v>
+      </c>
+      <c r="N327">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O327">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="328" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E328" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K328" t="b">
+        <v>0</v>
+      </c>
+      <c r="L328" t="s">
+        <v>16</v>
+      </c>
+      <c r="M328" t="s">
+        <v>16</v>
+      </c>
+      <c r="N328">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O328">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="329" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E329" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K329" t="b">
+        <v>0</v>
+      </c>
+      <c r="L329" t="s">
+        <v>16</v>
+      </c>
+      <c r="M329" t="s">
+        <v>16</v>
+      </c>
+      <c r="N329">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O329">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="330" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E330" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K330" t="b">
+        <v>0</v>
+      </c>
+      <c r="L330" t="s">
+        <v>16</v>
+      </c>
+      <c r="M330" t="s">
+        <v>16</v>
+      </c>
+      <c r="N330">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O330">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="331" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E331" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K331" t="b">
+        <v>0</v>
+      </c>
+      <c r="L331" t="s">
+        <v>16</v>
+      </c>
+      <c r="M331" t="s">
+        <v>16</v>
+      </c>
+      <c r="N331">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O331">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="332" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E332" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K332" t="b">
+        <v>0</v>
+      </c>
+      <c r="L332" t="s">
+        <v>16</v>
+      </c>
+      <c r="M332" t="s">
+        <v>16</v>
+      </c>
+      <c r="N332">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O332">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="333" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E333" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K333" t="b">
+        <v>0</v>
+      </c>
+      <c r="L333" t="s">
+        <v>16</v>
+      </c>
+      <c r="M333" t="s">
+        <v>16</v>
+      </c>
+      <c r="N333">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O333">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="334" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E334" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K334" t="b">
+        <v>0</v>
+      </c>
+      <c r="L334" t="s">
+        <v>16</v>
+      </c>
+      <c r="M334" t="s">
+        <v>16</v>
+      </c>
+      <c r="N334">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O334">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="335" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E335" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K335" t="b">
+        <v>0</v>
+      </c>
+      <c r="L335" t="s">
+        <v>16</v>
+      </c>
+      <c r="M335" t="s">
+        <v>16</v>
+      </c>
+      <c r="N335">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O335">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="336" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E336" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K336" t="b">
+        <v>0</v>
+      </c>
+      <c r="L336" t="s">
+        <v>16</v>
+      </c>
+      <c r="M336" t="s">
+        <v>16</v>
+      </c>
+      <c r="N336">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O336">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="337" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E337" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K337" t="b">
+        <v>0</v>
+      </c>
+      <c r="L337" t="s">
+        <v>16</v>
+      </c>
+      <c r="M337" t="s">
+        <v>16</v>
+      </c>
+      <c r="N337">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O337">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="338" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E338" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K338" t="b">
+        <v>0</v>
+      </c>
+      <c r="L338" t="s">
+        <v>16</v>
+      </c>
+      <c r="M338" t="s">
+        <v>16</v>
+      </c>
+      <c r="N338">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O338">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="339" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E339" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K339" t="b">
+        <v>0</v>
+      </c>
+      <c r="L339" t="s">
+        <v>16</v>
+      </c>
+      <c r="M339" t="s">
+        <v>16</v>
+      </c>
+      <c r="N339">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O339">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="340" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E340" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K340" t="b">
+        <v>0</v>
+      </c>
+      <c r="L340" t="s">
+        <v>16</v>
+      </c>
+      <c r="M340" t="s">
+        <v>16</v>
+      </c>
+      <c r="N340">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O340">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="341" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E341" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K341" t="b">
+        <v>0</v>
+      </c>
+      <c r="L341" t="s">
+        <v>16</v>
+      </c>
+      <c r="M341" t="s">
+        <v>16</v>
+      </c>
+      <c r="N341">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O341">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="342" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E342" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K342" t="b">
+        <v>0</v>
+      </c>
+      <c r="L342" t="s">
+        <v>16</v>
+      </c>
+      <c r="M342" t="s">
+        <v>16</v>
+      </c>
+      <c r="N342">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O342">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="343" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E343" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K343" t="b">
+        <v>0</v>
+      </c>
+      <c r="L343" t="s">
+        <v>16</v>
+      </c>
+      <c r="M343" t="s">
+        <v>16</v>
+      </c>
+      <c r="N343">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O343">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="344" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E344" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K344" t="b">
+        <v>0</v>
+      </c>
+      <c r="L344" t="s">
+        <v>16</v>
+      </c>
+      <c r="M344" t="s">
+        <v>16</v>
+      </c>
+      <c r="N344">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O344">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="345" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E345" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K345" t="b">
+        <v>0</v>
+      </c>
+      <c r="L345" t="s">
+        <v>16</v>
+      </c>
+      <c r="M345" t="s">
+        <v>16</v>
+      </c>
+      <c r="N345">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O345">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="346" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E346" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K346" t="b">
+        <v>0</v>
+      </c>
+      <c r="L346" t="s">
+        <v>16</v>
+      </c>
+      <c r="M346" t="s">
+        <v>16</v>
+      </c>
+      <c r="N346">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O346">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="347" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E347" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K347" t="b">
+        <v>0</v>
+      </c>
+      <c r="L347" t="s">
+        <v>16</v>
+      </c>
+      <c r="M347" t="s">
+        <v>16</v>
+      </c>
+      <c r="N347">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O347">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="348" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E348" s="5">
+        <f t="shared" si="17"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K348" t="b">
+        <v>0</v>
+      </c>
+      <c r="L348" t="s">
+        <v>16</v>
+      </c>
+      <c r="M348" t="s">
+        <v>16</v>
+      </c>
+      <c r="N348">
+        <f t="shared" si="18"/>
+        <v>9</v>
+      </c>
+      <c r="O348">
+        <f t="shared" si="19"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="349" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E349" s="5">
+        <f t="shared" ref="E349:E351" si="20">ROUND((D349-32)*(5/9),1)</f>
+        <v>-17.8</v>
+      </c>
+      <c r="K349" t="b">
+        <v>0</v>
+      </c>
+      <c r="L349" t="s">
+        <v>16</v>
+      </c>
+      <c r="M349" t="s">
+        <v>16</v>
+      </c>
+      <c r="N349">
+        <f t="shared" ref="N349:N354" si="21">IF(I349&lt;9,2,IF(I349&lt;=14,0,IF(I349&lt;=20,1,IF(I349&lt;=29,2,3))))+IF(H349&lt;=40,2,IF(H349&lt;=50,1,IF(H349&lt;=100,0,IF(H349&lt;=110,1,IF(H349&lt;=129,2,3)))))+IF(F349&lt;=70,3,IF(F349&lt;=80,2,IF(F349&lt;=100,1,IF(F349&lt;200,0,IF(F349&gt;=200,2,0)))))+IF(E349&lt;35,2,IF(E349&lt;=38.4,0,2))+IF(M349="Alert",0,IF(M349="Voice",1,IF(M349="Pain",2,IF(M349="Unresponsive",3,0))))</f>
+        <v>9</v>
+      </c>
+      <c r="O349">
+        <f t="shared" ref="O349:O354" si="22">IF(I349&lt;=8,3,IF(I349&lt;=11,1,IF(I349&lt;=20,0,IF(I349&lt;=24,2,3))))
++IF(J349&lt;=91,3,IF(J349&lt;=93,2,IF(J349&lt;=95,1,0)))
++IF(K349=TRUE,2,0)
++IF(F349&lt;=90,3,IF(F349&lt;=100,2,IF(F349&lt;=110,1,IF(F349&lt;=219,0,3))))
++IF(H349&lt;=40,3,IF(H349&lt;=50,1,IF(H349&lt;=90,0,IF(H349&lt;=110,1,IF(H349&lt;=130,2,3)))))
++IF(M349="Alert",0,3)
++IF(E349&lt;=35,3,IF(E349&lt;=36,1,IF(E349&lt;=38,0,IF(E349&lt;=39,1,2))))</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="350" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E350" s="5">
+        <f t="shared" si="20"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K350" t="b">
+        <v>0</v>
+      </c>
+      <c r="L350" t="s">
+        <v>16</v>
+      </c>
+      <c r="M350" t="s">
+        <v>16</v>
+      </c>
+      <c r="N350">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="O350">
+        <f t="shared" si="22"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="351" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="E351" s="5">
+        <f t="shared" si="20"/>
+        <v>-17.8</v>
+      </c>
+      <c r="K351" t="b">
+        <v>0</v>
+      </c>
+      <c r="L351" t="s">
+        <v>16</v>
+      </c>
+      <c r="M351" t="s">
+        <v>16</v>
+      </c>
+      <c r="N351">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="O351">
+        <f t="shared" si="22"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="352" spans="5:15" x14ac:dyDescent="0.3">
+      <c r="K352" t="b">
+        <v>0</v>
+      </c>
+      <c r="L352" t="s">
+        <v>16</v>
+      </c>
+      <c r="M352" t="s">
+        <v>16</v>
+      </c>
+      <c r="N352">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="O352">
+        <f t="shared" si="22"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="353" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K353" t="b">
+        <v>0</v>
+      </c>
+      <c r="L353" t="s">
+        <v>16</v>
+      </c>
+      <c r="M353" t="s">
+        <v>16</v>
+      </c>
+      <c r="N353">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="O353">
+        <f t="shared" si="22"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="354" spans="11:15" x14ac:dyDescent="0.3">
+      <c r="K354" t="b">
+        <v>0</v>
+      </c>
+      <c r="L354" t="s">
+        <v>16</v>
+      </c>
+      <c r="M354" t="s">
+        <v>16</v>
+      </c>
+      <c r="N354">
+        <f t="shared" si="21"/>
+        <v>9</v>
+      </c>
+      <c r="O354">
+        <f t="shared" si="22"/>
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
